--- a/examples/Agilent/ใบสั่งงาน JOB 1.xlsx
+++ b/examples/Agilent/ใบสั่งงาน JOB 1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\vatska\software\examples\Agilent\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1A45400-00DA-4CE2-A871-BE73F68F989E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A206FD7-49A1-4013-A5F4-D7A05BDDFE86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="958" xr2:uid="{4F180DBB-2D27-44A5-BB20-72766F3B0AE8}"/>
+    <workbookView xWindow="-28800" yWindow="690" windowWidth="28800" windowHeight="15150" tabRatio="958" activeTab="4" xr2:uid="{4F180DBB-2D27-44A5-BB20-72766F3B0AE8}"/>
   </bookViews>
   <sheets>
     <sheet name="ใบงาน Agilent_JOB 1.1" sheetId="17" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="252">
   <si>
     <t>ABW00002</t>
   </si>
@@ -855,6 +855,9 @@
   </si>
   <si>
     <t>PO12345</t>
+  </si>
+  <si>
+    <t>xxx</t>
   </si>
 </sst>
 </file>
@@ -1273,7 +1276,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="284">
+  <cellXfs count="281">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1506,7 +1509,6 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1565,14 +1567,7 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="8" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="8" fillId="6" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1622,6 +1617,8 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="25" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="8" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2051,13 +2048,12 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="25" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="3" builtinId="3"/>
@@ -2091,7 +2087,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>1295400</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2546,9 +2542,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1289050</xdr:colOff>
+      <xdr:colOff>1279525</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>9522</xdr:rowOff>
+      <xdr:rowOff>20952</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2674,9 +2670,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1289050</xdr:colOff>
+      <xdr:colOff>1275715</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>28574</xdr:rowOff>
+      <xdr:rowOff>19049</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3310,86 +3306,86 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="23.25" customHeight="1">
-      <c r="A1" s="173" t="s">
+      <c r="A1" s="171" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="173"/>
-      <c r="C1" s="173"/>
-      <c r="D1" s="173"/>
-      <c r="E1" s="173"/>
-      <c r="F1" s="173"/>
-      <c r="G1" s="173"/>
-      <c r="H1" s="173"/>
-      <c r="I1" s="173"/>
-      <c r="J1" s="173"/>
-      <c r="K1" s="173"/>
-      <c r="L1" s="173"/>
-      <c r="M1" s="173"/>
-      <c r="N1" s="173"/>
+      <c r="B1" s="171"/>
+      <c r="C1" s="171"/>
+      <c r="D1" s="171"/>
+      <c r="E1" s="171"/>
+      <c r="F1" s="171"/>
+      <c r="G1" s="171"/>
+      <c r="H1" s="171"/>
+      <c r="I1" s="171"/>
+      <c r="J1" s="171"/>
+      <c r="K1" s="171"/>
+      <c r="L1" s="171"/>
+      <c r="M1" s="171"/>
+      <c r="N1" s="171"/>
     </row>
     <row r="2" spans="1:15" ht="12" customHeight="1">
-      <c r="A2" s="173"/>
-      <c r="B2" s="173"/>
-      <c r="C2" s="173"/>
-      <c r="D2" s="173"/>
-      <c r="E2" s="173"/>
-      <c r="F2" s="173"/>
-      <c r="G2" s="173"/>
-      <c r="H2" s="173"/>
-      <c r="I2" s="173"/>
-      <c r="J2" s="173"/>
-      <c r="K2" s="173"/>
-      <c r="L2" s="173"/>
-      <c r="M2" s="173"/>
-      <c r="N2" s="173"/>
+      <c r="A2" s="171"/>
+      <c r="B2" s="171"/>
+      <c r="C2" s="171"/>
+      <c r="D2" s="171"/>
+      <c r="E2" s="171"/>
+      <c r="F2" s="171"/>
+      <c r="G2" s="171"/>
+      <c r="H2" s="171"/>
+      <c r="I2" s="171"/>
+      <c r="J2" s="171"/>
+      <c r="K2" s="171"/>
+      <c r="L2" s="171"/>
+      <c r="M2" s="171"/>
+      <c r="N2" s="171"/>
     </row>
     <row r="3" spans="1:15" ht="12" customHeight="1">
-      <c r="A3" s="173"/>
-      <c r="B3" s="173"/>
-      <c r="C3" s="173"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="173"/>
-      <c r="F3" s="173"/>
-      <c r="G3" s="173"/>
-      <c r="H3" s="173"/>
-      <c r="I3" s="173"/>
-      <c r="J3" s="173"/>
-      <c r="K3" s="173"/>
-      <c r="L3" s="173"/>
-      <c r="M3" s="173"/>
-      <c r="N3" s="173"/>
+      <c r="A3" s="171"/>
+      <c r="B3" s="171"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="171"/>
+      <c r="G3" s="171"/>
+      <c r="H3" s="171"/>
+      <c r="I3" s="171"/>
+      <c r="J3" s="171"/>
+      <c r="K3" s="171"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="171"/>
     </row>
     <row r="4" spans="1:15" ht="12" customHeight="1">
-      <c r="A4" s="173"/>
-      <c r="B4" s="173"/>
-      <c r="C4" s="173"/>
-      <c r="D4" s="173"/>
-      <c r="E4" s="173"/>
-      <c r="F4" s="173"/>
-      <c r="G4" s="173"/>
-      <c r="H4" s="173"/>
-      <c r="I4" s="173"/>
-      <c r="J4" s="173"/>
-      <c r="K4" s="173"/>
-      <c r="L4" s="173"/>
-      <c r="M4" s="173"/>
-      <c r="N4" s="173"/>
+      <c r="A4" s="171"/>
+      <c r="B4" s="171"/>
+      <c r="C4" s="171"/>
+      <c r="D4" s="171"/>
+      <c r="E4" s="171"/>
+      <c r="F4" s="171"/>
+      <c r="G4" s="171"/>
+      <c r="H4" s="171"/>
+      <c r="I4" s="171"/>
+      <c r="J4" s="171"/>
+      <c r="K4" s="171"/>
+      <c r="L4" s="171"/>
+      <c r="M4" s="171"/>
+      <c r="N4" s="171"/>
     </row>
     <row r="5" spans="1:15" ht="12" customHeight="1">
-      <c r="A5" s="173"/>
-      <c r="B5" s="173"/>
-      <c r="C5" s="173"/>
-      <c r="D5" s="173"/>
-      <c r="E5" s="173"/>
-      <c r="F5" s="173"/>
-      <c r="G5" s="173"/>
-      <c r="H5" s="173"/>
-      <c r="I5" s="173"/>
-      <c r="J5" s="173"/>
-      <c r="K5" s="173"/>
-      <c r="L5" s="173"/>
-      <c r="M5" s="173"/>
-      <c r="N5" s="173"/>
+      <c r="A5" s="171"/>
+      <c r="B5" s="171"/>
+      <c r="C5" s="171"/>
+      <c r="D5" s="171"/>
+      <c r="E5" s="171"/>
+      <c r="F5" s="171"/>
+      <c r="G5" s="171"/>
+      <c r="H5" s="171"/>
+      <c r="I5" s="171"/>
+      <c r="J5" s="171"/>
+      <c r="K5" s="171"/>
+      <c r="L5" s="171"/>
+      <c r="M5" s="171"/>
+      <c r="N5" s="171"/>
     </row>
     <row r="6" spans="1:15" ht="22.8">
       <c r="A6" s="11" t="s">
@@ -3404,7 +3400,7 @@
       <c r="A7" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="283">
+      <c r="B7" s="134">
         <v>46244</v>
       </c>
       <c r="C7" s="31"/>
@@ -3412,19 +3408,20 @@
         <v>84</v>
       </c>
       <c r="E7" s="13"/>
-      <c r="F7" s="93"/>
-      <c r="G7" s="93"/>
+      <c r="F7" s="92" t="s">
+        <v>251</v>
+      </c>
+      <c r="G7" s="92"/>
       <c r="J7" s="13"/>
       <c r="K7" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="L7" s="31" t="s">
+      <c r="M7" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="M7" s="94">
+      <c r="N7" s="93">
         <v>20260803</v>
       </c>
-      <c r="N7" s="92"/>
       <c r="O7" s="13"/>
     </row>
     <row r="8" spans="1:15" s="14" customFormat="1" ht="21" customHeight="1">
@@ -3438,17 +3435,16 @@
         <v>101</v>
       </c>
       <c r="E8" s="13"/>
-      <c r="F8" s="104" t="s">
+      <c r="F8" s="103" t="s">
         <v>5</v>
       </c>
       <c r="J8" s="13"/>
       <c r="K8" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="M8" s="119">
+      <c r="N8" s="115">
         <v>2000</v>
       </c>
-      <c r="N8" s="117"/>
       <c r="O8" s="13"/>
     </row>
     <row r="9" spans="1:15" s="14" customFormat="1" ht="21" customHeight="1">
@@ -3469,10 +3465,9 @@
       <c r="K9" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="M9" s="102" t="s">
+      <c r="N9" s="101" t="s">
         <v>250</v>
       </c>
-      <c r="N9" s="102"/>
       <c r="O9" s="13"/>
     </row>
     <row r="10" spans="1:15" s="14" customFormat="1" ht="21" customHeight="1">
@@ -3482,7 +3477,6 @@
       <c r="F10" s="13"/>
       <c r="J10" s="13"/>
       <c r="K10" s="13"/>
-      <c r="N10" s="13"/>
       <c r="O10" s="13"/>
     </row>
     <row r="11" spans="1:15" s="14" customFormat="1" ht="21" customHeight="1">
@@ -3545,55 +3539,55 @@
       <c r="N14" s="19"/>
       <c r="O14" s="19"/>
     </row>
-    <row r="15" spans="1:15" s="109" customFormat="1" ht="21" customHeight="1">
-      <c r="A15" s="176" t="s">
+    <row r="15" spans="1:15" s="108" customFormat="1" ht="21" customHeight="1">
+      <c r="A15" s="174" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="177" t="s">
+      <c r="B15" s="175" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="176" t="s">
+      <c r="C15" s="174" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="176" t="s">
+      <c r="D15" s="174" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="180" t="s">
+      <c r="E15" s="178" t="s">
         <v>50</v>
       </c>
-      <c r="F15" s="182" t="s">
+      <c r="F15" s="180" t="s">
         <v>51</v>
       </c>
-      <c r="G15" s="138" t="s">
+      <c r="G15" s="136" t="s">
         <v>50</v>
       </c>
-      <c r="H15" s="167" t="s">
+      <c r="H15" s="165" t="s">
         <v>49</v>
       </c>
-      <c r="I15" s="111"/>
-      <c r="J15" s="112"/>
-      <c r="K15" s="175"/>
-      <c r="L15" s="113"/>
-      <c r="M15" s="113"/>
-      <c r="N15" s="113"/>
-      <c r="O15" s="113"/>
-    </row>
-    <row r="16" spans="1:15" s="109" customFormat="1" ht="21" customHeight="1">
-      <c r="A16" s="176"/>
-      <c r="B16" s="178"/>
-      <c r="C16" s="176"/>
-      <c r="D16" s="176"/>
-      <c r="E16" s="181"/>
-      <c r="F16" s="183"/>
-      <c r="G16" s="167"/>
-      <c r="H16" s="168"/>
-      <c r="I16" s="111"/>
-      <c r="J16" s="112"/>
-      <c r="K16" s="175"/>
-      <c r="L16" s="113"/>
-      <c r="M16" s="113"/>
-      <c r="N16" s="113"/>
-      <c r="O16" s="113"/>
+      <c r="I15" s="110"/>
+      <c r="J15" s="111"/>
+      <c r="K15" s="173"/>
+      <c r="L15" s="112"/>
+      <c r="M15" s="112"/>
+      <c r="N15" s="112"/>
+      <c r="O15" s="112"/>
+    </row>
+    <row r="16" spans="1:15" s="108" customFormat="1" ht="21" customHeight="1">
+      <c r="A16" s="174"/>
+      <c r="B16" s="176"/>
+      <c r="C16" s="174"/>
+      <c r="D16" s="174"/>
+      <c r="E16" s="179"/>
+      <c r="F16" s="181"/>
+      <c r="G16" s="165"/>
+      <c r="H16" s="166"/>
+      <c r="I16" s="110"/>
+      <c r="J16" s="111"/>
+      <c r="K16" s="173"/>
+      <c r="L16" s="112"/>
+      <c r="M16" s="112"/>
+      <c r="N16" s="112"/>
+      <c r="O16" s="112"/>
     </row>
     <row r="17" spans="1:15" s="14" customFormat="1" ht="21" customHeight="1">
       <c r="A17" s="25">
@@ -3609,7 +3603,7 @@
         <v>1</v>
       </c>
       <c r="E17" s="28">
-        <f>D17*M8*(I44+J44)</f>
+        <f>D17*N8*(I44+J44)</f>
         <v>314800</v>
       </c>
       <c r="F17" s="26">
@@ -3623,7 +3617,7 @@
         <f>G17*0.00328/F17</f>
         <v>20.650879999999997</v>
       </c>
-      <c r="K17" s="174" t="s">
+      <c r="K17" s="172" t="s">
         <v>245</v>
       </c>
       <c r="M17" s="20"/>
@@ -3644,7 +3638,7 @@
       <c r="G18" s="30"/>
       <c r="H18" s="30"/>
       <c r="J18" s="13"/>
-      <c r="K18" s="174"/>
+      <c r="K18" s="172"/>
       <c r="M18" s="20"/>
       <c r="N18" s="19"/>
       <c r="O18" s="19"/>
@@ -3674,10 +3668,10 @@
       <c r="A20" s="29">
         <v>4</v>
       </c>
-      <c r="B20" s="156" t="s">
+      <c r="B20" s="154" t="s">
         <v>82</v>
       </c>
-      <c r="C20" s="157"/>
+      <c r="C20" s="155"/>
       <c r="D20" s="18" t="s">
         <v>83</v>
       </c>
@@ -3702,7 +3696,7 @@
         <v>23</v>
       </c>
       <c r="D21" s="29">
-        <f>M8</f>
+        <f>N8</f>
         <v>2000</v>
       </c>
       <c r="E21" s="29"/>
@@ -3726,7 +3720,7 @@
         <v>28</v>
       </c>
       <c r="D22" s="29">
-        <f>M8</f>
+        <f>N8</f>
         <v>2000</v>
       </c>
       <c r="E22" s="29"/>
@@ -3817,91 +3811,91 @@
       <c r="N27" s="13"/>
       <c r="O27" s="13"/>
     </row>
-    <row r="28" spans="1:15" s="109" customFormat="1" ht="30.45" customHeight="1">
-      <c r="A28" s="176" t="s">
+    <row r="28" spans="1:15" s="108" customFormat="1" ht="30.45" customHeight="1">
+      <c r="A28" s="174" t="s">
         <v>33</v>
       </c>
-      <c r="B28" s="177" t="s">
+      <c r="B28" s="175" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="176" t="s">
+      <c r="C28" s="174" t="s">
         <v>31</v>
       </c>
-      <c r="D28" s="176" t="s">
+      <c r="D28" s="174" t="s">
         <v>30</v>
       </c>
-      <c r="E28" s="106"/>
-      <c r="F28" s="167" t="s">
+      <c r="E28" s="105"/>
+      <c r="F28" s="165" t="s">
         <v>92</v>
       </c>
-      <c r="G28" s="138" t="s">
+      <c r="G28" s="136" t="s">
         <v>93</v>
       </c>
-      <c r="H28" s="138"/>
-      <c r="I28" s="138"/>
-      <c r="J28" s="172"/>
-      <c r="K28" s="138" t="s">
+      <c r="H28" s="136"/>
+      <c r="I28" s="136"/>
+      <c r="J28" s="170"/>
+      <c r="K28" s="136" t="s">
         <v>77</v>
       </c>
-      <c r="L28" s="138"/>
-      <c r="M28" s="138"/>
-      <c r="N28" s="138" t="s">
+      <c r="L28" s="136"/>
+      <c r="M28" s="136"/>
+      <c r="N28" s="136" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="29" spans="1:15" s="109" customFormat="1" ht="30.45" customHeight="1">
-      <c r="A29" s="177"/>
-      <c r="B29" s="178"/>
-      <c r="C29" s="176"/>
-      <c r="D29" s="176"/>
-      <c r="E29" s="110"/>
-      <c r="F29" s="179"/>
-      <c r="G29" s="107" t="s">
+    <row r="29" spans="1:15" s="108" customFormat="1" ht="30.45" customHeight="1">
+      <c r="A29" s="175"/>
+      <c r="B29" s="176"/>
+      <c r="C29" s="174"/>
+      <c r="D29" s="174"/>
+      <c r="E29" s="109"/>
+      <c r="F29" s="177"/>
+      <c r="G29" s="106" t="s">
         <v>94</v>
       </c>
-      <c r="H29" s="107" t="s">
+      <c r="H29" s="106" t="s">
         <v>95</v>
       </c>
-      <c r="I29" s="107" t="s">
+      <c r="I29" s="106" t="s">
         <v>96</v>
       </c>
-      <c r="J29" s="108" t="s">
+      <c r="J29" s="107" t="s">
         <v>89</v>
       </c>
-      <c r="K29" s="105" t="s">
+      <c r="K29" s="104" t="s">
         <v>42</v>
       </c>
-      <c r="L29" s="107" t="s">
+      <c r="L29" s="106" t="s">
         <v>39</v>
       </c>
-      <c r="M29" s="107" t="s">
+      <c r="M29" s="106" t="s">
         <v>40</v>
       </c>
-      <c r="N29" s="138"/>
+      <c r="N29" s="136"/>
     </row>
     <row r="30" spans="1:15" s="14" customFormat="1" ht="21" customHeight="1">
-      <c r="A30" s="146">
+      <c r="A30" s="144">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B30" s="158" t="s">
+      <c r="B30" s="156" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="161" t="s">
+      <c r="C30" s="159" t="s">
         <v>57</v>
       </c>
-      <c r="D30" s="164">
+      <c r="D30" s="162">
         <v>1</v>
       </c>
       <c r="E30" s="16"/>
-      <c r="F30" s="169">
-        <f>M8*D30</f>
+      <c r="F30" s="167">
+        <f>N8*D30</f>
         <v>2000</v>
       </c>
       <c r="G30" s="73"/>
       <c r="H30" s="73"/>
       <c r="I30" s="73"/>
       <c r="J30" s="74"/>
-      <c r="K30" s="139" t="s">
+      <c r="K30" s="137" t="s">
         <v>78</v>
       </c>
       <c r="L30" s="16"/>
@@ -3909,113 +3903,113 @@
       <c r="N30" s="45"/>
     </row>
     <row r="31" spans="1:15" s="14" customFormat="1" ht="21" customHeight="1">
-      <c r="A31" s="147"/>
-      <c r="B31" s="159"/>
-      <c r="C31" s="162"/>
-      <c r="D31" s="165"/>
+      <c r="A31" s="145"/>
+      <c r="B31" s="157"/>
+      <c r="C31" s="160"/>
+      <c r="D31" s="163"/>
       <c r="E31" s="16"/>
-      <c r="F31" s="170"/>
+      <c r="F31" s="168"/>
       <c r="G31" s="73"/>
       <c r="H31" s="73"/>
       <c r="I31" s="73"/>
       <c r="J31" s="74"/>
-      <c r="K31" s="139"/>
+      <c r="K31" s="137"/>
       <c r="L31" s="18"/>
       <c r="M31" s="45"/>
       <c r="N31" s="45"/>
     </row>
     <row r="32" spans="1:15" s="14" customFormat="1" ht="21" customHeight="1">
-      <c r="A32" s="147"/>
-      <c r="B32" s="159"/>
-      <c r="C32" s="162"/>
-      <c r="D32" s="165"/>
+      <c r="A32" s="145"/>
+      <c r="B32" s="157"/>
+      <c r="C32" s="160"/>
+      <c r="D32" s="163"/>
       <c r="E32" s="16"/>
-      <c r="F32" s="170"/>
+      <c r="F32" s="168"/>
       <c r="G32" s="73"/>
       <c r="H32" s="73"/>
       <c r="I32" s="73"/>
       <c r="J32" s="74"/>
-      <c r="K32" s="139"/>
+      <c r="K32" s="137"/>
       <c r="L32" s="45"/>
       <c r="M32" s="45"/>
       <c r="N32" s="45"/>
     </row>
     <row r="33" spans="1:15" s="14" customFormat="1" ht="21" customHeight="1">
-      <c r="A33" s="147"/>
-      <c r="B33" s="159"/>
-      <c r="C33" s="162"/>
-      <c r="D33" s="165"/>
+      <c r="A33" s="145"/>
+      <c r="B33" s="157"/>
+      <c r="C33" s="160"/>
+      <c r="D33" s="163"/>
       <c r="E33" s="16"/>
-      <c r="F33" s="170"/>
+      <c r="F33" s="168"/>
       <c r="G33" s="73"/>
       <c r="H33" s="73"/>
       <c r="I33" s="73"/>
       <c r="J33" s="74"/>
-      <c r="K33" s="139"/>
+      <c r="K33" s="137"/>
       <c r="L33" s="45"/>
       <c r="M33" s="45"/>
       <c r="N33" s="45"/>
     </row>
     <row r="34" spans="1:15" s="14" customFormat="1" ht="21" customHeight="1">
-      <c r="A34" s="147"/>
-      <c r="B34" s="159"/>
-      <c r="C34" s="162"/>
-      <c r="D34" s="165"/>
+      <c r="A34" s="145"/>
+      <c r="B34" s="157"/>
+      <c r="C34" s="160"/>
+      <c r="D34" s="163"/>
       <c r="E34" s="16"/>
-      <c r="F34" s="170"/>
+      <c r="F34" s="168"/>
       <c r="G34" s="73"/>
       <c r="H34" s="73"/>
       <c r="I34" s="73"/>
       <c r="J34" s="74"/>
-      <c r="K34" s="139"/>
+      <c r="K34" s="137"/>
       <c r="L34" s="45"/>
       <c r="M34" s="45"/>
       <c r="N34" s="45"/>
     </row>
     <row r="35" spans="1:15" s="14" customFormat="1" ht="21" customHeight="1">
-      <c r="A35" s="147"/>
-      <c r="B35" s="159"/>
-      <c r="C35" s="162"/>
-      <c r="D35" s="165"/>
+      <c r="A35" s="145"/>
+      <c r="B35" s="157"/>
+      <c r="C35" s="160"/>
+      <c r="D35" s="163"/>
       <c r="E35" s="18"/>
-      <c r="F35" s="170"/>
+      <c r="F35" s="168"/>
       <c r="G35" s="73"/>
       <c r="H35" s="73"/>
       <c r="I35" s="73"/>
       <c r="J35" s="74"/>
-      <c r="K35" s="139"/>
+      <c r="K35" s="137"/>
       <c r="L35" s="45"/>
       <c r="M35" s="45"/>
       <c r="N35" s="45"/>
     </row>
     <row r="36" spans="1:15" s="14" customFormat="1" ht="21" customHeight="1">
-      <c r="A36" s="147"/>
-      <c r="B36" s="159"/>
-      <c r="C36" s="162"/>
-      <c r="D36" s="165"/>
+      <c r="A36" s="145"/>
+      <c r="B36" s="157"/>
+      <c r="C36" s="160"/>
+      <c r="D36" s="163"/>
       <c r="E36" s="18"/>
-      <c r="F36" s="170"/>
+      <c r="F36" s="168"/>
       <c r="G36" s="73"/>
       <c r="H36" s="73"/>
       <c r="I36" s="73"/>
       <c r="J36" s="74"/>
-      <c r="K36" s="139"/>
+      <c r="K36" s="137"/>
       <c r="L36" s="45"/>
       <c r="M36" s="45"/>
       <c r="N36" s="45"/>
     </row>
     <row r="37" spans="1:15" s="14" customFormat="1" ht="21" customHeight="1">
-      <c r="A37" s="148"/>
-      <c r="B37" s="160"/>
-      <c r="C37" s="163"/>
-      <c r="D37" s="166"/>
+      <c r="A37" s="146"/>
+      <c r="B37" s="158"/>
+      <c r="C37" s="161"/>
+      <c r="D37" s="164"/>
       <c r="E37" s="18"/>
-      <c r="F37" s="171"/>
+      <c r="F37" s="169"/>
       <c r="G37" s="73"/>
       <c r="H37" s="73"/>
       <c r="I37" s="73"/>
       <c r="J37" s="74"/>
-      <c r="K37" s="139"/>
+      <c r="K37" s="137"/>
       <c r="L37" s="45"/>
       <c r="M37" s="45"/>
       <c r="N37" s="45"/>
@@ -4054,75 +4048,75 @@
       <c r="O40" s="13"/>
     </row>
     <row r="41" spans="1:15" s="22" customFormat="1" ht="21" hidden="1" customHeight="1">
-      <c r="A41" s="140" t="s">
+      <c r="A41" s="138" t="s">
         <v>33</v>
       </c>
-      <c r="B41" s="140" t="s">
+      <c r="B41" s="138" t="s">
         <v>34</v>
       </c>
-      <c r="C41" s="140" t="s">
+      <c r="C41" s="138" t="s">
         <v>35</v>
       </c>
-      <c r="D41" s="143" t="s">
+      <c r="D41" s="141" t="s">
         <v>35</v>
       </c>
       <c r="E41" s="9"/>
-      <c r="F41" s="140" t="s">
+      <c r="F41" s="138" t="s">
         <v>36</v>
       </c>
-      <c r="G41" s="140" t="s">
+      <c r="G41" s="138" t="s">
         <v>31</v>
       </c>
-      <c r="H41" s="153" t="s">
+      <c r="H41" s="151" t="s">
         <v>46</v>
       </c>
-      <c r="I41" s="153" t="s">
+      <c r="I41" s="151" t="s">
         <v>41</v>
       </c>
-      <c r="J41" s="153" t="s">
+      <c r="J41" s="151" t="s">
         <v>42</v>
       </c>
-      <c r="K41" s="153" t="s">
+      <c r="K41" s="151" t="s">
         <v>70</v>
       </c>
-      <c r="L41" s="149" t="s">
+      <c r="L41" s="147" t="s">
         <v>37</v>
       </c>
-      <c r="M41" s="150"/>
-      <c r="N41" s="149" t="s">
+      <c r="M41" s="148"/>
+      <c r="N41" s="147" t="s">
         <v>38</v>
       </c>
-      <c r="O41" s="150"/>
+      <c r="O41" s="148"/>
     </row>
     <row r="42" spans="1:15" s="22" customFormat="1" ht="21" hidden="1" customHeight="1">
-      <c r="A42" s="141"/>
-      <c r="B42" s="141"/>
-      <c r="C42" s="141"/>
-      <c r="D42" s="144"/>
+      <c r="A42" s="139"/>
+      <c r="B42" s="139"/>
+      <c r="C42" s="139"/>
+      <c r="D42" s="142"/>
       <c r="E42" s="1"/>
-      <c r="F42" s="141"/>
-      <c r="G42" s="141"/>
-      <c r="H42" s="154"/>
-      <c r="I42" s="154"/>
-      <c r="J42" s="154"/>
-      <c r="K42" s="154"/>
-      <c r="L42" s="151"/>
-      <c r="M42" s="152"/>
-      <c r="N42" s="151"/>
-      <c r="O42" s="152"/>
+      <c r="F42" s="139"/>
+      <c r="G42" s="139"/>
+      <c r="H42" s="152"/>
+      <c r="I42" s="152"/>
+      <c r="J42" s="152"/>
+      <c r="K42" s="152"/>
+      <c r="L42" s="149"/>
+      <c r="M42" s="150"/>
+      <c r="N42" s="149"/>
+      <c r="O42" s="150"/>
     </row>
     <row r="43" spans="1:15" s="22" customFormat="1" ht="21" hidden="1" customHeight="1">
-      <c r="A43" s="142"/>
-      <c r="B43" s="142"/>
-      <c r="C43" s="142"/>
-      <c r="D43" s="145"/>
+      <c r="A43" s="140"/>
+      <c r="B43" s="140"/>
+      <c r="C43" s="140"/>
+      <c r="D43" s="143"/>
       <c r="E43" s="10"/>
-      <c r="F43" s="142"/>
-      <c r="G43" s="142"/>
-      <c r="H43" s="155"/>
-      <c r="I43" s="155"/>
-      <c r="J43" s="155"/>
-      <c r="K43" s="155"/>
+      <c r="F43" s="140"/>
+      <c r="G43" s="140"/>
+      <c r="H43" s="153"/>
+      <c r="I43" s="153"/>
+      <c r="J43" s="153"/>
+      <c r="K43" s="153"/>
       <c r="L43" s="5" t="s">
         <v>39</v>
       </c>
@@ -4298,101 +4292,101 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="23.25" customHeight="1">
-      <c r="A1" s="173" t="s">
+      <c r="A1" s="171" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="173"/>
-      <c r="C1" s="173"/>
-      <c r="D1" s="173"/>
-      <c r="E1" s="173"/>
-      <c r="F1" s="173"/>
-      <c r="G1" s="173"/>
-      <c r="H1" s="173"/>
-      <c r="I1" s="173"/>
-      <c r="J1" s="173"/>
-      <c r="K1" s="173"/>
-      <c r="L1" s="173"/>
-      <c r="M1" s="173"/>
-      <c r="N1" s="173"/>
-      <c r="O1" s="173"/>
-      <c r="P1" s="173"/>
-      <c r="Q1" s="173"/>
+      <c r="B1" s="171"/>
+      <c r="C1" s="171"/>
+      <c r="D1" s="171"/>
+      <c r="E1" s="171"/>
+      <c r="F1" s="171"/>
+      <c r="G1" s="171"/>
+      <c r="H1" s="171"/>
+      <c r="I1" s="171"/>
+      <c r="J1" s="171"/>
+      <c r="K1" s="171"/>
+      <c r="L1" s="171"/>
+      <c r="M1" s="171"/>
+      <c r="N1" s="171"/>
+      <c r="O1" s="171"/>
+      <c r="P1" s="171"/>
+      <c r="Q1" s="171"/>
     </row>
     <row r="2" spans="1:18" ht="11.7" customHeight="1">
-      <c r="A2" s="173"/>
-      <c r="B2" s="173"/>
-      <c r="C2" s="173"/>
-      <c r="D2" s="173"/>
-      <c r="E2" s="173"/>
-      <c r="F2" s="173"/>
-      <c r="G2" s="173"/>
-      <c r="H2" s="173"/>
-      <c r="I2" s="173"/>
-      <c r="J2" s="173"/>
-      <c r="K2" s="173"/>
-      <c r="L2" s="173"/>
-      <c r="M2" s="173"/>
-      <c r="N2" s="173"/>
-      <c r="O2" s="173"/>
-      <c r="P2" s="173"/>
-      <c r="Q2" s="173"/>
+      <c r="A2" s="171"/>
+      <c r="B2" s="171"/>
+      <c r="C2" s="171"/>
+      <c r="D2" s="171"/>
+      <c r="E2" s="171"/>
+      <c r="F2" s="171"/>
+      <c r="G2" s="171"/>
+      <c r="H2" s="171"/>
+      <c r="I2" s="171"/>
+      <c r="J2" s="171"/>
+      <c r="K2" s="171"/>
+      <c r="L2" s="171"/>
+      <c r="M2" s="171"/>
+      <c r="N2" s="171"/>
+      <c r="O2" s="171"/>
+      <c r="P2" s="171"/>
+      <c r="Q2" s="171"/>
     </row>
     <row r="3" spans="1:18" ht="11.7" customHeight="1">
-      <c r="A3" s="173"/>
-      <c r="B3" s="173"/>
-      <c r="C3" s="173"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="173"/>
-      <c r="F3" s="173"/>
-      <c r="G3" s="173"/>
-      <c r="H3" s="173"/>
-      <c r="I3" s="173"/>
-      <c r="J3" s="173"/>
-      <c r="K3" s="173"/>
-      <c r="L3" s="173"/>
-      <c r="M3" s="173"/>
-      <c r="N3" s="173"/>
-      <c r="O3" s="173"/>
-      <c r="P3" s="173"/>
-      <c r="Q3" s="173"/>
+      <c r="A3" s="171"/>
+      <c r="B3" s="171"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="171"/>
+      <c r="G3" s="171"/>
+      <c r="H3" s="171"/>
+      <c r="I3" s="171"/>
+      <c r="J3" s="171"/>
+      <c r="K3" s="171"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="171"/>
+      <c r="O3" s="171"/>
+      <c r="P3" s="171"/>
+      <c r="Q3" s="171"/>
     </row>
     <row r="4" spans="1:18" ht="11.7" customHeight="1">
-      <c r="A4" s="173"/>
-      <c r="B4" s="173"/>
-      <c r="C4" s="173"/>
-      <c r="D4" s="173"/>
-      <c r="E4" s="173"/>
-      <c r="F4" s="173"/>
-      <c r="G4" s="173"/>
-      <c r="H4" s="173"/>
-      <c r="I4" s="173"/>
-      <c r="J4" s="173"/>
-      <c r="K4" s="173"/>
-      <c r="L4" s="173"/>
-      <c r="M4" s="173"/>
-      <c r="N4" s="173"/>
-      <c r="O4" s="173"/>
-      <c r="P4" s="173"/>
-      <c r="Q4" s="173"/>
+      <c r="A4" s="171"/>
+      <c r="B4" s="171"/>
+      <c r="C4" s="171"/>
+      <c r="D4" s="171"/>
+      <c r="E4" s="171"/>
+      <c r="F4" s="171"/>
+      <c r="G4" s="171"/>
+      <c r="H4" s="171"/>
+      <c r="I4" s="171"/>
+      <c r="J4" s="171"/>
+      <c r="K4" s="171"/>
+      <c r="L4" s="171"/>
+      <c r="M4" s="171"/>
+      <c r="N4" s="171"/>
+      <c r="O4" s="171"/>
+      <c r="P4" s="171"/>
+      <c r="Q4" s="171"/>
     </row>
     <row r="5" spans="1:18" ht="11.7" customHeight="1">
-      <c r="A5" s="173"/>
-      <c r="B5" s="173"/>
-      <c r="C5" s="173"/>
-      <c r="D5" s="173"/>
-      <c r="E5" s="173"/>
-      <c r="F5" s="173"/>
-      <c r="G5" s="173"/>
-      <c r="H5" s="173"/>
-      <c r="I5" s="173"/>
-      <c r="J5" s="173"/>
-      <c r="K5" s="173"/>
-      <c r="L5" s="173"/>
-      <c r="M5" s="173"/>
-      <c r="N5" s="173"/>
-      <c r="O5" s="173"/>
-      <c r="P5" s="173"/>
-      <c r="Q5" s="173"/>
+      <c r="A5" s="171"/>
+      <c r="B5" s="171"/>
+      <c r="C5" s="171"/>
+      <c r="D5" s="171"/>
+      <c r="E5" s="171"/>
+      <c r="F5" s="171"/>
+      <c r="G5" s="171"/>
+      <c r="H5" s="171"/>
+      <c r="I5" s="171"/>
+      <c r="J5" s="171"/>
+      <c r="K5" s="171"/>
+      <c r="L5" s="171"/>
+      <c r="M5" s="171"/>
+      <c r="N5" s="171"/>
+      <c r="O5" s="171"/>
+      <c r="P5" s="171"/>
+      <c r="Q5" s="171"/>
     </row>
     <row r="6" spans="1:18" ht="22.8">
       <c r="A6" s="11" t="s">
@@ -4403,34 +4397,35 @@
       </c>
     </row>
     <row r="7" spans="1:18" s="42" customFormat="1" ht="21" customHeight="1">
-      <c r="A7" s="96" t="s">
+      <c r="A7" s="95" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="99"/>
-      <c r="C7" s="96" t="s">
+      <c r="B7" s="135">
+        <v>46242</v>
+      </c>
+      <c r="C7" s="95" t="s">
         <v>84</v>
       </c>
-      <c r="D7" s="42">
+      <c r="D7" s="42" t="str">
         <f>'ใบงาน Agilent_JOB 1.1'!F7</f>
-        <v>0</v>
-      </c>
-      <c r="E7" s="96"/>
-      <c r="F7" s="98">
+        <v>xxx</v>
+      </c>
+      <c r="E7" s="95"/>
+      <c r="F7" s="97" t="str">
         <f>'ใบงาน Agilent_JOB 1.1'!F7</f>
-        <v>0</v>
+        <v>xxx</v>
       </c>
       <c r="K7" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="L7" s="99" t="s">
+      <c r="M7" s="98" t="s">
         <v>88</v>
       </c>
-      <c r="M7" s="99">
-        <f>'ใบงาน Agilent_JOB 1.1'!M7</f>
+      <c r="N7" s="98">
+        <f>'ใบงาน Agilent_JOB 1.1'!N7</f>
         <v>20260803</v>
       </c>
-      <c r="N7" s="98"/>
-      <c r="R7" s="96"/>
+      <c r="R7" s="95"/>
     </row>
     <row r="8" spans="1:18" s="14" customFormat="1" ht="21" customHeight="1">
       <c r="A8" s="13" t="s">
@@ -4447,14 +4442,14 @@
         <v>K9801-60098</v>
       </c>
       <c r="E8" s="13"/>
-      <c r="F8" s="128" t="s">
+      <c r="F8" s="124" t="s">
         <v>5</v>
       </c>
       <c r="K8" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="M8" s="120">
-        <f>'ใบงาน Agilent_JOB 1.1'!M8</f>
+      <c r="N8" s="116">
+        <f>'ใบงาน Agilent_JOB 1.1'!N8</f>
         <v>2000</v>
       </c>
       <c r="R8" s="13" t="s">
@@ -4481,8 +4476,8 @@
       <c r="K9" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="M9" s="116" t="str">
-        <f>'ใบงาน Agilent_JOB 1.1'!M9</f>
+      <c r="N9" s="114" t="str">
+        <f>'ใบงาน Agilent_JOB 1.1'!N9</f>
         <v>PO12345</v>
       </c>
       <c r="R9" s="13"/>
@@ -4523,7 +4518,7 @@
       <c r="B12" s="14" t="s">
         <v>244</v>
       </c>
-      <c r="H12" s="95" t="s">
+      <c r="H12" s="94" t="s">
         <v>16</v>
       </c>
       <c r="I12" s="13"/>
@@ -4554,57 +4549,57 @@
       <c r="Q14" s="20"/>
       <c r="R14" s="19"/>
     </row>
-    <row r="15" spans="1:18" s="109" customFormat="1" ht="31.95" customHeight="1">
-      <c r="A15" s="176" t="s">
+    <row r="15" spans="1:18" s="108" customFormat="1" ht="31.95" customHeight="1">
+      <c r="A15" s="174" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="177" t="s">
+      <c r="B15" s="175" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="176" t="s">
+      <c r="C15" s="174" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="176" t="s">
+      <c r="D15" s="174" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="106"/>
-      <c r="F15" s="106"/>
-      <c r="G15" s="106"/>
-      <c r="J15" s="180" t="s">
+      <c r="E15" s="105"/>
+      <c r="F15" s="105"/>
+      <c r="G15" s="105"/>
+      <c r="J15" s="178" t="s">
         <v>50</v>
       </c>
-      <c r="K15" s="182" t="s">
+      <c r="K15" s="180" t="s">
         <v>51</v>
       </c>
-      <c r="L15" s="138" t="s">
+      <c r="L15" s="136" t="s">
         <v>50</v>
       </c>
-      <c r="M15" s="167" t="s">
+      <c r="M15" s="165" t="s">
         <v>49</v>
       </c>
-      <c r="N15" s="111"/>
-      <c r="O15" s="175"/>
-      <c r="P15" s="113"/>
-      <c r="Q15" s="113"/>
-      <c r="R15" s="113"/>
-    </row>
-    <row r="16" spans="1:18" s="109" customFormat="1" ht="31.95" customHeight="1">
-      <c r="A16" s="176"/>
-      <c r="B16" s="178"/>
-      <c r="C16" s="176"/>
-      <c r="D16" s="176"/>
-      <c r="E16" s="110"/>
-      <c r="F16" s="110"/>
-      <c r="G16" s="110"/>
-      <c r="J16" s="181"/>
-      <c r="K16" s="183"/>
-      <c r="L16" s="167"/>
-      <c r="M16" s="168"/>
-      <c r="N16" s="111"/>
-      <c r="O16" s="175"/>
-      <c r="P16" s="113"/>
-      <c r="Q16" s="113"/>
-      <c r="R16" s="113"/>
+      <c r="N15" s="110"/>
+      <c r="O15" s="173"/>
+      <c r="P15" s="112"/>
+      <c r="Q15" s="112"/>
+      <c r="R15" s="112"/>
+    </row>
+    <row r="16" spans="1:18" s="108" customFormat="1" ht="31.95" customHeight="1">
+      <c r="A16" s="174"/>
+      <c r="B16" s="176"/>
+      <c r="C16" s="174"/>
+      <c r="D16" s="174"/>
+      <c r="E16" s="109"/>
+      <c r="F16" s="109"/>
+      <c r="G16" s="109"/>
+      <c r="J16" s="179"/>
+      <c r="K16" s="181"/>
+      <c r="L16" s="165"/>
+      <c r="M16" s="166"/>
+      <c r="N16" s="110"/>
+      <c r="O16" s="173"/>
+      <c r="P16" s="112"/>
+      <c r="Q16" s="112"/>
+      <c r="R16" s="112"/>
     </row>
     <row r="17" spans="1:18" s="14" customFormat="1" ht="21" customHeight="1">
       <c r="A17" s="49">
@@ -4619,20 +4614,20 @@
       <c r="D17" s="60">
         <v>1</v>
       </c>
-      <c r="E17" s="129">
-        <f>M8*D17*(I43+J43)</f>
+      <c r="E17" s="125">
+        <f>N8*D17*(I43+J43)</f>
         <v>1127600</v>
       </c>
       <c r="F17" s="70"/>
       <c r="G17" s="70"/>
-      <c r="J17" s="135">
+      <c r="J17" s="131">
         <f>E17</f>
         <v>1127600</v>
       </c>
       <c r="K17" s="16">
         <v>50</v>
       </c>
-      <c r="L17" s="136">
+      <c r="L17" s="132">
         <f>E17</f>
         <v>1127600</v>
       </c>
@@ -4641,7 +4636,7 @@
         <v>73.970559999999992</v>
       </c>
       <c r="N17" s="20"/>
-      <c r="O17" s="174" t="s">
+      <c r="O17" s="172" t="s">
         <v>245</v>
       </c>
       <c r="Q17" s="20"/>
@@ -4666,7 +4661,7 @@
       <c r="L18" s="45"/>
       <c r="M18" s="45"/>
       <c r="N18" s="20"/>
-      <c r="O18" s="174"/>
+      <c r="O18" s="172"/>
       <c r="Q18" s="20"/>
       <c r="R18" s="19"/>
     </row>
@@ -4698,16 +4693,16 @@
       <c r="A20" s="18">
         <v>4</v>
       </c>
-      <c r="B20" s="130" t="s">
+      <c r="B20" s="126" t="s">
         <v>82</v>
       </c>
-      <c r="C20" s="131"/>
+      <c r="C20" s="127"/>
       <c r="D20" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="E20" s="131"/>
-      <c r="F20" s="131"/>
-      <c r="G20" s="131"/>
+      <c r="E20" s="127"/>
+      <c r="F20" s="127"/>
+      <c r="G20" s="127"/>
       <c r="H20" s="46"/>
       <c r="J20" s="18"/>
       <c r="K20" s="18"/>
@@ -4728,8 +4723,8 @@
       <c r="C21" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="D21" s="132">
-        <f>M8</f>
+      <c r="D21" s="128">
+        <f>N8</f>
         <v>2000</v>
       </c>
       <c r="E21" s="67"/>
@@ -4754,8 +4749,8 @@
       <c r="C22" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="D22" s="132">
-        <f>M8</f>
+      <c r="D22" s="128">
+        <f>N8</f>
         <v>2000</v>
       </c>
       <c r="E22" s="46"/>
@@ -4859,106 +4854,106 @@
       <c r="O26" s="19"/>
       <c r="R26" s="13"/>
     </row>
-    <row r="27" spans="1:18" s="109" customFormat="1" ht="39.450000000000003" customHeight="1">
-      <c r="A27" s="176" t="s">
+    <row r="27" spans="1:18" s="108" customFormat="1" ht="39.450000000000003" customHeight="1">
+      <c r="A27" s="174" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="177" t="s">
+      <c r="B27" s="175" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="176" t="s">
+      <c r="C27" s="174" t="s">
         <v>31</v>
       </c>
-      <c r="D27" s="176" t="s">
+      <c r="D27" s="174" t="s">
         <v>30</v>
       </c>
-      <c r="E27" s="106"/>
-      <c r="F27" s="167" t="s">
+      <c r="E27" s="105"/>
+      <c r="F27" s="165" t="s">
         <v>92</v>
       </c>
-      <c r="G27" s="106"/>
-      <c r="H27" s="176" t="s">
+      <c r="G27" s="105"/>
+      <c r="H27" s="174" t="s">
         <v>31</v>
       </c>
-      <c r="I27" s="176" t="s">
+      <c r="I27" s="174" t="s">
         <v>30</v>
       </c>
-      <c r="J27" s="167" t="s">
+      <c r="J27" s="165" t="s">
         <v>92</v>
       </c>
-      <c r="K27" s="172" t="s">
+      <c r="K27" s="170" t="s">
         <v>93</v>
       </c>
-      <c r="L27" s="184"/>
-      <c r="M27" s="184"/>
-      <c r="N27" s="185"/>
-      <c r="O27" s="183" t="s">
+      <c r="L27" s="182"/>
+      <c r="M27" s="182"/>
+      <c r="N27" s="183"/>
+      <c r="O27" s="181" t="s">
         <v>77</v>
       </c>
-      <c r="P27" s="186"/>
-      <c r="Q27" s="186"/>
-      <c r="R27" s="186"/>
-    </row>
-    <row r="28" spans="1:18" s="109" customFormat="1" ht="34.950000000000003" customHeight="1">
-      <c r="A28" s="177"/>
-      <c r="B28" s="178"/>
-      <c r="C28" s="176"/>
-      <c r="D28" s="176"/>
-      <c r="E28" s="110"/>
-      <c r="F28" s="179"/>
-      <c r="G28" s="110"/>
-      <c r="H28" s="176"/>
-      <c r="I28" s="176"/>
-      <c r="J28" s="179"/>
-      <c r="K28" s="107" t="s">
+      <c r="P27" s="184"/>
+      <c r="Q27" s="184"/>
+      <c r="R27" s="184"/>
+    </row>
+    <row r="28" spans="1:18" s="108" customFormat="1" ht="34.950000000000003" customHeight="1">
+      <c r="A28" s="175"/>
+      <c r="B28" s="176"/>
+      <c r="C28" s="174"/>
+      <c r="D28" s="174"/>
+      <c r="E28" s="109"/>
+      <c r="F28" s="177"/>
+      <c r="G28" s="109"/>
+      <c r="H28" s="174"/>
+      <c r="I28" s="174"/>
+      <c r="J28" s="177"/>
+      <c r="K28" s="106" t="s">
         <v>94</v>
       </c>
-      <c r="L28" s="107" t="s">
+      <c r="L28" s="106" t="s">
         <v>95</v>
       </c>
-      <c r="M28" s="107" t="s">
+      <c r="M28" s="106" t="s">
         <v>96</v>
       </c>
-      <c r="N28" s="108" t="s">
+      <c r="N28" s="107" t="s">
         <v>89</v>
       </c>
-      <c r="O28" s="105" t="s">
+      <c r="O28" s="104" t="s">
         <v>42</v>
       </c>
-      <c r="P28" s="107" t="s">
+      <c r="P28" s="106" t="s">
         <v>39</v>
       </c>
-      <c r="Q28" s="107" t="s">
+      <c r="Q28" s="106" t="s">
         <v>40</v>
       </c>
-      <c r="R28" s="137" t="s">
+      <c r="R28" s="133" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="29" spans="1:18" s="14" customFormat="1" ht="21" customHeight="1">
-      <c r="A29" s="146">
+      <c r="A29" s="144">
         <v>1.2</v>
       </c>
-      <c r="B29" s="158" t="s">
+      <c r="B29" s="156" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="161" t="s">
+      <c r="C29" s="159" t="s">
         <v>58</v>
       </c>
-      <c r="D29" s="158">
+      <c r="D29" s="156">
         <v>1</v>
       </c>
-      <c r="E29" s="123"/>
-      <c r="F29" s="123"/>
-      <c r="G29" s="123"/>
-      <c r="H29" s="161" t="s">
+      <c r="E29" s="119"/>
+      <c r="F29" s="119"/>
+      <c r="G29" s="119"/>
+      <c r="H29" s="159" t="s">
         <v>58</v>
       </c>
-      <c r="I29" s="164">
+      <c r="I29" s="162">
         <v>1</v>
       </c>
-      <c r="J29" s="169">
-        <f>M8*D29</f>
+      <c r="J29" s="167">
+        <f>N8*D29</f>
         <v>2000</v>
       </c>
       <c r="K29" s="73"/>
@@ -4973,16 +4968,16 @@
       <c r="R29" s="30"/>
     </row>
     <row r="30" spans="1:18" s="14" customFormat="1" ht="21" customHeight="1">
-      <c r="A30" s="147"/>
-      <c r="B30" s="159"/>
-      <c r="C30" s="162"/>
-      <c r="D30" s="159"/>
-      <c r="E30" s="124"/>
-      <c r="F30" s="124"/>
-      <c r="G30" s="124"/>
-      <c r="H30" s="162"/>
-      <c r="I30" s="165"/>
-      <c r="J30" s="170"/>
+      <c r="A30" s="145"/>
+      <c r="B30" s="157"/>
+      <c r="C30" s="160"/>
+      <c r="D30" s="157"/>
+      <c r="E30" s="120"/>
+      <c r="F30" s="120"/>
+      <c r="G30" s="120"/>
+      <c r="H30" s="160"/>
+      <c r="I30" s="163"/>
+      <c r="J30" s="168"/>
       <c r="K30" s="73"/>
       <c r="L30" s="73"/>
       <c r="M30" s="73"/>
@@ -4993,16 +4988,16 @@
       <c r="R30" s="30"/>
     </row>
     <row r="31" spans="1:18" s="14" customFormat="1" ht="21" customHeight="1">
-      <c r="A31" s="147"/>
-      <c r="B31" s="159"/>
-      <c r="C31" s="162"/>
-      <c r="D31" s="159"/>
-      <c r="E31" s="124"/>
-      <c r="F31" s="124"/>
-      <c r="G31" s="124"/>
-      <c r="H31" s="162"/>
-      <c r="I31" s="165"/>
-      <c r="J31" s="170"/>
+      <c r="A31" s="145"/>
+      <c r="B31" s="157"/>
+      <c r="C31" s="160"/>
+      <c r="D31" s="157"/>
+      <c r="E31" s="120"/>
+      <c r="F31" s="120"/>
+      <c r="G31" s="120"/>
+      <c r="H31" s="160"/>
+      <c r="I31" s="163"/>
+      <c r="J31" s="168"/>
       <c r="K31" s="73"/>
       <c r="L31" s="73"/>
       <c r="M31" s="73"/>
@@ -5013,16 +5008,16 @@
       <c r="R31" s="30"/>
     </row>
     <row r="32" spans="1:18" s="14" customFormat="1" ht="21" customHeight="1">
-      <c r="A32" s="147"/>
-      <c r="B32" s="159"/>
-      <c r="C32" s="162"/>
-      <c r="D32" s="159"/>
-      <c r="E32" s="124"/>
-      <c r="F32" s="124"/>
-      <c r="G32" s="124"/>
-      <c r="H32" s="162"/>
-      <c r="I32" s="165"/>
-      <c r="J32" s="170"/>
+      <c r="A32" s="145"/>
+      <c r="B32" s="157"/>
+      <c r="C32" s="160"/>
+      <c r="D32" s="157"/>
+      <c r="E32" s="120"/>
+      <c r="F32" s="120"/>
+      <c r="G32" s="120"/>
+      <c r="H32" s="160"/>
+      <c r="I32" s="163"/>
+      <c r="J32" s="168"/>
       <c r="K32" s="73"/>
       <c r="L32" s="73"/>
       <c r="M32" s="73"/>
@@ -5033,16 +5028,16 @@
       <c r="R32" s="30"/>
     </row>
     <row r="33" spans="1:19" s="14" customFormat="1" ht="21" customHeight="1">
-      <c r="A33" s="147"/>
-      <c r="B33" s="159"/>
-      <c r="C33" s="162"/>
-      <c r="D33" s="159"/>
-      <c r="E33" s="124"/>
-      <c r="F33" s="124"/>
-      <c r="G33" s="124"/>
-      <c r="H33" s="162"/>
-      <c r="I33" s="165"/>
-      <c r="J33" s="170"/>
+      <c r="A33" s="145"/>
+      <c r="B33" s="157"/>
+      <c r="C33" s="160"/>
+      <c r="D33" s="157"/>
+      <c r="E33" s="120"/>
+      <c r="F33" s="120"/>
+      <c r="G33" s="120"/>
+      <c r="H33" s="160"/>
+      <c r="I33" s="163"/>
+      <c r="J33" s="168"/>
       <c r="K33" s="73"/>
       <c r="L33" s="73"/>
       <c r="M33" s="73"/>
@@ -5053,16 +5048,16 @@
       <c r="R33" s="30"/>
     </row>
     <row r="34" spans="1:19" s="14" customFormat="1" ht="21" customHeight="1">
-      <c r="A34" s="147"/>
-      <c r="B34" s="159"/>
-      <c r="C34" s="162"/>
-      <c r="D34" s="159"/>
-      <c r="E34" s="124"/>
-      <c r="F34" s="124"/>
-      <c r="G34" s="124"/>
-      <c r="H34" s="162"/>
-      <c r="I34" s="165"/>
-      <c r="J34" s="170"/>
+      <c r="A34" s="145"/>
+      <c r="B34" s="157"/>
+      <c r="C34" s="160"/>
+      <c r="D34" s="157"/>
+      <c r="E34" s="120"/>
+      <c r="F34" s="120"/>
+      <c r="G34" s="120"/>
+      <c r="H34" s="160"/>
+      <c r="I34" s="163"/>
+      <c r="J34" s="168"/>
       <c r="K34" s="73"/>
       <c r="L34" s="73"/>
       <c r="M34" s="73"/>
@@ -5073,16 +5068,16 @@
       <c r="R34" s="30"/>
     </row>
     <row r="35" spans="1:19" s="14" customFormat="1" ht="25.95" customHeight="1">
-      <c r="A35" s="147"/>
-      <c r="B35" s="159"/>
-      <c r="C35" s="162"/>
-      <c r="D35" s="159"/>
-      <c r="E35" s="124"/>
-      <c r="F35" s="124"/>
-      <c r="G35" s="124"/>
-      <c r="H35" s="162"/>
-      <c r="I35" s="165"/>
-      <c r="J35" s="170"/>
+      <c r="A35" s="145"/>
+      <c r="B35" s="157"/>
+      <c r="C35" s="160"/>
+      <c r="D35" s="157"/>
+      <c r="E35" s="120"/>
+      <c r="F35" s="120"/>
+      <c r="G35" s="120"/>
+      <c r="H35" s="160"/>
+      <c r="I35" s="163"/>
+      <c r="J35" s="168"/>
       <c r="K35" s="73"/>
       <c r="L35" s="73"/>
       <c r="M35" s="73"/>
@@ -5093,16 +5088,16 @@
       <c r="R35" s="30"/>
     </row>
     <row r="36" spans="1:19" s="14" customFormat="1" ht="21" customHeight="1">
-      <c r="A36" s="148"/>
-      <c r="B36" s="160"/>
-      <c r="C36" s="163"/>
-      <c r="D36" s="160"/>
-      <c r="E36" s="125"/>
-      <c r="F36" s="125"/>
-      <c r="G36" s="125"/>
-      <c r="H36" s="163"/>
-      <c r="I36" s="166"/>
-      <c r="J36" s="171"/>
+      <c r="A36" s="146"/>
+      <c r="B36" s="158"/>
+      <c r="C36" s="161"/>
+      <c r="D36" s="158"/>
+      <c r="E36" s="121"/>
+      <c r="F36" s="121"/>
+      <c r="G36" s="121"/>
+      <c r="H36" s="161"/>
+      <c r="I36" s="164"/>
+      <c r="J36" s="169"/>
       <c r="K36" s="73"/>
       <c r="L36" s="73"/>
       <c r="M36" s="73"/>
@@ -5140,72 +5135,72 @@
       <c r="R39" s="13"/>
     </row>
     <row r="40" spans="1:19" s="22" customFormat="1" ht="21" hidden="1" customHeight="1">
-      <c r="A40" s="188" t="s">
+      <c r="A40" s="186" t="s">
         <v>33</v>
       </c>
-      <c r="B40" s="188" t="s">
+      <c r="B40" s="186" t="s">
         <v>34</v>
       </c>
-      <c r="C40" s="188" t="s">
+      <c r="C40" s="186" t="s">
         <v>35</v>
       </c>
-      <c r="D40" s="191" t="s">
+      <c r="D40" s="189" t="s">
         <v>35</v>
       </c>
       <c r="E40" s="34"/>
-      <c r="F40" s="188" t="s">
+      <c r="F40" s="186" t="s">
         <v>36</v>
       </c>
-      <c r="G40" s="188" t="s">
+      <c r="G40" s="186" t="s">
         <v>31</v>
       </c>
-      <c r="H40" s="194" t="s">
+      <c r="H40" s="192" t="s">
         <v>46</v>
       </c>
-      <c r="I40" s="194" t="s">
+      <c r="I40" s="192" t="s">
         <v>41</v>
       </c>
-      <c r="J40" s="194" t="s">
+      <c r="J40" s="192" t="s">
         <v>42</v>
       </c>
-      <c r="K40" s="194" t="s">
+      <c r="K40" s="192" t="s">
         <v>70</v>
       </c>
-      <c r="L40" s="197" t="s">
+      <c r="L40" s="195" t="s">
         <v>37</v>
       </c>
-      <c r="M40" s="198"/>
-      <c r="N40" s="187" t="s">
+      <c r="M40" s="196"/>
+      <c r="N40" s="185" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="41" spans="1:19" s="22" customFormat="1" ht="21" hidden="1" customHeight="1">
-      <c r="A41" s="189"/>
-      <c r="B41" s="189"/>
-      <c r="C41" s="189"/>
-      <c r="D41" s="192"/>
-      <c r="F41" s="189"/>
-      <c r="G41" s="189"/>
-      <c r="H41" s="195"/>
-      <c r="I41" s="195"/>
-      <c r="J41" s="195"/>
-      <c r="K41" s="195"/>
-      <c r="L41" s="199"/>
-      <c r="M41" s="200"/>
-      <c r="N41" s="187"/>
+      <c r="A41" s="187"/>
+      <c r="B41" s="187"/>
+      <c r="C41" s="187"/>
+      <c r="D41" s="190"/>
+      <c r="F41" s="187"/>
+      <c r="G41" s="187"/>
+      <c r="H41" s="193"/>
+      <c r="I41" s="193"/>
+      <c r="J41" s="193"/>
+      <c r="K41" s="193"/>
+      <c r="L41" s="197"/>
+      <c r="M41" s="198"/>
+      <c r="N41" s="185"/>
     </row>
     <row r="42" spans="1:19" s="22" customFormat="1" ht="21" hidden="1" customHeight="1">
-      <c r="A42" s="190"/>
-      <c r="B42" s="190"/>
-      <c r="C42" s="190"/>
-      <c r="D42" s="193"/>
+      <c r="A42" s="188"/>
+      <c r="B42" s="188"/>
+      <c r="C42" s="188"/>
+      <c r="D42" s="191"/>
       <c r="E42" s="36"/>
-      <c r="F42" s="190"/>
-      <c r="G42" s="190"/>
-      <c r="H42" s="196"/>
-      <c r="I42" s="196"/>
-      <c r="J42" s="196"/>
-      <c r="K42" s="196"/>
+      <c r="F42" s="188"/>
+      <c r="G42" s="188"/>
+      <c r="H42" s="194"/>
+      <c r="I42" s="194"/>
+      <c r="J42" s="194"/>
+      <c r="K42" s="194"/>
       <c r="L42" s="35" t="s">
         <v>39</v>
       </c>
@@ -5253,9 +5248,9 @@
       <c r="L43" s="40"/>
       <c r="M43" s="40"/>
       <c r="N43" s="40"/>
-      <c r="Q43" s="133"/>
-      <c r="R43" s="133"/>
-      <c r="S43" s="133"/>
+      <c r="Q43" s="129"/>
+      <c r="R43" s="129"/>
+      <c r="S43" s="129"/>
     </row>
     <row r="44" spans="1:19" s="14" customFormat="1" ht="21" hidden="1" customHeight="1">
       <c r="A44" s="13"/>
@@ -5264,9 +5259,9 @@
       <c r="K44" s="13"/>
       <c r="M44" s="13"/>
       <c r="O44" s="13"/>
-      <c r="Q44" s="127"/>
-      <c r="R44" s="134"/>
-      <c r="S44" s="127"/>
+      <c r="Q44" s="123"/>
+      <c r="R44" s="130"/>
+      <c r="S44" s="123"/>
     </row>
     <row r="45" spans="1:19" s="14" customFormat="1" ht="21" hidden="1" customHeight="1">
       <c r="A45" s="13"/>
@@ -5279,9 +5274,9 @@
       <c r="O45" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="Q45" s="127"/>
-      <c r="R45" s="134"/>
-      <c r="S45" s="127"/>
+      <c r="Q45" s="123"/>
+      <c r="R45" s="130"/>
+      <c r="S45" s="123"/>
     </row>
     <row r="46" spans="1:19" s="14" customFormat="1" ht="21" hidden="1" customHeight="1">
       <c r="A46" s="8"/>
@@ -5292,9 +5287,9 @@
         <v>16</v>
       </c>
       <c r="O46" s="13"/>
-      <c r="Q46" s="127"/>
-      <c r="R46" s="134"/>
-      <c r="S46" s="127"/>
+      <c r="Q46" s="123"/>
+      <c r="R46" s="130"/>
+      <c r="S46" s="123"/>
     </row>
     <row r="47" spans="1:19" s="14" customFormat="1" ht="21" customHeight="1">
       <c r="A47" s="13"/>
@@ -5467,86 +5462,86 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="23.25" customHeight="1">
-      <c r="A1" s="173" t="s">
+      <c r="A1" s="171" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="173"/>
-      <c r="C1" s="173"/>
-      <c r="D1" s="173"/>
-      <c r="E1" s="173"/>
-      <c r="F1" s="173"/>
-      <c r="G1" s="173"/>
-      <c r="H1" s="173"/>
-      <c r="I1" s="173"/>
-      <c r="J1" s="173"/>
-      <c r="K1" s="173"/>
-      <c r="L1" s="173"/>
-      <c r="M1" s="173"/>
-      <c r="N1" s="173"/>
+      <c r="B1" s="171"/>
+      <c r="C1" s="171"/>
+      <c r="D1" s="171"/>
+      <c r="E1" s="171"/>
+      <c r="F1" s="171"/>
+      <c r="G1" s="171"/>
+      <c r="H1" s="171"/>
+      <c r="I1" s="171"/>
+      <c r="J1" s="171"/>
+      <c r="K1" s="171"/>
+      <c r="L1" s="171"/>
+      <c r="M1" s="171"/>
+      <c r="N1" s="171"/>
     </row>
     <row r="2" spans="1:15" ht="11.7" customHeight="1">
-      <c r="A2" s="173"/>
-      <c r="B2" s="173"/>
-      <c r="C2" s="173"/>
-      <c r="D2" s="173"/>
-      <c r="E2" s="173"/>
-      <c r="F2" s="173"/>
-      <c r="G2" s="173"/>
-      <c r="H2" s="173"/>
-      <c r="I2" s="173"/>
-      <c r="J2" s="173"/>
-      <c r="K2" s="173"/>
-      <c r="L2" s="173"/>
-      <c r="M2" s="173"/>
-      <c r="N2" s="173"/>
+      <c r="A2" s="171"/>
+      <c r="B2" s="171"/>
+      <c r="C2" s="171"/>
+      <c r="D2" s="171"/>
+      <c r="E2" s="171"/>
+      <c r="F2" s="171"/>
+      <c r="G2" s="171"/>
+      <c r="H2" s="171"/>
+      <c r="I2" s="171"/>
+      <c r="J2" s="171"/>
+      <c r="K2" s="171"/>
+      <c r="L2" s="171"/>
+      <c r="M2" s="171"/>
+      <c r="N2" s="171"/>
     </row>
     <row r="3" spans="1:15" ht="11.7" customHeight="1">
-      <c r="A3" s="173"/>
-      <c r="B3" s="173"/>
-      <c r="C3" s="173"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="173"/>
-      <c r="F3" s="173"/>
-      <c r="G3" s="173"/>
-      <c r="H3" s="173"/>
-      <c r="I3" s="173"/>
-      <c r="J3" s="173"/>
-      <c r="K3" s="173"/>
-      <c r="L3" s="173"/>
-      <c r="M3" s="173"/>
-      <c r="N3" s="173"/>
+      <c r="A3" s="171"/>
+      <c r="B3" s="171"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="171"/>
+      <c r="G3" s="171"/>
+      <c r="H3" s="171"/>
+      <c r="I3" s="171"/>
+      <c r="J3" s="171"/>
+      <c r="K3" s="171"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="171"/>
     </row>
     <row r="4" spans="1:15" ht="11.7" customHeight="1">
-      <c r="A4" s="173"/>
-      <c r="B4" s="173"/>
-      <c r="C4" s="173"/>
-      <c r="D4" s="173"/>
-      <c r="E4" s="173"/>
-      <c r="F4" s="173"/>
-      <c r="G4" s="173"/>
-      <c r="H4" s="173"/>
-      <c r="I4" s="173"/>
-      <c r="J4" s="173"/>
-      <c r="K4" s="173"/>
-      <c r="L4" s="173"/>
-      <c r="M4" s="173"/>
-      <c r="N4" s="173"/>
+      <c r="A4" s="171"/>
+      <c r="B4" s="171"/>
+      <c r="C4" s="171"/>
+      <c r="D4" s="171"/>
+      <c r="E4" s="171"/>
+      <c r="F4" s="171"/>
+      <c r="G4" s="171"/>
+      <c r="H4" s="171"/>
+      <c r="I4" s="171"/>
+      <c r="J4" s="171"/>
+      <c r="K4" s="171"/>
+      <c r="L4" s="171"/>
+      <c r="M4" s="171"/>
+      <c r="N4" s="171"/>
     </row>
     <row r="5" spans="1:15" ht="11.7" customHeight="1">
-      <c r="A5" s="173"/>
-      <c r="B5" s="173"/>
-      <c r="C5" s="173"/>
-      <c r="D5" s="173"/>
-      <c r="E5" s="173"/>
-      <c r="F5" s="173"/>
-      <c r="G5" s="173"/>
-      <c r="H5" s="173"/>
-      <c r="I5" s="173"/>
-      <c r="J5" s="173"/>
-      <c r="K5" s="173"/>
-      <c r="L5" s="173"/>
-      <c r="M5" s="173"/>
-      <c r="N5" s="173"/>
+      <c r="A5" s="171"/>
+      <c r="B5" s="171"/>
+      <c r="C5" s="171"/>
+      <c r="D5" s="171"/>
+      <c r="E5" s="171"/>
+      <c r="F5" s="171"/>
+      <c r="G5" s="171"/>
+      <c r="H5" s="171"/>
+      <c r="I5" s="171"/>
+      <c r="J5" s="171"/>
+      <c r="K5" s="171"/>
+      <c r="L5" s="171"/>
+      <c r="M5" s="171"/>
+      <c r="N5" s="171"/>
     </row>
     <row r="6" spans="1:15" ht="22.8">
       <c r="A6" s="11" t="s">
@@ -5561,29 +5556,30 @@
       <c r="A7" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="31"/>
+      <c r="B7" s="135">
+        <v>46242</v>
+      </c>
       <c r="C7" s="31"/>
       <c r="D7" s="13" t="s">
         <v>84</v>
       </c>
       <c r="E7" s="13"/>
-      <c r="F7" s="33">
+      <c r="F7" s="33" t="str">
         <f>'ใบงาน Agilent_JOB 1.2'!F7</f>
-        <v>0</v>
+        <v>xxx</v>
       </c>
       <c r="G7" s="31"/>
       <c r="J7" s="13"/>
       <c r="K7" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="L7" s="31" t="s">
+      <c r="M7" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="M7" s="31">
-        <f>'ใบงาน Agilent_JOB 1.1'!M7</f>
+      <c r="N7" s="31">
+        <f>'ใบงาน Agilent_JOB 1.1'!N7</f>
         <v>20260803</v>
       </c>
-      <c r="N7" s="33"/>
       <c r="O7" s="13"/>
     </row>
     <row r="8" spans="1:15" s="14" customFormat="1" ht="21" customHeight="1">
@@ -5597,19 +5593,16 @@
         <v>101</v>
       </c>
       <c r="E8" s="13"/>
-      <c r="F8" s="103" t="s">
+      <c r="F8" s="102" t="s">
         <v>5</v>
       </c>
       <c r="J8" s="13"/>
       <c r="K8" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="M8" s="121" cm="1">
-        <f t="array" ref="M8:N8">'ใบงาน Agilent_JOB 1.1'!M8:N8</f>
+      <c r="N8" s="117" cm="1">
+        <f t="array" ref="N8">'ใบงาน Agilent_JOB 1.1'!N8:N8</f>
         <v>2000</v>
-      </c>
-      <c r="N8" s="118">
-        <v>0</v>
       </c>
       <c r="O8" s="13"/>
     </row>
@@ -5631,12 +5624,9 @@
       <c r="K9" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="M9" s="42" t="str" cm="1">
-        <f t="array" ref="M9:N9">'ใบงาน Agilent_JOB 1.1'!M9:N9</f>
+      <c r="N9" s="42" t="str" cm="1">
+        <f t="array" ref="N9">'ใบงาน Agilent_JOB 1.1'!N9:N9</f>
         <v>PO12345</v>
-      </c>
-      <c r="N9" s="42">
-        <v>0</v>
       </c>
       <c r="O9" s="13"/>
     </row>
@@ -5708,55 +5698,55 @@
       <c r="N14" s="19"/>
       <c r="O14" s="19"/>
     </row>
-    <row r="15" spans="1:15" s="109" customFormat="1" ht="21" customHeight="1">
-      <c r="A15" s="176" t="s">
+    <row r="15" spans="1:15" s="108" customFormat="1" ht="21" customHeight="1">
+      <c r="A15" s="174" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="177" t="s">
+      <c r="B15" s="175" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="176" t="s">
+      <c r="C15" s="174" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="176" t="s">
+      <c r="D15" s="174" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="180" t="s">
+      <c r="E15" s="178" t="s">
         <v>50</v>
       </c>
-      <c r="F15" s="182" t="s">
+      <c r="F15" s="180" t="s">
         <v>51</v>
       </c>
-      <c r="G15" s="138" t="s">
+      <c r="G15" s="136" t="s">
         <v>50</v>
       </c>
-      <c r="H15" s="202" t="s">
+      <c r="H15" s="200" t="s">
         <v>49</v>
       </c>
-      <c r="I15" s="113"/>
-      <c r="J15" s="114"/>
-      <c r="K15" s="175"/>
-      <c r="L15" s="113"/>
-      <c r="M15" s="113"/>
-      <c r="N15" s="113"/>
-      <c r="O15" s="113"/>
-    </row>
-    <row r="16" spans="1:15" s="109" customFormat="1" ht="21" customHeight="1">
-      <c r="A16" s="176"/>
-      <c r="B16" s="178"/>
-      <c r="C16" s="176"/>
-      <c r="D16" s="176"/>
-      <c r="E16" s="181"/>
-      <c r="F16" s="183"/>
-      <c r="G16" s="167"/>
-      <c r="H16" s="203"/>
-      <c r="I16" s="113"/>
-      <c r="J16" s="114"/>
-      <c r="K16" s="175"/>
-      <c r="L16" s="113"/>
-      <c r="M16" s="113"/>
-      <c r="N16" s="113"/>
-      <c r="O16" s="113"/>
+      <c r="I15" s="112"/>
+      <c r="J15" s="113"/>
+      <c r="K15" s="173"/>
+      <c r="L15" s="112"/>
+      <c r="M15" s="112"/>
+      <c r="N15" s="112"/>
+      <c r="O15" s="112"/>
+    </row>
+    <row r="16" spans="1:15" s="108" customFormat="1" ht="21" customHeight="1">
+      <c r="A16" s="174"/>
+      <c r="B16" s="176"/>
+      <c r="C16" s="174"/>
+      <c r="D16" s="174"/>
+      <c r="E16" s="179"/>
+      <c r="F16" s="181"/>
+      <c r="G16" s="165"/>
+      <c r="H16" s="201"/>
+      <c r="I16" s="112"/>
+      <c r="J16" s="113"/>
+      <c r="K16" s="173"/>
+      <c r="L16" s="112"/>
+      <c r="M16" s="112"/>
+      <c r="N16" s="112"/>
+      <c r="O16" s="112"/>
     </row>
     <row r="17" spans="1:15" s="14" customFormat="1" ht="21" customHeight="1">
       <c r="A17" s="49">
@@ -5772,7 +5762,7 @@
         <v>6</v>
       </c>
       <c r="E17" s="50">
-        <f>M8*(I44+J44)*D17</f>
+        <f>N8*(I44+J44)*D17</f>
         <v>697800</v>
       </c>
       <c r="F17" s="16">
@@ -5788,7 +5778,7 @@
       </c>
       <c r="I17" s="20"/>
       <c r="J17" s="20"/>
-      <c r="K17" s="174" t="s">
+      <c r="K17" s="172" t="s">
         <v>245</v>
       </c>
       <c r="M17" s="20"/>
@@ -5810,7 +5800,7 @@
       <c r="H18" s="45"/>
       <c r="I18" s="20"/>
       <c r="J18" s="19"/>
-      <c r="K18" s="174"/>
+      <c r="K18" s="172"/>
       <c r="M18" s="20"/>
       <c r="N18" s="19"/>
       <c r="O18" s="19"/>
@@ -5841,10 +5831,10 @@
       <c r="A20" s="18">
         <v>4</v>
       </c>
-      <c r="B20" s="156" t="s">
+      <c r="B20" s="154" t="s">
         <v>82</v>
       </c>
-      <c r="C20" s="157"/>
+      <c r="C20" s="155"/>
       <c r="D20" s="18" t="s">
         <v>83</v>
       </c>
@@ -5870,7 +5860,7 @@
         <v>23</v>
       </c>
       <c r="D21" s="18">
-        <f>M8</f>
+        <f>N8</f>
         <v>2000</v>
       </c>
       <c r="E21" s="18"/>
@@ -5895,7 +5885,7 @@
         <v>28</v>
       </c>
       <c r="D22" s="18">
-        <f>M8</f>
+        <f>N8</f>
         <v>2000</v>
       </c>
       <c r="E22" s="18"/>
@@ -6001,91 +5991,91 @@
       <c r="N27" s="13"/>
       <c r="O27" s="13"/>
     </row>
-    <row r="28" spans="1:15" s="109" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A28" s="176" t="s">
+    <row r="28" spans="1:15" s="108" customFormat="1" ht="25.5" customHeight="1">
+      <c r="A28" s="174" t="s">
         <v>33</v>
       </c>
-      <c r="B28" s="177" t="s">
+      <c r="B28" s="175" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="176" t="s">
+      <c r="C28" s="174" t="s">
         <v>31</v>
       </c>
-      <c r="D28" s="176" t="s">
+      <c r="D28" s="174" t="s">
         <v>30</v>
       </c>
-      <c r="E28" s="106"/>
-      <c r="F28" s="167" t="s">
+      <c r="E28" s="105"/>
+      <c r="F28" s="165" t="s">
         <v>92</v>
       </c>
-      <c r="G28" s="138" t="s">
+      <c r="G28" s="136" t="s">
         <v>93</v>
       </c>
-      <c r="H28" s="138"/>
-      <c r="I28" s="138"/>
-      <c r="J28" s="172"/>
-      <c r="K28" s="138" t="s">
+      <c r="H28" s="136"/>
+      <c r="I28" s="136"/>
+      <c r="J28" s="170"/>
+      <c r="K28" s="136" t="s">
         <v>77</v>
       </c>
-      <c r="L28" s="138"/>
-      <c r="M28" s="138"/>
-      <c r="N28" s="138" t="s">
+      <c r="L28" s="136"/>
+      <c r="M28" s="136"/>
+      <c r="N28" s="136" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="29" spans="1:15" s="109" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A29" s="177"/>
-      <c r="B29" s="178"/>
-      <c r="C29" s="176"/>
-      <c r="D29" s="176"/>
-      <c r="E29" s="110"/>
-      <c r="F29" s="179"/>
-      <c r="G29" s="107" t="s">
+    <row r="29" spans="1:15" s="108" customFormat="1" ht="25.5" customHeight="1">
+      <c r="A29" s="175"/>
+      <c r="B29" s="176"/>
+      <c r="C29" s="174"/>
+      <c r="D29" s="174"/>
+      <c r="E29" s="109"/>
+      <c r="F29" s="177"/>
+      <c r="G29" s="106" t="s">
         <v>94</v>
       </c>
-      <c r="H29" s="107" t="s">
+      <c r="H29" s="106" t="s">
         <v>95</v>
       </c>
-      <c r="I29" s="107" t="s">
+      <c r="I29" s="106" t="s">
         <v>96</v>
       </c>
-      <c r="J29" s="108" t="s">
+      <c r="J29" s="107" t="s">
         <v>89</v>
       </c>
-      <c r="K29" s="105" t="s">
+      <c r="K29" s="104" t="s">
         <v>42</v>
       </c>
-      <c r="L29" s="107" t="s">
+      <c r="L29" s="106" t="s">
         <v>39</v>
       </c>
-      <c r="M29" s="107" t="s">
+      <c r="M29" s="106" t="s">
         <v>40</v>
       </c>
-      <c r="N29" s="138"/>
+      <c r="N29" s="136"/>
     </row>
     <row r="30" spans="1:15" s="14" customFormat="1" ht="21" customHeight="1">
-      <c r="A30" s="146">
+      <c r="A30" s="144">
         <v>1.3</v>
       </c>
-      <c r="B30" s="158" t="s">
+      <c r="B30" s="156" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="161" t="s">
+      <c r="C30" s="159" t="s">
         <v>59</v>
       </c>
-      <c r="D30" s="201">
+      <c r="D30" s="199">
         <v>6</v>
       </c>
       <c r="E30" s="16"/>
-      <c r="F30" s="201">
-        <f>M8*D30</f>
+      <c r="F30" s="199">
+        <f>N8*D30</f>
         <v>12000</v>
       </c>
       <c r="G30" s="73"/>
       <c r="H30" s="73"/>
       <c r="I30" s="73"/>
       <c r="J30" s="74"/>
-      <c r="K30" s="139" t="s">
+      <c r="K30" s="137" t="s">
         <v>80</v>
       </c>
       <c r="L30" s="16"/>
@@ -6093,113 +6083,113 @@
       <c r="N30" s="45"/>
     </row>
     <row r="31" spans="1:15" s="14" customFormat="1" ht="21" customHeight="1">
-      <c r="A31" s="147"/>
-      <c r="B31" s="159"/>
-      <c r="C31" s="162"/>
-      <c r="D31" s="170"/>
+      <c r="A31" s="145"/>
+      <c r="B31" s="157"/>
+      <c r="C31" s="160"/>
+      <c r="D31" s="168"/>
       <c r="E31" s="45"/>
-      <c r="F31" s="170"/>
+      <c r="F31" s="168"/>
       <c r="G31" s="73"/>
       <c r="H31" s="73"/>
       <c r="I31" s="73"/>
       <c r="J31" s="74"/>
-      <c r="K31" s="139"/>
+      <c r="K31" s="137"/>
       <c r="L31" s="18"/>
       <c r="M31" s="45"/>
       <c r="N31" s="45"/>
     </row>
     <row r="32" spans="1:15" s="14" customFormat="1" ht="21" customHeight="1">
-      <c r="A32" s="147"/>
-      <c r="B32" s="159"/>
-      <c r="C32" s="162"/>
-      <c r="D32" s="170"/>
+      <c r="A32" s="145"/>
+      <c r="B32" s="157"/>
+      <c r="C32" s="160"/>
+      <c r="D32" s="168"/>
       <c r="E32" s="18"/>
-      <c r="F32" s="170"/>
+      <c r="F32" s="168"/>
       <c r="G32" s="73"/>
       <c r="H32" s="73"/>
       <c r="I32" s="73"/>
       <c r="J32" s="74"/>
-      <c r="K32" s="139"/>
+      <c r="K32" s="137"/>
       <c r="L32" s="45"/>
       <c r="M32" s="45"/>
       <c r="N32" s="45"/>
     </row>
     <row r="33" spans="1:15" s="14" customFormat="1" ht="21" customHeight="1">
-      <c r="A33" s="147"/>
-      <c r="B33" s="159"/>
-      <c r="C33" s="162"/>
-      <c r="D33" s="170"/>
+      <c r="A33" s="145"/>
+      <c r="B33" s="157"/>
+      <c r="C33" s="160"/>
+      <c r="D33" s="168"/>
       <c r="E33" s="18"/>
-      <c r="F33" s="170"/>
+      <c r="F33" s="168"/>
       <c r="G33" s="73"/>
       <c r="H33" s="73"/>
       <c r="I33" s="73"/>
       <c r="J33" s="74"/>
-      <c r="K33" s="139"/>
+      <c r="K33" s="137"/>
       <c r="L33" s="45"/>
       <c r="M33" s="45"/>
       <c r="N33" s="45"/>
     </row>
     <row r="34" spans="1:15" s="14" customFormat="1" ht="21" customHeight="1">
-      <c r="A34" s="147"/>
-      <c r="B34" s="159"/>
-      <c r="C34" s="162"/>
-      <c r="D34" s="170"/>
+      <c r="A34" s="145"/>
+      <c r="B34" s="157"/>
+      <c r="C34" s="160"/>
+      <c r="D34" s="168"/>
       <c r="E34" s="18"/>
-      <c r="F34" s="170"/>
+      <c r="F34" s="168"/>
       <c r="G34" s="73"/>
       <c r="H34" s="73"/>
       <c r="I34" s="73"/>
       <c r="J34" s="74"/>
-      <c r="K34" s="139"/>
+      <c r="K34" s="137"/>
       <c r="L34" s="45"/>
       <c r="M34" s="45"/>
       <c r="N34" s="45"/>
     </row>
     <row r="35" spans="1:15" s="14" customFormat="1" ht="21" customHeight="1">
-      <c r="A35" s="147"/>
-      <c r="B35" s="159"/>
-      <c r="C35" s="162"/>
-      <c r="D35" s="170"/>
+      <c r="A35" s="145"/>
+      <c r="B35" s="157"/>
+      <c r="C35" s="160"/>
+      <c r="D35" s="168"/>
       <c r="E35" s="18"/>
-      <c r="F35" s="170"/>
+      <c r="F35" s="168"/>
       <c r="G35" s="73"/>
       <c r="H35" s="73"/>
       <c r="I35" s="73"/>
       <c r="J35" s="74"/>
-      <c r="K35" s="139"/>
+      <c r="K35" s="137"/>
       <c r="L35" s="45"/>
       <c r="M35" s="45"/>
       <c r="N35" s="45"/>
     </row>
     <row r="36" spans="1:15" s="14" customFormat="1" ht="21" customHeight="1">
-      <c r="A36" s="147"/>
-      <c r="B36" s="159"/>
-      <c r="C36" s="162"/>
-      <c r="D36" s="170"/>
+      <c r="A36" s="145"/>
+      <c r="B36" s="157"/>
+      <c r="C36" s="160"/>
+      <c r="D36" s="168"/>
       <c r="E36" s="18"/>
-      <c r="F36" s="170"/>
+      <c r="F36" s="168"/>
       <c r="G36" s="73"/>
       <c r="H36" s="73"/>
       <c r="I36" s="73"/>
       <c r="J36" s="74"/>
-      <c r="K36" s="139"/>
+      <c r="K36" s="137"/>
       <c r="L36" s="45"/>
       <c r="M36" s="45"/>
       <c r="N36" s="45"/>
     </row>
     <row r="37" spans="1:15" s="14" customFormat="1" ht="21" customHeight="1">
-      <c r="A37" s="148"/>
-      <c r="B37" s="160"/>
-      <c r="C37" s="163"/>
-      <c r="D37" s="171"/>
+      <c r="A37" s="146"/>
+      <c r="B37" s="158"/>
+      <c r="C37" s="161"/>
+      <c r="D37" s="169"/>
       <c r="E37" s="18"/>
-      <c r="F37" s="171"/>
+      <c r="F37" s="169"/>
       <c r="G37" s="73"/>
       <c r="H37" s="73"/>
       <c r="I37" s="73"/>
       <c r="J37" s="74"/>
-      <c r="K37" s="139"/>
+      <c r="K37" s="137"/>
       <c r="L37" s="45"/>
       <c r="M37" s="45"/>
       <c r="N37" s="45"/>
@@ -6242,74 +6232,74 @@
       <c r="O40" s="13"/>
     </row>
     <row r="41" spans="1:15" s="22" customFormat="1" ht="21" hidden="1" customHeight="1">
-      <c r="A41" s="188" t="s">
+      <c r="A41" s="186" t="s">
         <v>33</v>
       </c>
-      <c r="B41" s="188" t="s">
+      <c r="B41" s="186" t="s">
         <v>34</v>
       </c>
-      <c r="C41" s="188" t="s">
+      <c r="C41" s="186" t="s">
         <v>35</v>
       </c>
-      <c r="D41" s="191" t="s">
+      <c r="D41" s="189" t="s">
         <v>35</v>
       </c>
       <c r="E41" s="34"/>
-      <c r="F41" s="188" t="s">
+      <c r="F41" s="186" t="s">
         <v>36</v>
       </c>
-      <c r="G41" s="188" t="s">
+      <c r="G41" s="186" t="s">
         <v>31</v>
       </c>
-      <c r="H41" s="194" t="s">
+      <c r="H41" s="192" t="s">
         <v>46</v>
       </c>
-      <c r="I41" s="194" t="s">
+      <c r="I41" s="192" t="s">
         <v>41</v>
       </c>
-      <c r="J41" s="194" t="s">
+      <c r="J41" s="192" t="s">
         <v>42</v>
       </c>
-      <c r="K41" s="194" t="s">
+      <c r="K41" s="192" t="s">
         <v>70</v>
       </c>
-      <c r="L41" s="197" t="s">
+      <c r="L41" s="195" t="s">
         <v>37</v>
       </c>
-      <c r="M41" s="198"/>
-      <c r="N41" s="187" t="s">
+      <c r="M41" s="196"/>
+      <c r="N41" s="185" t="s">
         <v>38</v>
       </c>
-      <c r="O41" s="187"/>
+      <c r="O41" s="185"/>
     </row>
     <row r="42" spans="1:15" s="22" customFormat="1" ht="21" hidden="1" customHeight="1">
-      <c r="A42" s="189"/>
-      <c r="B42" s="189"/>
-      <c r="C42" s="189"/>
-      <c r="D42" s="192"/>
-      <c r="F42" s="189"/>
-      <c r="G42" s="189"/>
-      <c r="H42" s="195"/>
-      <c r="I42" s="195"/>
-      <c r="J42" s="195"/>
-      <c r="K42" s="195"/>
-      <c r="L42" s="199"/>
-      <c r="M42" s="200"/>
-      <c r="N42" s="187"/>
-      <c r="O42" s="187"/>
+      <c r="A42" s="187"/>
+      <c r="B42" s="187"/>
+      <c r="C42" s="187"/>
+      <c r="D42" s="190"/>
+      <c r="F42" s="187"/>
+      <c r="G42" s="187"/>
+      <c r="H42" s="193"/>
+      <c r="I42" s="193"/>
+      <c r="J42" s="193"/>
+      <c r="K42" s="193"/>
+      <c r="L42" s="197"/>
+      <c r="M42" s="198"/>
+      <c r="N42" s="185"/>
+      <c r="O42" s="185"/>
     </row>
     <row r="43" spans="1:15" s="22" customFormat="1" ht="21" hidden="1" customHeight="1">
-      <c r="A43" s="190"/>
-      <c r="B43" s="190"/>
-      <c r="C43" s="190"/>
-      <c r="D43" s="193"/>
+      <c r="A43" s="188"/>
+      <c r="B43" s="188"/>
+      <c r="C43" s="188"/>
+      <c r="D43" s="191"/>
       <c r="E43" s="36"/>
-      <c r="F43" s="190"/>
-      <c r="G43" s="190"/>
-      <c r="H43" s="196"/>
-      <c r="I43" s="196"/>
-      <c r="J43" s="196"/>
-      <c r="K43" s="196"/>
+      <c r="F43" s="188"/>
+      <c r="G43" s="188"/>
+      <c r="H43" s="194"/>
+      <c r="I43" s="194"/>
+      <c r="J43" s="194"/>
+      <c r="K43" s="194"/>
       <c r="L43" s="35" t="s">
         <v>39</v>
       </c>
@@ -6594,86 +6584,86 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="23.25" customHeight="1">
-      <c r="A1" s="173" t="s">
+      <c r="A1" s="171" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="173"/>
-      <c r="C1" s="173"/>
-      <c r="D1" s="173"/>
-      <c r="E1" s="173"/>
-      <c r="F1" s="173"/>
-      <c r="G1" s="173"/>
-      <c r="H1" s="173"/>
-      <c r="I1" s="173"/>
-      <c r="J1" s="173"/>
-      <c r="K1" s="173"/>
-      <c r="L1" s="173"/>
-      <c r="M1" s="173"/>
-      <c r="N1" s="173"/>
+      <c r="B1" s="171"/>
+      <c r="C1" s="171"/>
+      <c r="D1" s="171"/>
+      <c r="E1" s="171"/>
+      <c r="F1" s="171"/>
+      <c r="G1" s="171"/>
+      <c r="H1" s="171"/>
+      <c r="I1" s="171"/>
+      <c r="J1" s="171"/>
+      <c r="K1" s="171"/>
+      <c r="L1" s="171"/>
+      <c r="M1" s="171"/>
+      <c r="N1" s="171"/>
     </row>
     <row r="2" spans="1:15" ht="11.7" customHeight="1">
-      <c r="A2" s="173"/>
-      <c r="B2" s="173"/>
-      <c r="C2" s="173"/>
-      <c r="D2" s="173"/>
-      <c r="E2" s="173"/>
-      <c r="F2" s="173"/>
-      <c r="G2" s="173"/>
-      <c r="H2" s="173"/>
-      <c r="I2" s="173"/>
-      <c r="J2" s="173"/>
-      <c r="K2" s="173"/>
-      <c r="L2" s="173"/>
-      <c r="M2" s="173"/>
-      <c r="N2" s="173"/>
+      <c r="A2" s="171"/>
+      <c r="B2" s="171"/>
+      <c r="C2" s="171"/>
+      <c r="D2" s="171"/>
+      <c r="E2" s="171"/>
+      <c r="F2" s="171"/>
+      <c r="G2" s="171"/>
+      <c r="H2" s="171"/>
+      <c r="I2" s="171"/>
+      <c r="J2" s="171"/>
+      <c r="K2" s="171"/>
+      <c r="L2" s="171"/>
+      <c r="M2" s="171"/>
+      <c r="N2" s="171"/>
     </row>
     <row r="3" spans="1:15" ht="11.7" customHeight="1">
-      <c r="A3" s="173"/>
-      <c r="B3" s="173"/>
-      <c r="C3" s="173"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="173"/>
-      <c r="F3" s="173"/>
-      <c r="G3" s="173"/>
-      <c r="H3" s="173"/>
-      <c r="I3" s="173"/>
-      <c r="J3" s="173"/>
-      <c r="K3" s="173"/>
-      <c r="L3" s="173"/>
-      <c r="M3" s="173"/>
-      <c r="N3" s="173"/>
+      <c r="A3" s="171"/>
+      <c r="B3" s="171"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="171"/>
+      <c r="G3" s="171"/>
+      <c r="H3" s="171"/>
+      <c r="I3" s="171"/>
+      <c r="J3" s="171"/>
+      <c r="K3" s="171"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="171"/>
     </row>
     <row r="4" spans="1:15" ht="11.7" customHeight="1">
-      <c r="A4" s="173"/>
-      <c r="B4" s="173"/>
-      <c r="C4" s="173"/>
-      <c r="D4" s="173"/>
-      <c r="E4" s="173"/>
-      <c r="F4" s="173"/>
-      <c r="G4" s="173"/>
-      <c r="H4" s="173"/>
-      <c r="I4" s="173"/>
-      <c r="J4" s="173"/>
-      <c r="K4" s="173"/>
-      <c r="L4" s="173"/>
-      <c r="M4" s="173"/>
-      <c r="N4" s="173"/>
+      <c r="A4" s="171"/>
+      <c r="B4" s="171"/>
+      <c r="C4" s="171"/>
+      <c r="D4" s="171"/>
+      <c r="E4" s="171"/>
+      <c r="F4" s="171"/>
+      <c r="G4" s="171"/>
+      <c r="H4" s="171"/>
+      <c r="I4" s="171"/>
+      <c r="J4" s="171"/>
+      <c r="K4" s="171"/>
+      <c r="L4" s="171"/>
+      <c r="M4" s="171"/>
+      <c r="N4" s="171"/>
     </row>
     <row r="5" spans="1:15" ht="11.7" customHeight="1">
-      <c r="A5" s="173"/>
-      <c r="B5" s="173"/>
-      <c r="C5" s="173"/>
-      <c r="D5" s="173"/>
-      <c r="E5" s="173"/>
-      <c r="F5" s="173"/>
-      <c r="G5" s="173"/>
-      <c r="H5" s="173"/>
-      <c r="I5" s="173"/>
-      <c r="J5" s="173"/>
-      <c r="K5" s="173"/>
-      <c r="L5" s="173"/>
-      <c r="M5" s="173"/>
-      <c r="N5" s="173"/>
+      <c r="A5" s="171"/>
+      <c r="B5" s="171"/>
+      <c r="C5" s="171"/>
+      <c r="D5" s="171"/>
+      <c r="E5" s="171"/>
+      <c r="F5" s="171"/>
+      <c r="G5" s="171"/>
+      <c r="H5" s="171"/>
+      <c r="I5" s="171"/>
+      <c r="J5" s="171"/>
+      <c r="K5" s="171"/>
+      <c r="L5" s="171"/>
+      <c r="M5" s="171"/>
+      <c r="N5" s="171"/>
     </row>
     <row r="6" spans="1:15" ht="22.8">
       <c r="A6" s="11" t="s">
@@ -6688,29 +6678,30 @@
       <c r="A7" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="31"/>
+      <c r="B7" s="135">
+        <v>46242</v>
+      </c>
       <c r="C7" s="31"/>
       <c r="D7" s="13" t="s">
         <v>84</v>
       </c>
       <c r="E7" s="13"/>
-      <c r="F7" s="33">
+      <c r="F7" s="33" t="str">
         <f>'ใบงาน Agilent_JOB 1.1'!F7</f>
-        <v>0</v>
+        <v>xxx</v>
       </c>
       <c r="G7" s="31"/>
       <c r="J7" s="13"/>
       <c r="K7" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="L7" s="31" t="s">
+      <c r="M7" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="M7" s="31">
-        <f>'ใบงาน Agilent_JOB 1.1'!M7</f>
+      <c r="N7" s="31">
+        <f>'ใบงาน Agilent_JOB 1.1'!N7</f>
         <v>20260803</v>
       </c>
-      <c r="N7" s="33"/>
       <c r="O7" s="13"/>
     </row>
     <row r="8" spans="1:15" s="14" customFormat="1" ht="21" customHeight="1">
@@ -6724,19 +6715,16 @@
         <v>101</v>
       </c>
       <c r="E8" s="13"/>
-      <c r="F8" s="126" t="s">
+      <c r="F8" s="122" t="s">
         <v>5</v>
       </c>
       <c r="J8" s="13"/>
       <c r="K8" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="M8" s="121">
-        <f>'ใบงาน Agilent_JOB 1.1'!M8</f>
+      <c r="N8" s="117">
+        <f>'ใบงาน Agilent_JOB 1.1'!N8</f>
         <v>2000</v>
-      </c>
-      <c r="N8" s="118" t="s">
-        <v>16</v>
       </c>
       <c r="O8" s="13"/>
     </row>
@@ -6758,12 +6746,9 @@
       <c r="K9" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="M9" s="14" t="str">
-        <f>'ใบงาน Agilent_JOB 1.1'!M9</f>
+      <c r="N9" s="14" t="str">
+        <f>'ใบงาน Agilent_JOB 1.1'!N9</f>
         <v>PO12345</v>
-      </c>
-      <c r="N9" s="14" t="s">
-        <v>16</v>
       </c>
       <c r="O9" s="13"/>
     </row>
@@ -6800,7 +6785,7 @@
       <c r="B12" s="14" t="s">
         <v>244</v>
       </c>
-      <c r="C12" s="95" t="s">
+      <c r="C12" s="94" t="s">
         <v>16</v>
       </c>
       <c r="D12" s="13"/>
@@ -6837,55 +6822,55 @@
       <c r="N14" s="19"/>
       <c r="O14" s="19"/>
     </row>
-    <row r="15" spans="1:15" s="109" customFormat="1" ht="21" customHeight="1">
-      <c r="A15" s="176" t="s">
+    <row r="15" spans="1:15" s="108" customFormat="1" ht="21" customHeight="1">
+      <c r="A15" s="174" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="177" t="s">
+      <c r="B15" s="175" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="176" t="s">
+      <c r="C15" s="174" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="176" t="s">
+      <c r="D15" s="174" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="180" t="s">
+      <c r="E15" s="178" t="s">
         <v>50</v>
       </c>
-      <c r="F15" s="182" t="s">
+      <c r="F15" s="180" t="s">
         <v>51</v>
       </c>
-      <c r="G15" s="138" t="s">
+      <c r="G15" s="136" t="s">
         <v>50</v>
       </c>
-      <c r="H15" s="202" t="s">
+      <c r="H15" s="200" t="s">
         <v>49</v>
       </c>
-      <c r="I15" s="113"/>
-      <c r="J15" s="114"/>
-      <c r="K15" s="175"/>
-      <c r="L15" s="113"/>
-      <c r="M15" s="113"/>
-      <c r="N15" s="113"/>
-      <c r="O15" s="113"/>
-    </row>
-    <row r="16" spans="1:15" s="109" customFormat="1" ht="21" customHeight="1">
-      <c r="A16" s="176"/>
-      <c r="B16" s="178"/>
-      <c r="C16" s="176"/>
-      <c r="D16" s="176"/>
-      <c r="E16" s="181"/>
-      <c r="F16" s="183"/>
-      <c r="G16" s="167"/>
-      <c r="H16" s="203"/>
-      <c r="I16" s="113"/>
-      <c r="J16" s="114"/>
-      <c r="K16" s="175"/>
-      <c r="L16" s="113"/>
-      <c r="M16" s="113"/>
-      <c r="N16" s="113"/>
-      <c r="O16" s="113"/>
+      <c r="I15" s="112"/>
+      <c r="J15" s="113"/>
+      <c r="K15" s="173"/>
+      <c r="L15" s="112"/>
+      <c r="M15" s="112"/>
+      <c r="N15" s="112"/>
+      <c r="O15" s="112"/>
+    </row>
+    <row r="16" spans="1:15" s="108" customFormat="1" ht="21" customHeight="1">
+      <c r="A16" s="174"/>
+      <c r="B16" s="176"/>
+      <c r="C16" s="174"/>
+      <c r="D16" s="174"/>
+      <c r="E16" s="179"/>
+      <c r="F16" s="181"/>
+      <c r="G16" s="165"/>
+      <c r="H16" s="201"/>
+      <c r="I16" s="112"/>
+      <c r="J16" s="113"/>
+      <c r="K16" s="173"/>
+      <c r="L16" s="112"/>
+      <c r="M16" s="112"/>
+      <c r="N16" s="112"/>
+      <c r="O16" s="112"/>
     </row>
     <row r="17" spans="1:15" s="14" customFormat="1" ht="21" customHeight="1">
       <c r="A17" s="49">
@@ -6901,7 +6886,7 @@
         <v>6</v>
       </c>
       <c r="E17" s="50">
-        <f>D17*M8*(I44+J44)</f>
+        <f>D17*N8*(I44+J44)</f>
         <v>3717600</v>
       </c>
       <c r="F17" s="16">
@@ -6917,7 +6902,7 @@
       </c>
       <c r="I17" s="20"/>
       <c r="J17" s="20"/>
-      <c r="K17" s="174" t="s">
+      <c r="K17" s="172" t="s">
         <v>245</v>
       </c>
       <c r="M17" s="20"/>
@@ -6939,7 +6924,7 @@
       <c r="H18" s="45"/>
       <c r="I18" s="20"/>
       <c r="J18" s="19"/>
-      <c r="K18" s="174"/>
+      <c r="K18" s="172"/>
       <c r="M18" s="20"/>
       <c r="N18" s="19"/>
       <c r="O18" s="19"/>
@@ -6970,10 +6955,10 @@
       <c r="A20" s="18">
         <v>4</v>
       </c>
-      <c r="B20" s="156" t="s">
+      <c r="B20" s="154" t="s">
         <v>82</v>
       </c>
-      <c r="C20" s="157"/>
+      <c r="C20" s="155"/>
       <c r="D20" s="18" t="s">
         <v>83</v>
       </c>
@@ -6999,7 +6984,7 @@
         <v>24</v>
       </c>
       <c r="D21" s="18">
-        <f>M8</f>
+        <f>N8</f>
         <v>2000</v>
       </c>
       <c r="E21" s="18"/>
@@ -7024,7 +7009,7 @@
         <v>28</v>
       </c>
       <c r="D22" s="18">
-        <f>M8</f>
+        <f>N8</f>
         <v>2000</v>
       </c>
       <c r="E22" s="18"/>
@@ -7120,91 +7105,91 @@
       <c r="N27" s="13"/>
       <c r="O27" s="13"/>
     </row>
-    <row r="28" spans="1:15" s="109" customFormat="1" ht="21" customHeight="1">
-      <c r="A28" s="176" t="s">
+    <row r="28" spans="1:15" s="108" customFormat="1" ht="21" customHeight="1">
+      <c r="A28" s="174" t="s">
         <v>33</v>
       </c>
-      <c r="B28" s="177" t="s">
+      <c r="B28" s="175" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="176" t="s">
+      <c r="C28" s="174" t="s">
         <v>31</v>
       </c>
-      <c r="D28" s="176" t="s">
+      <c r="D28" s="174" t="s">
         <v>30</v>
       </c>
-      <c r="E28" s="106"/>
-      <c r="F28" s="167" t="s">
+      <c r="E28" s="105"/>
+      <c r="F28" s="165" t="s">
         <v>92</v>
       </c>
-      <c r="G28" s="138" t="s">
+      <c r="G28" s="136" t="s">
         <v>93</v>
       </c>
-      <c r="H28" s="138"/>
-      <c r="I28" s="138"/>
-      <c r="J28" s="172"/>
-      <c r="K28" s="138" t="s">
+      <c r="H28" s="136"/>
+      <c r="I28" s="136"/>
+      <c r="J28" s="170"/>
+      <c r="K28" s="136" t="s">
         <v>77</v>
       </c>
-      <c r="L28" s="138"/>
-      <c r="M28" s="138"/>
-      <c r="N28" s="138" t="s">
+      <c r="L28" s="136"/>
+      <c r="M28" s="136"/>
+      <c r="N28" s="136" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="29" spans="1:15" s="109" customFormat="1" ht="27" customHeight="1">
-      <c r="A29" s="176"/>
-      <c r="B29" s="178"/>
-      <c r="C29" s="176"/>
-      <c r="D29" s="176"/>
-      <c r="E29" s="110"/>
-      <c r="F29" s="179"/>
-      <c r="G29" s="107" t="s">
+    <row r="29" spans="1:15" s="108" customFormat="1" ht="27" customHeight="1">
+      <c r="A29" s="174"/>
+      <c r="B29" s="176"/>
+      <c r="C29" s="174"/>
+      <c r="D29" s="174"/>
+      <c r="E29" s="109"/>
+      <c r="F29" s="177"/>
+      <c r="G29" s="106" t="s">
         <v>94</v>
       </c>
-      <c r="H29" s="107" t="s">
+      <c r="H29" s="106" t="s">
         <v>95</v>
       </c>
-      <c r="I29" s="107" t="s">
+      <c r="I29" s="106" t="s">
         <v>96</v>
       </c>
-      <c r="J29" s="108" t="s">
+      <c r="J29" s="107" t="s">
         <v>89</v>
       </c>
-      <c r="K29" s="105" t="s">
+      <c r="K29" s="104" t="s">
         <v>42</v>
       </c>
-      <c r="L29" s="107" t="s">
+      <c r="L29" s="106" t="s">
         <v>39</v>
       </c>
-      <c r="M29" s="107" t="s">
+      <c r="M29" s="106" t="s">
         <v>40</v>
       </c>
-      <c r="N29" s="138"/>
+      <c r="N29" s="136"/>
     </row>
     <row r="30" spans="1:15" s="14" customFormat="1" ht="21" customHeight="1">
-      <c r="A30" s="146">
+      <c r="A30" s="144">
         <v>1.4</v>
       </c>
-      <c r="B30" s="158" t="s">
+      <c r="B30" s="156" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="161" t="s">
+      <c r="C30" s="159" t="s">
         <v>60</v>
       </c>
-      <c r="D30" s="201">
+      <c r="D30" s="199">
         <v>6</v>
       </c>
       <c r="E30" s="16"/>
-      <c r="F30" s="201">
-        <f>M8*D30</f>
+      <c r="F30" s="199">
+        <f>N8*D30</f>
         <v>12000</v>
       </c>
       <c r="G30" s="73"/>
       <c r="H30" s="73"/>
       <c r="I30" s="73"/>
       <c r="J30" s="74"/>
-      <c r="K30" s="139" t="s">
+      <c r="K30" s="137" t="s">
         <v>97</v>
       </c>
       <c r="L30" s="16"/>
@@ -7212,113 +7197,113 @@
       <c r="N30" s="45"/>
     </row>
     <row r="31" spans="1:15" s="14" customFormat="1" ht="21" customHeight="1">
-      <c r="A31" s="147"/>
-      <c r="B31" s="159"/>
-      <c r="C31" s="162"/>
-      <c r="D31" s="170"/>
+      <c r="A31" s="145"/>
+      <c r="B31" s="157"/>
+      <c r="C31" s="160"/>
+      <c r="D31" s="168"/>
       <c r="E31" s="45"/>
-      <c r="F31" s="170"/>
+      <c r="F31" s="168"/>
       <c r="G31" s="73"/>
       <c r="H31" s="73"/>
       <c r="I31" s="73"/>
       <c r="J31" s="74"/>
-      <c r="K31" s="139"/>
+      <c r="K31" s="137"/>
       <c r="L31" s="18"/>
       <c r="M31" s="45"/>
       <c r="N31" s="45"/>
     </row>
     <row r="32" spans="1:15" s="14" customFormat="1" ht="21" customHeight="1">
-      <c r="A32" s="147"/>
-      <c r="B32" s="159"/>
-      <c r="C32" s="162"/>
-      <c r="D32" s="170"/>
+      <c r="A32" s="145"/>
+      <c r="B32" s="157"/>
+      <c r="C32" s="160"/>
+      <c r="D32" s="168"/>
       <c r="E32" s="18"/>
-      <c r="F32" s="170"/>
+      <c r="F32" s="168"/>
       <c r="G32" s="73"/>
       <c r="H32" s="73"/>
       <c r="I32" s="73"/>
       <c r="J32" s="74"/>
-      <c r="K32" s="139"/>
+      <c r="K32" s="137"/>
       <c r="L32" s="45"/>
       <c r="M32" s="45"/>
       <c r="N32" s="45"/>
     </row>
     <row r="33" spans="1:15" s="14" customFormat="1" ht="21" customHeight="1">
-      <c r="A33" s="147"/>
-      <c r="B33" s="159"/>
-      <c r="C33" s="162"/>
-      <c r="D33" s="170"/>
+      <c r="A33" s="145"/>
+      <c r="B33" s="157"/>
+      <c r="C33" s="160"/>
+      <c r="D33" s="168"/>
       <c r="E33" s="18"/>
-      <c r="F33" s="170"/>
+      <c r="F33" s="168"/>
       <c r="G33" s="73"/>
       <c r="H33" s="73"/>
       <c r="I33" s="73"/>
       <c r="J33" s="74"/>
-      <c r="K33" s="139"/>
+      <c r="K33" s="137"/>
       <c r="L33" s="45"/>
       <c r="M33" s="45"/>
       <c r="N33" s="45"/>
     </row>
     <row r="34" spans="1:15" s="14" customFormat="1" ht="21" customHeight="1">
-      <c r="A34" s="147"/>
-      <c r="B34" s="159"/>
-      <c r="C34" s="162"/>
-      <c r="D34" s="170"/>
+      <c r="A34" s="145"/>
+      <c r="B34" s="157"/>
+      <c r="C34" s="160"/>
+      <c r="D34" s="168"/>
       <c r="E34" s="18"/>
-      <c r="F34" s="170"/>
+      <c r="F34" s="168"/>
       <c r="G34" s="73"/>
       <c r="H34" s="73"/>
       <c r="I34" s="73"/>
       <c r="J34" s="74"/>
-      <c r="K34" s="139"/>
+      <c r="K34" s="137"/>
       <c r="L34" s="45"/>
       <c r="M34" s="45"/>
       <c r="N34" s="45"/>
     </row>
     <row r="35" spans="1:15" s="14" customFormat="1" ht="21" customHeight="1">
-      <c r="A35" s="147"/>
-      <c r="B35" s="159"/>
-      <c r="C35" s="162"/>
-      <c r="D35" s="170"/>
+      <c r="A35" s="145"/>
+      <c r="B35" s="157"/>
+      <c r="C35" s="160"/>
+      <c r="D35" s="168"/>
       <c r="E35" s="18"/>
-      <c r="F35" s="170"/>
+      <c r="F35" s="168"/>
       <c r="G35" s="73"/>
       <c r="H35" s="73"/>
       <c r="I35" s="73"/>
       <c r="J35" s="74"/>
-      <c r="K35" s="139"/>
+      <c r="K35" s="137"/>
       <c r="L35" s="45"/>
       <c r="M35" s="45"/>
       <c r="N35" s="45"/>
     </row>
     <row r="36" spans="1:15" s="14" customFormat="1" ht="21" customHeight="1">
-      <c r="A36" s="147"/>
-      <c r="B36" s="159"/>
-      <c r="C36" s="162"/>
-      <c r="D36" s="170"/>
+      <c r="A36" s="145"/>
+      <c r="B36" s="157"/>
+      <c r="C36" s="160"/>
+      <c r="D36" s="168"/>
       <c r="E36" s="18"/>
-      <c r="F36" s="170"/>
+      <c r="F36" s="168"/>
       <c r="G36" s="73"/>
       <c r="H36" s="73"/>
       <c r="I36" s="73"/>
       <c r="J36" s="74"/>
-      <c r="K36" s="139"/>
+      <c r="K36" s="137"/>
       <c r="L36" s="45"/>
       <c r="M36" s="45"/>
       <c r="N36" s="45"/>
     </row>
     <row r="37" spans="1:15" s="14" customFormat="1" ht="21" customHeight="1">
-      <c r="A37" s="148"/>
-      <c r="B37" s="160"/>
-      <c r="C37" s="163"/>
-      <c r="D37" s="171"/>
+      <c r="A37" s="146"/>
+      <c r="B37" s="158"/>
+      <c r="C37" s="161"/>
+      <c r="D37" s="169"/>
       <c r="E37" s="18"/>
-      <c r="F37" s="171"/>
+      <c r="F37" s="169"/>
       <c r="G37" s="73"/>
       <c r="H37" s="73"/>
       <c r="I37" s="73"/>
       <c r="J37" s="74"/>
-      <c r="K37" s="139"/>
+      <c r="K37" s="137"/>
       <c r="L37" s="45"/>
       <c r="M37" s="45"/>
       <c r="N37" s="45"/>
@@ -7357,74 +7342,74 @@
       <c r="O40" s="13"/>
     </row>
     <row r="41" spans="1:15" s="22" customFormat="1" ht="21" hidden="1" customHeight="1">
-      <c r="A41" s="188" t="s">
+      <c r="A41" s="186" t="s">
         <v>33</v>
       </c>
-      <c r="B41" s="188" t="s">
+      <c r="B41" s="186" t="s">
         <v>34</v>
       </c>
-      <c r="C41" s="188" t="s">
+      <c r="C41" s="186" t="s">
         <v>35</v>
       </c>
-      <c r="D41" s="191" t="s">
+      <c r="D41" s="189" t="s">
         <v>35</v>
       </c>
       <c r="E41" s="34"/>
-      <c r="F41" s="188" t="s">
+      <c r="F41" s="186" t="s">
         <v>36</v>
       </c>
-      <c r="G41" s="188" t="s">
+      <c r="G41" s="186" t="s">
         <v>31</v>
       </c>
-      <c r="H41" s="194" t="s">
+      <c r="H41" s="192" t="s">
         <v>46</v>
       </c>
-      <c r="I41" s="194" t="s">
+      <c r="I41" s="192" t="s">
         <v>41</v>
       </c>
-      <c r="J41" s="194" t="s">
+      <c r="J41" s="192" t="s">
         <v>42</v>
       </c>
-      <c r="K41" s="194" t="s">
+      <c r="K41" s="192" t="s">
         <v>70</v>
       </c>
-      <c r="L41" s="197" t="s">
+      <c r="L41" s="195" t="s">
         <v>37</v>
       </c>
-      <c r="M41" s="198"/>
-      <c r="N41" s="187" t="s">
+      <c r="M41" s="196"/>
+      <c r="N41" s="185" t="s">
         <v>38</v>
       </c>
-      <c r="O41" s="187"/>
+      <c r="O41" s="185"/>
     </row>
     <row r="42" spans="1:15" s="22" customFormat="1" ht="21" hidden="1" customHeight="1">
-      <c r="A42" s="189"/>
-      <c r="B42" s="189"/>
-      <c r="C42" s="189"/>
-      <c r="D42" s="192"/>
-      <c r="F42" s="189"/>
-      <c r="G42" s="189"/>
-      <c r="H42" s="195"/>
-      <c r="I42" s="195"/>
-      <c r="J42" s="195"/>
-      <c r="K42" s="195"/>
-      <c r="L42" s="199"/>
-      <c r="M42" s="200"/>
-      <c r="N42" s="187"/>
-      <c r="O42" s="187"/>
+      <c r="A42" s="187"/>
+      <c r="B42" s="187"/>
+      <c r="C42" s="187"/>
+      <c r="D42" s="190"/>
+      <c r="F42" s="187"/>
+      <c r="G42" s="187"/>
+      <c r="H42" s="193"/>
+      <c r="I42" s="193"/>
+      <c r="J42" s="193"/>
+      <c r="K42" s="193"/>
+      <c r="L42" s="197"/>
+      <c r="M42" s="198"/>
+      <c r="N42" s="185"/>
+      <c r="O42" s="185"/>
     </row>
     <row r="43" spans="1:15" s="22" customFormat="1" ht="21" hidden="1" customHeight="1">
-      <c r="A43" s="190"/>
-      <c r="B43" s="190"/>
-      <c r="C43" s="190"/>
-      <c r="D43" s="193"/>
+      <c r="A43" s="188"/>
+      <c r="B43" s="188"/>
+      <c r="C43" s="188"/>
+      <c r="D43" s="191"/>
       <c r="E43" s="36"/>
-      <c r="F43" s="190"/>
-      <c r="G43" s="190"/>
-      <c r="H43" s="196"/>
-      <c r="I43" s="196"/>
-      <c r="J43" s="196"/>
-      <c r="K43" s="196"/>
+      <c r="F43" s="188"/>
+      <c r="G43" s="188"/>
+      <c r="H43" s="194"/>
+      <c r="I43" s="194"/>
+      <c r="J43" s="194"/>
+      <c r="K43" s="194"/>
       <c r="L43" s="35" t="s">
         <v>39</v>
       </c>
@@ -7722,86 +7707,86 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="23.25" customHeight="1">
-      <c r="A1" s="173" t="s">
+      <c r="A1" s="171" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="173"/>
-      <c r="C1" s="173"/>
-      <c r="D1" s="173"/>
-      <c r="E1" s="173"/>
-      <c r="F1" s="173"/>
-      <c r="G1" s="173"/>
-      <c r="H1" s="173"/>
-      <c r="I1" s="173"/>
-      <c r="J1" s="173"/>
-      <c r="K1" s="173"/>
-      <c r="L1" s="173"/>
-      <c r="M1" s="173"/>
-      <c r="N1" s="173"/>
+      <c r="B1" s="171"/>
+      <c r="C1" s="171"/>
+      <c r="D1" s="171"/>
+      <c r="E1" s="171"/>
+      <c r="F1" s="171"/>
+      <c r="G1" s="171"/>
+      <c r="H1" s="171"/>
+      <c r="I1" s="171"/>
+      <c r="J1" s="171"/>
+      <c r="K1" s="171"/>
+      <c r="L1" s="171"/>
+      <c r="M1" s="171"/>
+      <c r="N1" s="171"/>
     </row>
     <row r="2" spans="1:15" ht="11.7" customHeight="1">
-      <c r="A2" s="173"/>
-      <c r="B2" s="173"/>
-      <c r="C2" s="173"/>
-      <c r="D2" s="173"/>
-      <c r="E2" s="173"/>
-      <c r="F2" s="173"/>
-      <c r="G2" s="173"/>
-      <c r="H2" s="173"/>
-      <c r="I2" s="173"/>
-      <c r="J2" s="173"/>
-      <c r="K2" s="173"/>
-      <c r="L2" s="173"/>
-      <c r="M2" s="173"/>
-      <c r="N2" s="173"/>
+      <c r="A2" s="171"/>
+      <c r="B2" s="171"/>
+      <c r="C2" s="171"/>
+      <c r="D2" s="171"/>
+      <c r="E2" s="171"/>
+      <c r="F2" s="171"/>
+      <c r="G2" s="171"/>
+      <c r="H2" s="171"/>
+      <c r="I2" s="171"/>
+      <c r="J2" s="171"/>
+      <c r="K2" s="171"/>
+      <c r="L2" s="171"/>
+      <c r="M2" s="171"/>
+      <c r="N2" s="171"/>
     </row>
     <row r="3" spans="1:15" ht="11.7" customHeight="1">
-      <c r="A3" s="173"/>
-      <c r="B3" s="173"/>
-      <c r="C3" s="173"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="173"/>
-      <c r="F3" s="173"/>
-      <c r="G3" s="173"/>
-      <c r="H3" s="173"/>
-      <c r="I3" s="173"/>
-      <c r="J3" s="173"/>
-      <c r="K3" s="173"/>
-      <c r="L3" s="173"/>
-      <c r="M3" s="173"/>
-      <c r="N3" s="173"/>
+      <c r="A3" s="171"/>
+      <c r="B3" s="171"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="171"/>
+      <c r="G3" s="171"/>
+      <c r="H3" s="171"/>
+      <c r="I3" s="171"/>
+      <c r="J3" s="171"/>
+      <c r="K3" s="171"/>
+      <c r="L3" s="171"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="171"/>
     </row>
     <row r="4" spans="1:15" ht="11.7" customHeight="1">
-      <c r="A4" s="173"/>
-      <c r="B4" s="173"/>
-      <c r="C4" s="173"/>
-      <c r="D4" s="173"/>
-      <c r="E4" s="173"/>
-      <c r="F4" s="173"/>
-      <c r="G4" s="173"/>
-      <c r="H4" s="173"/>
-      <c r="I4" s="173"/>
-      <c r="J4" s="173"/>
-      <c r="K4" s="173"/>
-      <c r="L4" s="173"/>
-      <c r="M4" s="173"/>
-      <c r="N4" s="173"/>
+      <c r="A4" s="171"/>
+      <c r="B4" s="171"/>
+      <c r="C4" s="171"/>
+      <c r="D4" s="171"/>
+      <c r="E4" s="171"/>
+      <c r="F4" s="171"/>
+      <c r="G4" s="171"/>
+      <c r="H4" s="171"/>
+      <c r="I4" s="171"/>
+      <c r="J4" s="171"/>
+      <c r="K4" s="171"/>
+      <c r="L4" s="171"/>
+      <c r="M4" s="171"/>
+      <c r="N4" s="171"/>
     </row>
     <row r="5" spans="1:15" ht="11.7" customHeight="1">
-      <c r="A5" s="173"/>
-      <c r="B5" s="173"/>
-      <c r="C5" s="173"/>
-      <c r="D5" s="173"/>
-      <c r="E5" s="173"/>
-      <c r="F5" s="173"/>
-      <c r="G5" s="173"/>
-      <c r="H5" s="173"/>
-      <c r="I5" s="173"/>
-      <c r="J5" s="173"/>
-      <c r="K5" s="173"/>
-      <c r="L5" s="173"/>
-      <c r="M5" s="173"/>
-      <c r="N5" s="173"/>
+      <c r="A5" s="171"/>
+      <c r="B5" s="171"/>
+      <c r="C5" s="171"/>
+      <c r="D5" s="171"/>
+      <c r="E5" s="171"/>
+      <c r="F5" s="171"/>
+      <c r="G5" s="171"/>
+      <c r="H5" s="171"/>
+      <c r="I5" s="171"/>
+      <c r="J5" s="171"/>
+      <c r="K5" s="171"/>
+      <c r="L5" s="171"/>
+      <c r="M5" s="171"/>
+      <c r="N5" s="171"/>
     </row>
     <row r="6" spans="1:15" ht="22.8">
       <c r="A6" s="11" t="s">
@@ -7816,29 +7801,30 @@
       <c r="A7" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="31"/>
+      <c r="B7" s="135">
+        <v>46242</v>
+      </c>
       <c r="C7" s="31"/>
       <c r="D7" s="13" t="s">
         <v>84</v>
       </c>
       <c r="E7" s="13"/>
-      <c r="F7" s="33">
+      <c r="F7" s="33" t="str">
         <f>'ใบงาน Agilent_JOB 1.1'!F7</f>
-        <v>0</v>
+        <v>xxx</v>
       </c>
       <c r="G7" s="31"/>
       <c r="J7" s="13"/>
       <c r="K7" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="L7" s="31" t="s">
+      <c r="M7" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="M7" s="31">
-        <f>'ใบงาน Agilent_JOB 1.1'!M7</f>
+      <c r="N7" s="31">
+        <f>'ใบงาน Agilent_JOB 1.1'!N7</f>
         <v>20260803</v>
       </c>
-      <c r="N7" s="33"/>
       <c r="O7" s="13"/>
     </row>
     <row r="8" spans="1:15" s="14" customFormat="1" ht="21" customHeight="1">
@@ -7852,18 +7838,17 @@
         <v>101</v>
       </c>
       <c r="E8" s="13"/>
-      <c r="F8" s="104" t="s">
+      <c r="F8" s="103" t="s">
         <v>5</v>
       </c>
       <c r="J8" s="13"/>
       <c r="K8" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="M8" s="120">
-        <f>'ใบงาน Agilent_JOB 1.1'!M8</f>
+      <c r="N8" s="116">
+        <f>'ใบงาน Agilent_JOB 1.1'!N8</f>
         <v>2000</v>
       </c>
-      <c r="N8" s="115"/>
       <c r="O8" s="13"/>
     </row>
     <row r="9" spans="1:15" s="14" customFormat="1" ht="21" customHeight="1">
@@ -7884,8 +7869,8 @@
       <c r="K9" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="M9" s="14" t="str">
-        <f>'ใบงาน Agilent_JOB 1.1'!M9</f>
+      <c r="N9" s="14" t="str">
+        <f>'ใบงาน Agilent_JOB 1.1'!N9</f>
         <v>PO12345</v>
       </c>
       <c r="O9" s="13"/>
@@ -7923,7 +7908,7 @@
       <c r="B12" s="14" t="s">
         <v>244</v>
       </c>
-      <c r="C12" s="95"/>
+      <c r="C12" s="94"/>
       <c r="D12" s="13"/>
       <c r="E12" s="13"/>
       <c r="F12" s="13"/>
@@ -7959,50 +7944,50 @@
       <c r="O14" s="19"/>
     </row>
     <row r="15" spans="1:15" s="14" customFormat="1" ht="21" customHeight="1">
-      <c r="A15" s="206" t="s">
+      <c r="A15" s="204" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="207" t="s">
+      <c r="B15" s="205" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="206" t="s">
+      <c r="C15" s="204" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="206" t="s">
+      <c r="D15" s="204" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="215" t="s">
+      <c r="E15" s="213" t="s">
         <v>50</v>
       </c>
-      <c r="F15" s="209" t="s">
+      <c r="F15" s="207" t="s">
         <v>51</v>
       </c>
-      <c r="G15" s="211" t="s">
+      <c r="G15" s="209" t="s">
         <v>50</v>
       </c>
-      <c r="H15" s="212" t="s">
+      <c r="H15" s="210" t="s">
         <v>49</v>
       </c>
       <c r="I15" s="43"/>
       <c r="J15" s="44"/>
-      <c r="K15" s="214"/>
+      <c r="K15" s="212"/>
       <c r="L15" s="20"/>
       <c r="M15" s="20"/>
       <c r="N15" s="20"/>
       <c r="O15" s="20"/>
     </row>
     <row r="16" spans="1:15" s="14" customFormat="1" ht="21" customHeight="1">
-      <c r="A16" s="206"/>
-      <c r="B16" s="208"/>
-      <c r="C16" s="206"/>
-      <c r="D16" s="206"/>
-      <c r="E16" s="216"/>
-      <c r="F16" s="210"/>
-      <c r="G16" s="212"/>
-      <c r="H16" s="213"/>
+      <c r="A16" s="204"/>
+      <c r="B16" s="206"/>
+      <c r="C16" s="204"/>
+      <c r="D16" s="204"/>
+      <c r="E16" s="214"/>
+      <c r="F16" s="208"/>
+      <c r="G16" s="210"/>
+      <c r="H16" s="211"/>
       <c r="I16" s="43"/>
       <c r="J16" s="44"/>
-      <c r="K16" s="214"/>
+      <c r="K16" s="212"/>
       <c r="L16" s="20"/>
       <c r="M16" s="20"/>
       <c r="N16" s="20"/>
@@ -8022,7 +8007,7 @@
         <v>6</v>
       </c>
       <c r="E17" s="50">
-        <f>D17*(I44+J44)*M8</f>
+        <f>D17*(I44+J44)*N8</f>
         <v>9204000</v>
       </c>
       <c r="F17" s="16">
@@ -8038,7 +8023,7 @@
       </c>
       <c r="I17" s="20"/>
       <c r="J17" s="20"/>
-      <c r="K17" s="174" t="s">
+      <c r="K17" s="172" t="s">
         <v>245</v>
       </c>
       <c r="M17" s="20"/>
@@ -8060,7 +8045,7 @@
       <c r="H18" s="45"/>
       <c r="I18" s="20"/>
       <c r="J18" s="19"/>
-      <c r="K18" s="174"/>
+      <c r="K18" s="172"/>
       <c r="M18" s="20"/>
       <c r="N18" s="19"/>
       <c r="O18" s="19"/>
@@ -8091,10 +8076,10 @@
       <c r="A20" s="18">
         <v>4</v>
       </c>
-      <c r="B20" s="156" t="s">
+      <c r="B20" s="154" t="s">
         <v>82</v>
       </c>
-      <c r="C20" s="157"/>
+      <c r="C20" s="155"/>
       <c r="D20" s="18" t="s">
         <v>83</v>
       </c>
@@ -8120,7 +8105,7 @@
         <v>24</v>
       </c>
       <c r="D21" s="18">
-        <f>M8</f>
+        <f>N8</f>
         <v>2000</v>
       </c>
       <c r="E21" s="18"/>
@@ -8145,7 +8130,7 @@
         <v>28</v>
       </c>
       <c r="D22" s="18">
-        <f>M8</f>
+        <f>N8</f>
         <v>2000</v>
       </c>
       <c r="E22" s="18"/>
@@ -8257,91 +8242,91 @@
       <c r="N27" s="13"/>
       <c r="O27" s="13"/>
     </row>
-    <row r="28" spans="1:15" s="109" customFormat="1" ht="25.95" customHeight="1">
-      <c r="A28" s="176" t="s">
+    <row r="28" spans="1:15" s="108" customFormat="1" ht="25.95" customHeight="1">
+      <c r="A28" s="174" t="s">
         <v>33</v>
       </c>
-      <c r="B28" s="177" t="s">
+      <c r="B28" s="175" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="176" t="s">
+      <c r="C28" s="174" t="s">
         <v>31</v>
       </c>
-      <c r="D28" s="176" t="s">
+      <c r="D28" s="174" t="s">
         <v>30</v>
       </c>
-      <c r="E28" s="106"/>
-      <c r="F28" s="204" t="s">
+      <c r="E28" s="105"/>
+      <c r="F28" s="202" t="s">
         <v>92</v>
       </c>
-      <c r="G28" s="138" t="s">
+      <c r="G28" s="136" t="s">
         <v>93</v>
       </c>
-      <c r="H28" s="138"/>
-      <c r="I28" s="138"/>
-      <c r="J28" s="172"/>
-      <c r="K28" s="138" t="s">
+      <c r="H28" s="136"/>
+      <c r="I28" s="136"/>
+      <c r="J28" s="170"/>
+      <c r="K28" s="136" t="s">
         <v>77</v>
       </c>
-      <c r="L28" s="138"/>
-      <c r="M28" s="138"/>
-      <c r="N28" s="138" t="s">
+      <c r="L28" s="136"/>
+      <c r="M28" s="136"/>
+      <c r="N28" s="136" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="29" spans="1:15" s="109" customFormat="1" ht="25.95" customHeight="1">
-      <c r="A29" s="176"/>
-      <c r="B29" s="178"/>
-      <c r="C29" s="176"/>
-      <c r="D29" s="176"/>
-      <c r="E29" s="110"/>
-      <c r="F29" s="205"/>
-      <c r="G29" s="107" t="s">
+    <row r="29" spans="1:15" s="108" customFormat="1" ht="25.95" customHeight="1">
+      <c r="A29" s="174"/>
+      <c r="B29" s="176"/>
+      <c r="C29" s="174"/>
+      <c r="D29" s="174"/>
+      <c r="E29" s="109"/>
+      <c r="F29" s="203"/>
+      <c r="G29" s="106" t="s">
         <v>94</v>
       </c>
-      <c r="H29" s="107" t="s">
+      <c r="H29" s="106" t="s">
         <v>95</v>
       </c>
-      <c r="I29" s="107" t="s">
+      <c r="I29" s="106" t="s">
         <v>96</v>
       </c>
-      <c r="J29" s="108" t="s">
+      <c r="J29" s="107" t="s">
         <v>89</v>
       </c>
-      <c r="K29" s="107" t="s">
+      <c r="K29" s="106" t="s">
         <v>42</v>
       </c>
-      <c r="L29" s="107" t="s">
+      <c r="L29" s="106" t="s">
         <v>39</v>
       </c>
-      <c r="M29" s="107" t="s">
+      <c r="M29" s="106" t="s">
         <v>40</v>
       </c>
-      <c r="N29" s="138"/>
+      <c r="N29" s="136"/>
     </row>
     <row r="30" spans="1:15" s="14" customFormat="1" ht="21" customHeight="1">
-      <c r="A30" s="146">
+      <c r="A30" s="144">
         <v>1.5</v>
       </c>
-      <c r="B30" s="158" t="s">
+      <c r="B30" s="156" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="161" t="s">
+      <c r="C30" s="159" t="s">
         <v>61</v>
       </c>
-      <c r="D30" s="201">
+      <c r="D30" s="199">
         <v>6</v>
       </c>
       <c r="E30" s="16"/>
-      <c r="F30" s="201">
-        <f>M8*D30</f>
+      <c r="F30" s="199">
+        <f>N8*D30</f>
         <v>12000</v>
       </c>
       <c r="G30" s="73"/>
       <c r="H30" s="73"/>
       <c r="I30" s="73"/>
       <c r="J30" s="74"/>
-      <c r="K30" s="139" t="s">
+      <c r="K30" s="137" t="s">
         <v>81</v>
       </c>
       <c r="L30" s="16"/>
@@ -8349,113 +8334,113 @@
       <c r="N30" s="45"/>
     </row>
     <row r="31" spans="1:15" s="14" customFormat="1" ht="21" customHeight="1">
-      <c r="A31" s="147"/>
-      <c r="B31" s="159"/>
-      <c r="C31" s="162"/>
-      <c r="D31" s="170"/>
+      <c r="A31" s="145"/>
+      <c r="B31" s="157"/>
+      <c r="C31" s="160"/>
+      <c r="D31" s="168"/>
       <c r="E31" s="45"/>
-      <c r="F31" s="170"/>
+      <c r="F31" s="168"/>
       <c r="G31" s="73"/>
       <c r="H31" s="73"/>
       <c r="I31" s="73"/>
       <c r="J31" s="74"/>
-      <c r="K31" s="139"/>
+      <c r="K31" s="137"/>
       <c r="L31" s="18"/>
       <c r="M31" s="45"/>
       <c r="N31" s="45"/>
     </row>
     <row r="32" spans="1:15" s="14" customFormat="1" ht="21" customHeight="1">
-      <c r="A32" s="147"/>
-      <c r="B32" s="159"/>
-      <c r="C32" s="162"/>
-      <c r="D32" s="170"/>
+      <c r="A32" s="145"/>
+      <c r="B32" s="157"/>
+      <c r="C32" s="160"/>
+      <c r="D32" s="168"/>
       <c r="E32" s="18"/>
-      <c r="F32" s="170"/>
+      <c r="F32" s="168"/>
       <c r="G32" s="73"/>
       <c r="H32" s="73"/>
       <c r="I32" s="73"/>
       <c r="J32" s="74"/>
-      <c r="K32" s="139"/>
+      <c r="K32" s="137"/>
       <c r="L32" s="45"/>
       <c r="M32" s="45"/>
       <c r="N32" s="45"/>
     </row>
     <row r="33" spans="1:15" s="14" customFormat="1" ht="21" customHeight="1">
-      <c r="A33" s="147"/>
-      <c r="B33" s="159"/>
-      <c r="C33" s="162"/>
-      <c r="D33" s="170"/>
+      <c r="A33" s="145"/>
+      <c r="B33" s="157"/>
+      <c r="C33" s="160"/>
+      <c r="D33" s="168"/>
       <c r="E33" s="18"/>
-      <c r="F33" s="170"/>
+      <c r="F33" s="168"/>
       <c r="G33" s="73"/>
       <c r="H33" s="73"/>
       <c r="I33" s="73"/>
       <c r="J33" s="74"/>
-      <c r="K33" s="139"/>
+      <c r="K33" s="137"/>
       <c r="L33" s="45"/>
       <c r="M33" s="45"/>
       <c r="N33" s="45"/>
     </row>
     <row r="34" spans="1:15" s="14" customFormat="1" ht="21" customHeight="1">
-      <c r="A34" s="147"/>
-      <c r="B34" s="159"/>
-      <c r="C34" s="162"/>
-      <c r="D34" s="170"/>
+      <c r="A34" s="145"/>
+      <c r="B34" s="157"/>
+      <c r="C34" s="160"/>
+      <c r="D34" s="168"/>
       <c r="E34" s="18"/>
-      <c r="F34" s="170"/>
+      <c r="F34" s="168"/>
       <c r="G34" s="73"/>
       <c r="H34" s="73"/>
       <c r="I34" s="73"/>
       <c r="J34" s="74"/>
-      <c r="K34" s="139"/>
+      <c r="K34" s="137"/>
       <c r="L34" s="45"/>
       <c r="M34" s="45"/>
       <c r="N34" s="45"/>
     </row>
     <row r="35" spans="1:15" s="14" customFormat="1" ht="21" customHeight="1">
-      <c r="A35" s="147"/>
-      <c r="B35" s="159"/>
-      <c r="C35" s="162"/>
-      <c r="D35" s="170"/>
+      <c r="A35" s="145"/>
+      <c r="B35" s="157"/>
+      <c r="C35" s="160"/>
+      <c r="D35" s="168"/>
       <c r="E35" s="18"/>
-      <c r="F35" s="170"/>
+      <c r="F35" s="168"/>
       <c r="G35" s="73"/>
       <c r="H35" s="73"/>
       <c r="I35" s="73"/>
       <c r="J35" s="74"/>
-      <c r="K35" s="139"/>
+      <c r="K35" s="137"/>
       <c r="L35" s="45"/>
       <c r="M35" s="45"/>
       <c r="N35" s="45"/>
     </row>
     <row r="36" spans="1:15" s="14" customFormat="1" ht="21" customHeight="1">
-      <c r="A36" s="147"/>
-      <c r="B36" s="159"/>
-      <c r="C36" s="162"/>
-      <c r="D36" s="170"/>
+      <c r="A36" s="145"/>
+      <c r="B36" s="157"/>
+      <c r="C36" s="160"/>
+      <c r="D36" s="168"/>
       <c r="E36" s="18"/>
-      <c r="F36" s="170"/>
+      <c r="F36" s="168"/>
       <c r="G36" s="73"/>
       <c r="H36" s="73"/>
       <c r="I36" s="73"/>
       <c r="J36" s="74"/>
-      <c r="K36" s="139"/>
+      <c r="K36" s="137"/>
       <c r="L36" s="45"/>
       <c r="M36" s="45"/>
       <c r="N36" s="45"/>
     </row>
     <row r="37" spans="1:15" s="14" customFormat="1" ht="21" customHeight="1">
-      <c r="A37" s="148"/>
-      <c r="B37" s="160"/>
-      <c r="C37" s="163"/>
-      <c r="D37" s="171"/>
+      <c r="A37" s="146"/>
+      <c r="B37" s="158"/>
+      <c r="C37" s="161"/>
+      <c r="D37" s="169"/>
       <c r="E37" s="18"/>
-      <c r="F37" s="171"/>
+      <c r="F37" s="169"/>
       <c r="G37" s="73"/>
       <c r="H37" s="73"/>
       <c r="I37" s="73"/>
       <c r="J37" s="74"/>
-      <c r="K37" s="139"/>
+      <c r="K37" s="137"/>
       <c r="L37" s="45"/>
       <c r="M37" s="45"/>
       <c r="N37" s="45"/>
@@ -8494,74 +8479,74 @@
       <c r="O40" s="13"/>
     </row>
     <row r="41" spans="1:15" s="22" customFormat="1" ht="21" hidden="1" customHeight="1">
-      <c r="A41" s="188" t="s">
+      <c r="A41" s="186" t="s">
         <v>33</v>
       </c>
-      <c r="B41" s="188" t="s">
+      <c r="B41" s="186" t="s">
         <v>34</v>
       </c>
-      <c r="C41" s="188" t="s">
+      <c r="C41" s="186" t="s">
         <v>35</v>
       </c>
-      <c r="D41" s="191" t="s">
+      <c r="D41" s="189" t="s">
         <v>35</v>
       </c>
       <c r="E41" s="34"/>
-      <c r="F41" s="188" t="s">
+      <c r="F41" s="186" t="s">
         <v>36</v>
       </c>
-      <c r="G41" s="188" t="s">
+      <c r="G41" s="186" t="s">
         <v>31</v>
       </c>
-      <c r="H41" s="194" t="s">
+      <c r="H41" s="192" t="s">
         <v>46</v>
       </c>
-      <c r="I41" s="194" t="s">
+      <c r="I41" s="192" t="s">
         <v>41</v>
       </c>
-      <c r="J41" s="194" t="s">
+      <c r="J41" s="192" t="s">
         <v>42</v>
       </c>
-      <c r="K41" s="194" t="s">
+      <c r="K41" s="192" t="s">
         <v>70</v>
       </c>
-      <c r="L41" s="197" t="s">
+      <c r="L41" s="195" t="s">
         <v>37</v>
       </c>
-      <c r="M41" s="198"/>
-      <c r="N41" s="187" t="s">
+      <c r="M41" s="196"/>
+      <c r="N41" s="185" t="s">
         <v>38</v>
       </c>
-      <c r="O41" s="187"/>
+      <c r="O41" s="185"/>
     </row>
     <row r="42" spans="1:15" s="22" customFormat="1" ht="21" hidden="1" customHeight="1">
-      <c r="A42" s="189"/>
-      <c r="B42" s="189"/>
-      <c r="C42" s="189"/>
-      <c r="D42" s="192"/>
-      <c r="F42" s="189"/>
-      <c r="G42" s="189"/>
-      <c r="H42" s="195"/>
-      <c r="I42" s="195"/>
-      <c r="J42" s="195"/>
-      <c r="K42" s="195"/>
-      <c r="L42" s="199"/>
-      <c r="M42" s="200"/>
-      <c r="N42" s="187"/>
-      <c r="O42" s="187"/>
+      <c r="A42" s="187"/>
+      <c r="B42" s="187"/>
+      <c r="C42" s="187"/>
+      <c r="D42" s="190"/>
+      <c r="F42" s="187"/>
+      <c r="G42" s="187"/>
+      <c r="H42" s="193"/>
+      <c r="I42" s="193"/>
+      <c r="J42" s="193"/>
+      <c r="K42" s="193"/>
+      <c r="L42" s="197"/>
+      <c r="M42" s="198"/>
+      <c r="N42" s="185"/>
+      <c r="O42" s="185"/>
     </row>
     <row r="43" spans="1:15" s="22" customFormat="1" ht="21" hidden="1" customHeight="1">
-      <c r="A43" s="190"/>
-      <c r="B43" s="190"/>
-      <c r="C43" s="190"/>
-      <c r="D43" s="193"/>
+      <c r="A43" s="188"/>
+      <c r="B43" s="188"/>
+      <c r="C43" s="188"/>
+      <c r="D43" s="191"/>
       <c r="E43" s="36"/>
-      <c r="F43" s="190"/>
-      <c r="G43" s="190"/>
-      <c r="H43" s="196"/>
-      <c r="I43" s="196"/>
-      <c r="J43" s="196"/>
-      <c r="K43" s="196"/>
+      <c r="F43" s="188"/>
+      <c r="G43" s="188"/>
+      <c r="H43" s="194"/>
+      <c r="I43" s="194"/>
+      <c r="J43" s="194"/>
+      <c r="K43" s="194"/>
       <c r="L43" s="35" t="s">
         <v>39</v>
       </c>
@@ -8839,28 +8824,28 @@
   <sheetData>
     <row r="1" spans="1:26" ht="15">
       <c r="A1" s="78"/>
-      <c r="B1" s="266" t="s">
+      <c r="B1" s="264" t="s">
         <v>103</v>
       </c>
-      <c r="C1" s="266"/>
-      <c r="D1" s="266"/>
-      <c r="E1" s="266"/>
-      <c r="F1" s="266"/>
-      <c r="G1" s="266"/>
-      <c r="H1" s="266"/>
-      <c r="I1" s="266"/>
-      <c r="J1" s="266"/>
-      <c r="K1" s="266"/>
-      <c r="L1" s="266"/>
-      <c r="M1" s="266"/>
-      <c r="N1" s="266"/>
-      <c r="O1" s="266"/>
-      <c r="P1" s="266"/>
-      <c r="Q1" s="266"/>
-      <c r="R1" s="266"/>
-      <c r="S1" s="266"/>
-      <c r="T1" s="266"/>
-      <c r="U1" s="266"/>
+      <c r="C1" s="264"/>
+      <c r="D1" s="264"/>
+      <c r="E1" s="264"/>
+      <c r="F1" s="264"/>
+      <c r="G1" s="264"/>
+      <c r="H1" s="264"/>
+      <c r="I1" s="264"/>
+      <c r="J1" s="264"/>
+      <c r="K1" s="264"/>
+      <c r="L1" s="264"/>
+      <c r="M1" s="264"/>
+      <c r="N1" s="264"/>
+      <c r="O1" s="264"/>
+      <c r="P1" s="264"/>
+      <c r="Q1" s="264"/>
+      <c r="R1" s="264"/>
+      <c r="S1" s="264"/>
+      <c r="T1" s="264"/>
+      <c r="U1" s="264"/>
       <c r="V1" s="79"/>
       <c r="W1" s="79"/>
       <c r="X1" s="79"/>
@@ -8869,26 +8854,26 @@
     </row>
     <row r="2" spans="1:26" ht="15">
       <c r="A2" s="78"/>
-      <c r="B2" s="266"/>
-      <c r="C2" s="266"/>
-      <c r="D2" s="266"/>
-      <c r="E2" s="266"/>
-      <c r="F2" s="266"/>
-      <c r="G2" s="266"/>
-      <c r="H2" s="266"/>
-      <c r="I2" s="266"/>
-      <c r="J2" s="266"/>
-      <c r="K2" s="266"/>
-      <c r="L2" s="266"/>
-      <c r="M2" s="266"/>
-      <c r="N2" s="266"/>
-      <c r="O2" s="266"/>
-      <c r="P2" s="266"/>
-      <c r="Q2" s="266"/>
-      <c r="R2" s="266"/>
-      <c r="S2" s="266"/>
-      <c r="T2" s="266"/>
-      <c r="U2" s="266"/>
+      <c r="B2" s="264"/>
+      <c r="C2" s="264"/>
+      <c r="D2" s="264"/>
+      <c r="E2" s="264"/>
+      <c r="F2" s="264"/>
+      <c r="G2" s="264"/>
+      <c r="H2" s="264"/>
+      <c r="I2" s="264"/>
+      <c r="J2" s="264"/>
+      <c r="K2" s="264"/>
+      <c r="L2" s="264"/>
+      <c r="M2" s="264"/>
+      <c r="N2" s="264"/>
+      <c r="O2" s="264"/>
+      <c r="P2" s="264"/>
+      <c r="Q2" s="264"/>
+      <c r="R2" s="264"/>
+      <c r="S2" s="264"/>
+      <c r="T2" s="264"/>
+      <c r="U2" s="264"/>
       <c r="V2" s="79"/>
       <c r="W2" s="79"/>
       <c r="X2" s="79"/>
@@ -8897,26 +8882,26 @@
     </row>
     <row r="3" spans="1:26" ht="15">
       <c r="A3" s="78"/>
-      <c r="B3" s="266"/>
-      <c r="C3" s="266"/>
-      <c r="D3" s="266"/>
-      <c r="E3" s="266"/>
-      <c r="F3" s="266"/>
-      <c r="G3" s="266"/>
-      <c r="H3" s="266"/>
-      <c r="I3" s="266"/>
-      <c r="J3" s="266"/>
-      <c r="K3" s="266"/>
-      <c r="L3" s="266"/>
-      <c r="M3" s="266"/>
-      <c r="N3" s="266"/>
-      <c r="O3" s="266"/>
-      <c r="P3" s="266"/>
-      <c r="Q3" s="266"/>
-      <c r="R3" s="266"/>
-      <c r="S3" s="266"/>
-      <c r="T3" s="266"/>
-      <c r="U3" s="266"/>
+      <c r="B3" s="264"/>
+      <c r="C3" s="264"/>
+      <c r="D3" s="264"/>
+      <c r="E3" s="264"/>
+      <c r="F3" s="264"/>
+      <c r="G3" s="264"/>
+      <c r="H3" s="264"/>
+      <c r="I3" s="264"/>
+      <c r="J3" s="264"/>
+      <c r="K3" s="264"/>
+      <c r="L3" s="264"/>
+      <c r="M3" s="264"/>
+      <c r="N3" s="264"/>
+      <c r="O3" s="264"/>
+      <c r="P3" s="264"/>
+      <c r="Q3" s="264"/>
+      <c r="R3" s="264"/>
+      <c r="S3" s="264"/>
+      <c r="T3" s="264"/>
+      <c r="U3" s="264"/>
       <c r="V3" s="79"/>
       <c r="W3" s="79"/>
       <c r="X3" s="79"/>
@@ -8925,26 +8910,26 @@
     </row>
     <row r="4" spans="1:26" ht="15">
       <c r="A4" s="78"/>
-      <c r="B4" s="266"/>
-      <c r="C4" s="266"/>
-      <c r="D4" s="266"/>
-      <c r="E4" s="266"/>
-      <c r="F4" s="266"/>
-      <c r="G4" s="266"/>
-      <c r="H4" s="266"/>
-      <c r="I4" s="266"/>
-      <c r="J4" s="266"/>
-      <c r="K4" s="266"/>
-      <c r="L4" s="266"/>
-      <c r="M4" s="266"/>
-      <c r="N4" s="266"/>
-      <c r="O4" s="266"/>
-      <c r="P4" s="266"/>
-      <c r="Q4" s="266"/>
-      <c r="R4" s="266"/>
-      <c r="S4" s="266"/>
-      <c r="T4" s="266"/>
-      <c r="U4" s="266"/>
+      <c r="B4" s="264"/>
+      <c r="C4" s="264"/>
+      <c r="D4" s="264"/>
+      <c r="E4" s="264"/>
+      <c r="F4" s="264"/>
+      <c r="G4" s="264"/>
+      <c r="H4" s="264"/>
+      <c r="I4" s="264"/>
+      <c r="J4" s="264"/>
+      <c r="K4" s="264"/>
+      <c r="L4" s="264"/>
+      <c r="M4" s="264"/>
+      <c r="N4" s="264"/>
+      <c r="O4" s="264"/>
+      <c r="P4" s="264"/>
+      <c r="Q4" s="264"/>
+      <c r="R4" s="264"/>
+      <c r="S4" s="264"/>
+      <c r="T4" s="264"/>
+      <c r="U4" s="264"/>
       <c r="V4" s="79"/>
       <c r="W4" s="79"/>
       <c r="X4" s="79"/>
@@ -8953,26 +8938,26 @@
     </row>
     <row r="5" spans="1:26" ht="15">
       <c r="A5" s="78"/>
-      <c r="B5" s="266"/>
-      <c r="C5" s="266"/>
-      <c r="D5" s="266"/>
-      <c r="E5" s="266"/>
-      <c r="F5" s="266"/>
-      <c r="G5" s="266"/>
-      <c r="H5" s="266"/>
-      <c r="I5" s="266"/>
-      <c r="J5" s="266"/>
-      <c r="K5" s="266"/>
-      <c r="L5" s="266"/>
-      <c r="M5" s="266"/>
-      <c r="N5" s="266"/>
-      <c r="O5" s="266"/>
-      <c r="P5" s="266"/>
-      <c r="Q5" s="266"/>
-      <c r="R5" s="266"/>
-      <c r="S5" s="266"/>
-      <c r="T5" s="266"/>
-      <c r="U5" s="266"/>
+      <c r="B5" s="264"/>
+      <c r="C5" s="264"/>
+      <c r="D5" s="264"/>
+      <c r="E5" s="264"/>
+      <c r="F5" s="264"/>
+      <c r="G5" s="264"/>
+      <c r="H5" s="264"/>
+      <c r="I5" s="264"/>
+      <c r="J5" s="264"/>
+      <c r="K5" s="264"/>
+      <c r="L5" s="264"/>
+      <c r="M5" s="264"/>
+      <c r="N5" s="264"/>
+      <c r="O5" s="264"/>
+      <c r="P5" s="264"/>
+      <c r="Q5" s="264"/>
+      <c r="R5" s="264"/>
+      <c r="S5" s="264"/>
+      <c r="T5" s="264"/>
+      <c r="U5" s="264"/>
       <c r="V5" s="79"/>
       <c r="W5" s="79"/>
       <c r="X5" s="79"/>
@@ -8980,54 +8965,54 @@
       <c r="Z5" s="79"/>
     </row>
     <row r="6" spans="1:26" ht="30">
-      <c r="A6" s="278" t="s">
+      <c r="A6" s="276" t="s">
         <v>104</v>
       </c>
-      <c r="B6" s="278"/>
-      <c r="C6" s="278"/>
-      <c r="D6" s="278"/>
-      <c r="E6" s="278"/>
-      <c r="F6" s="278"/>
-      <c r="G6" s="278"/>
-      <c r="H6" s="278"/>
-      <c r="I6" s="278"/>
-      <c r="J6" s="278"/>
-      <c r="K6" s="278"/>
-      <c r="L6" s="278"/>
-      <c r="M6" s="278"/>
-      <c r="N6" s="278"/>
-      <c r="O6" s="278"/>
-      <c r="P6" s="278"/>
-      <c r="Q6" s="278"/>
-      <c r="R6" s="278"/>
-      <c r="S6" s="278"/>
-      <c r="T6" s="278"/>
-      <c r="U6" s="278"/>
-      <c r="V6" s="278"/>
-      <c r="W6" s="278"/>
-      <c r="X6" s="278"/>
-      <c r="Y6" s="278"/>
-      <c r="Z6" s="278"/>
+      <c r="B6" s="276"/>
+      <c r="C6" s="276"/>
+      <c r="D6" s="276"/>
+      <c r="E6" s="276"/>
+      <c r="F6" s="276"/>
+      <c r="G6" s="276"/>
+      <c r="H6" s="276"/>
+      <c r="I6" s="276"/>
+      <c r="J6" s="276"/>
+      <c r="K6" s="276"/>
+      <c r="L6" s="276"/>
+      <c r="M6" s="276"/>
+      <c r="N6" s="276"/>
+      <c r="O6" s="276"/>
+      <c r="P6" s="276"/>
+      <c r="Q6" s="276"/>
+      <c r="R6" s="276"/>
+      <c r="S6" s="276"/>
+      <c r="T6" s="276"/>
+      <c r="U6" s="276"/>
+      <c r="V6" s="276"/>
+      <c r="W6" s="276"/>
+      <c r="X6" s="276"/>
+      <c r="Y6" s="276"/>
+      <c r="Z6" s="276"/>
     </row>
     <row r="7" spans="1:26" s="14" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A7" s="267" t="s">
+      <c r="A7" s="265" t="s">
         <v>104</v>
       </c>
-      <c r="B7" s="267"/>
+      <c r="B7" s="265"/>
       <c r="C7" s="72" t="s">
         <v>224</v>
       </c>
       <c r="E7" s="19"/>
       <c r="F7" s="19"/>
-      <c r="G7" s="280">
+      <c r="G7" s="278" t="str">
         <f>'ใบงาน Agilent_JOB 1.1'!F7</f>
-        <v>0</v>
-      </c>
-      <c r="H7" s="280"/>
-      <c r="I7" s="280"/>
-      <c r="J7" s="280"/>
-      <c r="K7" s="280"/>
-      <c r="L7" s="280"/>
+        <v>xxx</v>
+      </c>
+      <c r="H7" s="278"/>
+      <c r="I7" s="278"/>
+      <c r="J7" s="278"/>
+      <c r="K7" s="278"/>
+      <c r="L7" s="278"/>
       <c r="M7" s="19"/>
       <c r="N7" s="19"/>
       <c r="O7" s="19"/>
@@ -9037,35 +9022,35 @@
       <c r="S7" s="82" t="s">
         <v>87</v>
       </c>
-      <c r="W7" s="279">
-        <f>'ใบงาน Agilent_JOB 1.1'!M7</f>
+      <c r="W7" s="277">
+        <f>'ใบงาน Agilent_JOB 1.1'!N7</f>
         <v>20260803</v>
       </c>
-      <c r="X7" s="279"/>
+      <c r="X7" s="277"/>
       <c r="Y7" s="42"/>
       <c r="Z7" s="42"/>
     </row>
     <row r="8" spans="1:26" s="14" customFormat="1" ht="13.8">
-      <c r="A8" s="96" t="s">
+      <c r="A8" s="95" t="s">
         <v>225</v>
       </c>
-      <c r="B8" s="97" t="str">
+      <c r="B8" s="96" t="str">
         <f>'ใบงาน Agilent_JOB 1.1'!F8</f>
         <v>K9801-60098</v>
       </c>
-      <c r="C8" s="97" t="s">
+      <c r="C8" s="96" t="s">
         <v>226</v>
       </c>
-      <c r="D8" s="97"/>
-      <c r="E8" s="97"/>
-      <c r="F8" s="97"/>
-      <c r="G8" s="279" t="str">
+      <c r="D8" s="96"/>
+      <c r="E8" s="96"/>
+      <c r="F8" s="96"/>
+      <c r="G8" s="277" t="str">
         <f>'ใบงาน Agilent_JOB 1.1'!F9</f>
         <v>K9801-60079</v>
       </c>
-      <c r="H8" s="279"/>
-      <c r="I8" s="279"/>
-      <c r="J8" s="279"/>
+      <c r="H8" s="277"/>
+      <c r="I8" s="277"/>
+      <c r="J8" s="277"/>
       <c r="K8" s="71"/>
       <c r="L8" s="71"/>
       <c r="M8" s="71"/>
@@ -9078,21 +9063,21 @@
       <c r="T8" s="71"/>
     </row>
     <row r="9" spans="1:26" s="14" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A9" s="268" t="s">
+      <c r="A9" s="266" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="268"/>
+      <c r="B9" s="266"/>
       <c r="C9" s="42"/>
       <c r="D9" s="42"/>
       <c r="E9" s="42"/>
       <c r="F9" s="42"/>
-      <c r="G9" s="279" t="str">
+      <c r="G9" s="277" t="str">
         <f>'ใบงาน Agilent_JOB 1.2'!F9</f>
         <v>K9801-60080</v>
       </c>
-      <c r="H9" s="279"/>
-      <c r="I9" s="279"/>
-      <c r="J9" s="279"/>
+      <c r="H9" s="277"/>
+      <c r="I9" s="277"/>
+      <c r="J9" s="277"/>
       <c r="L9" s="19"/>
       <c r="M9" s="19"/>
       <c r="N9" s="19"/>
@@ -9100,34 +9085,34 @@
       <c r="P9" s="19"/>
       <c r="Q9" s="19"/>
       <c r="R9" s="19"/>
-      <c r="S9" s="174" t="s">
+      <c r="S9" s="172" t="s">
         <v>245</v>
       </c>
-      <c r="T9" s="174"/>
-      <c r="U9" s="174"/>
-      <c r="V9" s="174"/>
+      <c r="T9" s="172"/>
+      <c r="U9" s="172"/>
+      <c r="V9" s="172"/>
     </row>
     <row r="10" spans="1:26" s="14" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A10" s="96" t="s">
+      <c r="A10" s="95" t="s">
         <v>247</v>
       </c>
-      <c r="B10" s="122">
-        <f>'ใบงาน Agilent_JOB 1.1'!M8</f>
+      <c r="B10" s="118">
+        <f>'ใบงาน Agilent_JOB 1.1'!N8</f>
         <v>2000</v>
       </c>
-      <c r="C10" s="101"/>
-      <c r="D10" s="226" t="s">
+      <c r="C10" s="100"/>
+      <c r="D10" s="224" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="226"/>
-      <c r="F10" s="226"/>
-      <c r="G10" s="226" t="str">
+      <c r="E10" s="224"/>
+      <c r="F10" s="224"/>
+      <c r="G10" s="224" t="str">
         <f>'ใบงาน Agilent_JOB 1.3'!F9</f>
         <v>K9801-60081</v>
       </c>
-      <c r="H10" s="226"/>
-      <c r="I10" s="226"/>
-      <c r="J10" s="226"/>
+      <c r="H10" s="224"/>
+      <c r="I10" s="224"/>
+      <c r="J10" s="224"/>
       <c r="K10" s="72"/>
       <c r="L10" s="19"/>
       <c r="M10" s="19"/>
@@ -9136,25 +9121,25 @@
       <c r="P10" s="19"/>
       <c r="Q10" s="19"/>
       <c r="R10" s="19"/>
-      <c r="S10" s="174"/>
-      <c r="T10" s="174"/>
-      <c r="U10" s="174"/>
-      <c r="V10" s="174"/>
+      <c r="S10" s="172"/>
+      <c r="T10" s="172"/>
+      <c r="U10" s="172"/>
+      <c r="V10" s="172"/>
     </row>
     <row r="11" spans="1:26" s="14" customFormat="1" ht="13.8">
-      <c r="A11" s="101"/>
+      <c r="A11" s="100"/>
       <c r="B11" s="77"/>
-      <c r="C11" s="101"/>
-      <c r="D11" s="101"/>
-      <c r="E11" s="101"/>
-      <c r="F11" s="101"/>
-      <c r="G11" s="226" t="str">
+      <c r="C11" s="100"/>
+      <c r="D11" s="100"/>
+      <c r="E11" s="100"/>
+      <c r="F11" s="100"/>
+      <c r="G11" s="224" t="str">
         <f>'ใบงาน Agilent_JOB 1.4'!F9</f>
         <v>K9801-60084</v>
       </c>
-      <c r="H11" s="226"/>
-      <c r="I11" s="226"/>
-      <c r="J11" s="226"/>
+      <c r="H11" s="224"/>
+      <c r="I11" s="224"/>
+      <c r="J11" s="224"/>
       <c r="K11" s="19"/>
       <c r="L11" s="19"/>
       <c r="M11" s="19"/>
@@ -9167,21 +9152,21 @@
       <c r="T11" s="19"/>
     </row>
     <row r="12" spans="1:26" s="14" customFormat="1" ht="13.8">
-      <c r="A12" s="101" t="s">
+      <c r="A12" s="100" t="s">
         <v>244</v>
       </c>
       <c r="B12" s="77"/>
-      <c r="C12" s="101"/>
-      <c r="D12" s="101"/>
-      <c r="E12" s="101"/>
-      <c r="F12" s="101"/>
-      <c r="G12" s="226" t="str">
+      <c r="C12" s="100"/>
+      <c r="D12" s="100"/>
+      <c r="E12" s="100"/>
+      <c r="F12" s="100"/>
+      <c r="G12" s="224" t="str">
         <f>'ใบงาน Agilent_JOB 1.5'!F9</f>
         <v>K9801-60085</v>
       </c>
-      <c r="H12" s="226"/>
-      <c r="I12" s="226"/>
-      <c r="J12" s="226"/>
+      <c r="H12" s="224"/>
+      <c r="I12" s="224"/>
+      <c r="J12" s="224"/>
       <c r="K12" s="19"/>
       <c r="L12" s="19"/>
       <c r="M12" s="19"/>
@@ -9216,72 +9201,72 @@
       <c r="T13" s="19"/>
     </row>
     <row r="14" spans="1:26" s="14" customFormat="1" ht="13.8">
-      <c r="A14" s="269" t="s">
+      <c r="A14" s="267" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="269" t="s">
+      <c r="B14" s="267" t="s">
         <v>105</v>
       </c>
-      <c r="C14" s="197" t="s">
+      <c r="C14" s="195" t="s">
         <v>106</v>
       </c>
-      <c r="D14" s="271"/>
-      <c r="E14" s="271"/>
-      <c r="F14" s="271"/>
-      <c r="G14" s="271"/>
-      <c r="H14" s="272"/>
-      <c r="I14" s="197" t="s">
+      <c r="D14" s="269"/>
+      <c r="E14" s="269"/>
+      <c r="F14" s="269"/>
+      <c r="G14" s="269"/>
+      <c r="H14" s="270"/>
+      <c r="I14" s="195" t="s">
         <v>39</v>
       </c>
-      <c r="J14" s="271"/>
-      <c r="K14" s="271"/>
-      <c r="L14" s="271"/>
-      <c r="M14" s="271"/>
-      <c r="N14" s="272"/>
-      <c r="O14" s="197" t="s">
+      <c r="J14" s="269"/>
+      <c r="K14" s="269"/>
+      <c r="L14" s="269"/>
+      <c r="M14" s="269"/>
+      <c r="N14" s="270"/>
+      <c r="O14" s="195" t="s">
         <v>40</v>
       </c>
-      <c r="P14" s="275"/>
-      <c r="Q14" s="275"/>
-      <c r="R14" s="275"/>
-      <c r="S14" s="275"/>
-      <c r="T14" s="198"/>
-      <c r="U14" s="277" t="s">
+      <c r="P14" s="273"/>
+      <c r="Q14" s="273"/>
+      <c r="R14" s="273"/>
+      <c r="S14" s="273"/>
+      <c r="T14" s="196"/>
+      <c r="U14" s="275" t="s">
         <v>107</v>
       </c>
-      <c r="V14" s="277"/>
-      <c r="W14" s="277"/>
-      <c r="X14" s="277"/>
-      <c r="Y14" s="277"/>
-      <c r="Z14" s="277"/>
+      <c r="V14" s="275"/>
+      <c r="W14" s="275"/>
+      <c r="X14" s="275"/>
+      <c r="Y14" s="275"/>
+      <c r="Z14" s="275"/>
     </row>
     <row r="15" spans="1:26" s="14" customFormat="1" ht="13.8">
-      <c r="A15" s="270"/>
-      <c r="B15" s="269"/>
-      <c r="C15" s="193"/>
-      <c r="D15" s="273"/>
-      <c r="E15" s="273"/>
-      <c r="F15" s="273"/>
-      <c r="G15" s="273"/>
-      <c r="H15" s="274"/>
-      <c r="I15" s="193"/>
-      <c r="J15" s="273"/>
-      <c r="K15" s="273"/>
-      <c r="L15" s="273"/>
-      <c r="M15" s="273"/>
-      <c r="N15" s="274"/>
-      <c r="O15" s="199"/>
-      <c r="P15" s="276"/>
-      <c r="Q15" s="276"/>
-      <c r="R15" s="276"/>
-      <c r="S15" s="276"/>
-      <c r="T15" s="200"/>
-      <c r="U15" s="277"/>
-      <c r="V15" s="277"/>
-      <c r="W15" s="277"/>
-      <c r="X15" s="277"/>
-      <c r="Y15" s="277"/>
-      <c r="Z15" s="277"/>
+      <c r="A15" s="268"/>
+      <c r="B15" s="267"/>
+      <c r="C15" s="191"/>
+      <c r="D15" s="271"/>
+      <c r="E15" s="271"/>
+      <c r="F15" s="271"/>
+      <c r="G15" s="271"/>
+      <c r="H15" s="272"/>
+      <c r="I15" s="191"/>
+      <c r="J15" s="271"/>
+      <c r="K15" s="271"/>
+      <c r="L15" s="271"/>
+      <c r="M15" s="271"/>
+      <c r="N15" s="272"/>
+      <c r="O15" s="197"/>
+      <c r="P15" s="274"/>
+      <c r="Q15" s="274"/>
+      <c r="R15" s="274"/>
+      <c r="S15" s="274"/>
+      <c r="T15" s="198"/>
+      <c r="U15" s="275"/>
+      <c r="V15" s="275"/>
+      <c r="W15" s="275"/>
+      <c r="X15" s="275"/>
+      <c r="Y15" s="275"/>
+      <c r="Z15" s="275"/>
     </row>
     <row r="16" spans="1:26" s="83" customFormat="1" ht="35.700000000000003" customHeight="1">
       <c r="A16" s="84">
@@ -9290,182 +9275,182 @@
       <c r="B16" s="85" t="s">
         <v>108</v>
       </c>
-      <c r="C16" s="227"/>
-      <c r="D16" s="227"/>
-      <c r="E16" s="227"/>
-      <c r="F16" s="227"/>
-      <c r="G16" s="227"/>
-      <c r="H16" s="227"/>
-      <c r="I16" s="227"/>
-      <c r="J16" s="227"/>
-      <c r="K16" s="227"/>
-      <c r="L16" s="227"/>
-      <c r="M16" s="227"/>
-      <c r="N16" s="227"/>
-      <c r="O16" s="227"/>
-      <c r="P16" s="227"/>
-      <c r="Q16" s="227"/>
-      <c r="R16" s="227"/>
-      <c r="S16" s="227"/>
-      <c r="T16" s="227"/>
-      <c r="U16" s="227"/>
-      <c r="V16" s="227"/>
-      <c r="W16" s="227"/>
-      <c r="X16" s="227"/>
-      <c r="Y16" s="227"/>
-      <c r="Z16" s="227"/>
+      <c r="C16" s="225"/>
+      <c r="D16" s="225"/>
+      <c r="E16" s="225"/>
+      <c r="F16" s="225"/>
+      <c r="G16" s="225"/>
+      <c r="H16" s="225"/>
+      <c r="I16" s="225"/>
+      <c r="J16" s="225"/>
+      <c r="K16" s="225"/>
+      <c r="L16" s="225"/>
+      <c r="M16" s="225"/>
+      <c r="N16" s="225"/>
+      <c r="O16" s="225"/>
+      <c r="P16" s="225"/>
+      <c r="Q16" s="225"/>
+      <c r="R16" s="225"/>
+      <c r="S16" s="225"/>
+      <c r="T16" s="225"/>
+      <c r="U16" s="225"/>
+      <c r="V16" s="225"/>
+      <c r="W16" s="225"/>
+      <c r="X16" s="225"/>
+      <c r="Y16" s="225"/>
+      <c r="Z16" s="225"/>
     </row>
     <row r="17" spans="1:26" s="83" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A17" s="263">
+      <c r="A17" s="261">
         <v>2</v>
       </c>
       <c r="B17" s="86" t="s">
         <v>109</v>
       </c>
-      <c r="C17" s="227"/>
-      <c r="D17" s="227"/>
-      <c r="E17" s="227"/>
-      <c r="F17" s="227"/>
-      <c r="G17" s="227"/>
-      <c r="H17" s="227"/>
-      <c r="I17" s="227"/>
-      <c r="J17" s="227"/>
-      <c r="K17" s="227"/>
-      <c r="L17" s="227"/>
-      <c r="M17" s="227"/>
-      <c r="N17" s="227"/>
-      <c r="O17" s="227"/>
-      <c r="P17" s="227"/>
-      <c r="Q17" s="227"/>
-      <c r="R17" s="227"/>
-      <c r="S17" s="227"/>
-      <c r="T17" s="227"/>
-      <c r="U17" s="227"/>
-      <c r="V17" s="227"/>
-      <c r="W17" s="227"/>
-      <c r="X17" s="227"/>
-      <c r="Y17" s="227"/>
-      <c r="Z17" s="227"/>
+      <c r="C17" s="225"/>
+      <c r="D17" s="225"/>
+      <c r="E17" s="225"/>
+      <c r="F17" s="225"/>
+      <c r="G17" s="225"/>
+      <c r="H17" s="225"/>
+      <c r="I17" s="225"/>
+      <c r="J17" s="225"/>
+      <c r="K17" s="225"/>
+      <c r="L17" s="225"/>
+      <c r="M17" s="225"/>
+      <c r="N17" s="225"/>
+      <c r="O17" s="225"/>
+      <c r="P17" s="225"/>
+      <c r="Q17" s="225"/>
+      <c r="R17" s="225"/>
+      <c r="S17" s="225"/>
+      <c r="T17" s="225"/>
+      <c r="U17" s="225"/>
+      <c r="V17" s="225"/>
+      <c r="W17" s="225"/>
+      <c r="X17" s="225"/>
+      <c r="Y17" s="225"/>
+      <c r="Z17" s="225"/>
     </row>
     <row r="18" spans="1:26" s="83" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A18" s="264"/>
+      <c r="A18" s="262"/>
       <c r="B18" s="86" t="s">
         <v>110</v>
       </c>
-      <c r="C18" s="227"/>
-      <c r="D18" s="227"/>
-      <c r="E18" s="227"/>
-      <c r="F18" s="227"/>
-      <c r="G18" s="227"/>
-      <c r="H18" s="227"/>
-      <c r="I18" s="227"/>
-      <c r="J18" s="227"/>
-      <c r="K18" s="227"/>
-      <c r="L18" s="227"/>
-      <c r="M18" s="227"/>
-      <c r="N18" s="227"/>
-      <c r="O18" s="227"/>
-      <c r="P18" s="227"/>
-      <c r="Q18" s="227"/>
-      <c r="R18" s="227"/>
-      <c r="S18" s="227"/>
-      <c r="T18" s="227"/>
-      <c r="U18" s="227"/>
-      <c r="V18" s="227"/>
-      <c r="W18" s="227"/>
-      <c r="X18" s="227"/>
-      <c r="Y18" s="227"/>
-      <c r="Z18" s="227"/>
+      <c r="C18" s="225"/>
+      <c r="D18" s="225"/>
+      <c r="E18" s="225"/>
+      <c r="F18" s="225"/>
+      <c r="G18" s="225"/>
+      <c r="H18" s="225"/>
+      <c r="I18" s="225"/>
+      <c r="J18" s="225"/>
+      <c r="K18" s="225"/>
+      <c r="L18" s="225"/>
+      <c r="M18" s="225"/>
+      <c r="N18" s="225"/>
+      <c r="O18" s="225"/>
+      <c r="P18" s="225"/>
+      <c r="Q18" s="225"/>
+      <c r="R18" s="225"/>
+      <c r="S18" s="225"/>
+      <c r="T18" s="225"/>
+      <c r="U18" s="225"/>
+      <c r="V18" s="225"/>
+      <c r="W18" s="225"/>
+      <c r="X18" s="225"/>
+      <c r="Y18" s="225"/>
+      <c r="Z18" s="225"/>
     </row>
     <row r="19" spans="1:26" s="83" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A19" s="264"/>
+      <c r="A19" s="262"/>
       <c r="B19" s="86" t="s">
         <v>111</v>
       </c>
-      <c r="C19" s="227"/>
-      <c r="D19" s="227"/>
-      <c r="E19" s="227"/>
-      <c r="F19" s="227"/>
-      <c r="G19" s="227"/>
-      <c r="H19" s="227"/>
-      <c r="I19" s="227"/>
-      <c r="J19" s="227"/>
-      <c r="K19" s="227"/>
-      <c r="L19" s="227"/>
-      <c r="M19" s="227"/>
-      <c r="N19" s="227"/>
-      <c r="O19" s="227"/>
-      <c r="P19" s="227"/>
-      <c r="Q19" s="227"/>
-      <c r="R19" s="227"/>
-      <c r="S19" s="227"/>
-      <c r="T19" s="227"/>
-      <c r="U19" s="227"/>
-      <c r="V19" s="227"/>
-      <c r="W19" s="227"/>
-      <c r="X19" s="227"/>
-      <c r="Y19" s="227"/>
-      <c r="Z19" s="227"/>
+      <c r="C19" s="225"/>
+      <c r="D19" s="225"/>
+      <c r="E19" s="225"/>
+      <c r="F19" s="225"/>
+      <c r="G19" s="225"/>
+      <c r="H19" s="225"/>
+      <c r="I19" s="225"/>
+      <c r="J19" s="225"/>
+      <c r="K19" s="225"/>
+      <c r="L19" s="225"/>
+      <c r="M19" s="225"/>
+      <c r="N19" s="225"/>
+      <c r="O19" s="225"/>
+      <c r="P19" s="225"/>
+      <c r="Q19" s="225"/>
+      <c r="R19" s="225"/>
+      <c r="S19" s="225"/>
+      <c r="T19" s="225"/>
+      <c r="U19" s="225"/>
+      <c r="V19" s="225"/>
+      <c r="W19" s="225"/>
+      <c r="X19" s="225"/>
+      <c r="Y19" s="225"/>
+      <c r="Z19" s="225"/>
     </row>
     <row r="20" spans="1:26" s="83" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A20" s="264"/>
+      <c r="A20" s="262"/>
       <c r="B20" s="86" t="s">
         <v>112</v>
       </c>
-      <c r="C20" s="227"/>
-      <c r="D20" s="227"/>
-      <c r="E20" s="227"/>
-      <c r="F20" s="227"/>
-      <c r="G20" s="227"/>
-      <c r="H20" s="227"/>
-      <c r="I20" s="227"/>
-      <c r="J20" s="227"/>
-      <c r="K20" s="227"/>
-      <c r="L20" s="227"/>
-      <c r="M20" s="227"/>
-      <c r="N20" s="227"/>
-      <c r="O20" s="227"/>
-      <c r="P20" s="227"/>
-      <c r="Q20" s="227"/>
-      <c r="R20" s="227"/>
-      <c r="S20" s="227"/>
-      <c r="T20" s="227"/>
-      <c r="U20" s="227"/>
-      <c r="V20" s="227"/>
-      <c r="W20" s="227"/>
-      <c r="X20" s="227"/>
-      <c r="Y20" s="227"/>
-      <c r="Z20" s="227"/>
+      <c r="C20" s="225"/>
+      <c r="D20" s="225"/>
+      <c r="E20" s="225"/>
+      <c r="F20" s="225"/>
+      <c r="G20" s="225"/>
+      <c r="H20" s="225"/>
+      <c r="I20" s="225"/>
+      <c r="J20" s="225"/>
+      <c r="K20" s="225"/>
+      <c r="L20" s="225"/>
+      <c r="M20" s="225"/>
+      <c r="N20" s="225"/>
+      <c r="O20" s="225"/>
+      <c r="P20" s="225"/>
+      <c r="Q20" s="225"/>
+      <c r="R20" s="225"/>
+      <c r="S20" s="225"/>
+      <c r="T20" s="225"/>
+      <c r="U20" s="225"/>
+      <c r="V20" s="225"/>
+      <c r="W20" s="225"/>
+      <c r="X20" s="225"/>
+      <c r="Y20" s="225"/>
+      <c r="Z20" s="225"/>
     </row>
     <row r="21" spans="1:26" s="83" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A21" s="265"/>
+      <c r="A21" s="263"/>
       <c r="B21" s="86" t="s">
         <v>113</v>
       </c>
-      <c r="C21" s="227"/>
-      <c r="D21" s="227"/>
-      <c r="E21" s="227"/>
-      <c r="F21" s="227"/>
-      <c r="G21" s="227"/>
-      <c r="H21" s="227"/>
-      <c r="I21" s="227"/>
-      <c r="J21" s="227"/>
-      <c r="K21" s="227"/>
-      <c r="L21" s="227"/>
-      <c r="M21" s="227"/>
-      <c r="N21" s="227"/>
-      <c r="O21" s="227"/>
-      <c r="P21" s="227"/>
-      <c r="Q21" s="227"/>
-      <c r="R21" s="227"/>
-      <c r="S21" s="227"/>
-      <c r="T21" s="227"/>
-      <c r="U21" s="227"/>
-      <c r="V21" s="227"/>
-      <c r="W21" s="227"/>
-      <c r="X21" s="227"/>
-      <c r="Y21" s="227"/>
-      <c r="Z21" s="227"/>
+      <c r="C21" s="225"/>
+      <c r="D21" s="225"/>
+      <c r="E21" s="225"/>
+      <c r="F21" s="225"/>
+      <c r="G21" s="225"/>
+      <c r="H21" s="225"/>
+      <c r="I21" s="225"/>
+      <c r="J21" s="225"/>
+      <c r="K21" s="225"/>
+      <c r="L21" s="225"/>
+      <c r="M21" s="225"/>
+      <c r="N21" s="225"/>
+      <c r="O21" s="225"/>
+      <c r="P21" s="225"/>
+      <c r="Q21" s="225"/>
+      <c r="R21" s="225"/>
+      <c r="S21" s="225"/>
+      <c r="T21" s="225"/>
+      <c r="U21" s="225"/>
+      <c r="V21" s="225"/>
+      <c r="W21" s="225"/>
+      <c r="X21" s="225"/>
+      <c r="Y21" s="225"/>
+      <c r="Z21" s="225"/>
     </row>
     <row r="22" spans="1:26" s="83" customFormat="1" ht="22.5" customHeight="1">
       <c r="A22" s="84">
@@ -9474,30 +9459,30 @@
       <c r="B22" s="85" t="s">
         <v>114</v>
       </c>
-      <c r="C22" s="227"/>
-      <c r="D22" s="227"/>
-      <c r="E22" s="227"/>
-      <c r="F22" s="227"/>
-      <c r="G22" s="227"/>
-      <c r="H22" s="227"/>
-      <c r="I22" s="227"/>
-      <c r="J22" s="227"/>
-      <c r="K22" s="227"/>
-      <c r="L22" s="227"/>
-      <c r="M22" s="227"/>
-      <c r="N22" s="227"/>
-      <c r="O22" s="227"/>
-      <c r="P22" s="227"/>
-      <c r="Q22" s="227"/>
-      <c r="R22" s="227"/>
-      <c r="S22" s="227"/>
-      <c r="T22" s="227"/>
-      <c r="U22" s="227"/>
-      <c r="V22" s="227"/>
-      <c r="W22" s="227"/>
-      <c r="X22" s="227"/>
-      <c r="Y22" s="227"/>
-      <c r="Z22" s="227"/>
+      <c r="C22" s="225"/>
+      <c r="D22" s="225"/>
+      <c r="E22" s="225"/>
+      <c r="F22" s="225"/>
+      <c r="G22" s="225"/>
+      <c r="H22" s="225"/>
+      <c r="I22" s="225"/>
+      <c r="J22" s="225"/>
+      <c r="K22" s="225"/>
+      <c r="L22" s="225"/>
+      <c r="M22" s="225"/>
+      <c r="N22" s="225"/>
+      <c r="O22" s="225"/>
+      <c r="P22" s="225"/>
+      <c r="Q22" s="225"/>
+      <c r="R22" s="225"/>
+      <c r="S22" s="225"/>
+      <c r="T22" s="225"/>
+      <c r="U22" s="225"/>
+      <c r="V22" s="225"/>
+      <c r="W22" s="225"/>
+      <c r="X22" s="225"/>
+      <c r="Y22" s="225"/>
+      <c r="Z22" s="225"/>
     </row>
     <row r="23" spans="1:26" s="83" customFormat="1" ht="22.5" customHeight="1">
       <c r="A23" s="84">
@@ -9506,30 +9491,30 @@
       <c r="B23" s="85" t="s">
         <v>115</v>
       </c>
-      <c r="C23" s="227"/>
-      <c r="D23" s="227"/>
-      <c r="E23" s="227"/>
-      <c r="F23" s="227"/>
-      <c r="G23" s="227"/>
-      <c r="H23" s="227"/>
-      <c r="I23" s="227"/>
-      <c r="J23" s="227"/>
-      <c r="K23" s="227"/>
-      <c r="L23" s="227"/>
-      <c r="M23" s="227"/>
-      <c r="N23" s="227"/>
-      <c r="O23" s="227"/>
-      <c r="P23" s="227"/>
-      <c r="Q23" s="227"/>
-      <c r="R23" s="227"/>
-      <c r="S23" s="227"/>
-      <c r="T23" s="227"/>
-      <c r="U23" s="227"/>
-      <c r="V23" s="227"/>
-      <c r="W23" s="227"/>
-      <c r="X23" s="227"/>
-      <c r="Y23" s="227"/>
-      <c r="Z23" s="227"/>
+      <c r="C23" s="225"/>
+      <c r="D23" s="225"/>
+      <c r="E23" s="225"/>
+      <c r="F23" s="225"/>
+      <c r="G23" s="225"/>
+      <c r="H23" s="225"/>
+      <c r="I23" s="225"/>
+      <c r="J23" s="225"/>
+      <c r="K23" s="225"/>
+      <c r="L23" s="225"/>
+      <c r="M23" s="225"/>
+      <c r="N23" s="225"/>
+      <c r="O23" s="225"/>
+      <c r="P23" s="225"/>
+      <c r="Q23" s="225"/>
+      <c r="R23" s="225"/>
+      <c r="S23" s="225"/>
+      <c r="T23" s="225"/>
+      <c r="U23" s="225"/>
+      <c r="V23" s="225"/>
+      <c r="W23" s="225"/>
+      <c r="X23" s="225"/>
+      <c r="Y23" s="225"/>
+      <c r="Z23" s="225"/>
     </row>
     <row r="24" spans="1:26" s="83" customFormat="1" ht="22.5" customHeight="1">
       <c r="A24" s="84">
@@ -9538,30 +9523,30 @@
       <c r="B24" s="85" t="s">
         <v>116</v>
       </c>
-      <c r="C24" s="227"/>
-      <c r="D24" s="227"/>
-      <c r="E24" s="227"/>
-      <c r="F24" s="227"/>
-      <c r="G24" s="227"/>
-      <c r="H24" s="227"/>
-      <c r="I24" s="227"/>
-      <c r="J24" s="227"/>
-      <c r="K24" s="227"/>
-      <c r="L24" s="227"/>
-      <c r="M24" s="227"/>
-      <c r="N24" s="227"/>
-      <c r="O24" s="227"/>
-      <c r="P24" s="227"/>
-      <c r="Q24" s="227"/>
-      <c r="R24" s="227"/>
-      <c r="S24" s="227"/>
-      <c r="T24" s="227"/>
-      <c r="U24" s="227"/>
-      <c r="V24" s="227"/>
-      <c r="W24" s="227"/>
-      <c r="X24" s="227"/>
-      <c r="Y24" s="227"/>
-      <c r="Z24" s="227"/>
+      <c r="C24" s="225"/>
+      <c r="D24" s="225"/>
+      <c r="E24" s="225"/>
+      <c r="F24" s="225"/>
+      <c r="G24" s="225"/>
+      <c r="H24" s="225"/>
+      <c r="I24" s="225"/>
+      <c r="J24" s="225"/>
+      <c r="K24" s="225"/>
+      <c r="L24" s="225"/>
+      <c r="M24" s="225"/>
+      <c r="N24" s="225"/>
+      <c r="O24" s="225"/>
+      <c r="P24" s="225"/>
+      <c r="Q24" s="225"/>
+      <c r="R24" s="225"/>
+      <c r="S24" s="225"/>
+      <c r="T24" s="225"/>
+      <c r="U24" s="225"/>
+      <c r="V24" s="225"/>
+      <c r="W24" s="225"/>
+      <c r="X24" s="225"/>
+      <c r="Y24" s="225"/>
+      <c r="Z24" s="225"/>
     </row>
     <row r="25" spans="1:26" s="83" customFormat="1" ht="20.7" customHeight="1">
       <c r="A25" s="84">
@@ -9570,256 +9555,256 @@
       <c r="B25" s="85" t="s">
         <v>227</v>
       </c>
-      <c r="C25" s="227"/>
-      <c r="D25" s="227"/>
-      <c r="E25" s="227"/>
-      <c r="F25" s="227"/>
-      <c r="G25" s="227"/>
-      <c r="H25" s="227"/>
-      <c r="I25" s="227"/>
-      <c r="J25" s="227"/>
-      <c r="K25" s="227"/>
-      <c r="L25" s="227"/>
-      <c r="M25" s="227"/>
-      <c r="N25" s="227"/>
-      <c r="O25" s="227"/>
-      <c r="P25" s="227"/>
-      <c r="Q25" s="227"/>
-      <c r="R25" s="227"/>
-      <c r="S25" s="227"/>
-      <c r="T25" s="227"/>
-      <c r="U25" s="227"/>
-      <c r="V25" s="227"/>
-      <c r="W25" s="227"/>
-      <c r="X25" s="227"/>
-      <c r="Y25" s="227"/>
-      <c r="Z25" s="227"/>
+      <c r="C25" s="225"/>
+      <c r="D25" s="225"/>
+      <c r="E25" s="225"/>
+      <c r="F25" s="225"/>
+      <c r="G25" s="225"/>
+      <c r="H25" s="225"/>
+      <c r="I25" s="225"/>
+      <c r="J25" s="225"/>
+      <c r="K25" s="225"/>
+      <c r="L25" s="225"/>
+      <c r="M25" s="225"/>
+      <c r="N25" s="225"/>
+      <c r="O25" s="225"/>
+      <c r="P25" s="225"/>
+      <c r="Q25" s="225"/>
+      <c r="R25" s="225"/>
+      <c r="S25" s="225"/>
+      <c r="T25" s="225"/>
+      <c r="U25" s="225"/>
+      <c r="V25" s="225"/>
+      <c r="W25" s="225"/>
+      <c r="X25" s="225"/>
+      <c r="Y25" s="225"/>
+      <c r="Z25" s="225"/>
     </row>
     <row r="26" spans="1:26" s="14" customFormat="1" ht="13.8">
       <c r="A26" s="13"/>
-      <c r="C26" s="244"/>
-      <c r="D26" s="244"/>
-      <c r="E26" s="244"/>
-      <c r="F26" s="244"/>
+      <c r="C26" s="242"/>
+      <c r="D26" s="242"/>
+      <c r="E26" s="242"/>
+      <c r="F26" s="242"/>
     </row>
     <row r="27" spans="1:26" s="14" customFormat="1" ht="15.6">
-      <c r="A27" s="262" t="s">
+      <c r="A27" s="260" t="s">
         <v>117</v>
       </c>
-      <c r="B27" s="262"/>
-      <c r="C27" s="262"/>
-      <c r="D27" s="262"/>
-      <c r="E27" s="262"/>
-      <c r="F27" s="262"/>
-      <c r="G27" s="262"/>
-      <c r="H27" s="262"/>
-      <c r="I27" s="262"/>
-      <c r="J27" s="262"/>
+      <c r="B27" s="260"/>
+      <c r="C27" s="260"/>
+      <c r="D27" s="260"/>
+      <c r="E27" s="260"/>
+      <c r="F27" s="260"/>
+      <c r="G27" s="260"/>
+      <c r="H27" s="260"/>
+      <c r="I27" s="260"/>
+      <c r="J27" s="260"/>
     </row>
     <row r="28" spans="1:26" s="87" customFormat="1" ht="15">
-      <c r="A28" s="251" t="s">
+      <c r="A28" s="249" t="s">
         <v>118</v>
       </c>
-      <c r="B28" s="252"/>
-      <c r="C28" s="258" t="s">
+      <c r="B28" s="250"/>
+      <c r="C28" s="256" t="s">
         <v>119</v>
       </c>
-      <c r="D28" s="258"/>
-      <c r="E28" s="258"/>
-      <c r="F28" s="258"/>
-      <c r="G28" s="259" t="s">
+      <c r="D28" s="256"/>
+      <c r="E28" s="256"/>
+      <c r="F28" s="256"/>
+      <c r="G28" s="257" t="s">
         <v>120</v>
       </c>
-      <c r="H28" s="260"/>
-      <c r="I28" s="260"/>
-      <c r="J28" s="261"/>
-      <c r="L28" s="256" t="s">
+      <c r="H28" s="258"/>
+      <c r="I28" s="258"/>
+      <c r="J28" s="259"/>
+      <c r="L28" s="254" t="s">
         <v>16</v>
       </c>
-      <c r="M28" s="256"/>
+      <c r="M28" s="254"/>
     </row>
     <row r="29" spans="1:26" s="87" customFormat="1" ht="15">
-      <c r="A29" s="251" t="s">
+      <c r="A29" s="249" t="s">
         <v>121</v>
       </c>
-      <c r="B29" s="252"/>
-      <c r="C29" s="257">
+      <c r="B29" s="250"/>
+      <c r="C29" s="255">
         <v>10</v>
       </c>
-      <c r="D29" s="257"/>
-      <c r="E29" s="257"/>
-      <c r="F29" s="257"/>
-      <c r="G29" s="257">
+      <c r="D29" s="255"/>
+      <c r="E29" s="255"/>
+      <c r="F29" s="255"/>
+      <c r="G29" s="255">
         <v>10</v>
       </c>
-      <c r="H29" s="257"/>
-      <c r="I29" s="257"/>
-      <c r="J29" s="257"/>
-      <c r="L29" s="256"/>
-      <c r="M29" s="256"/>
+      <c r="H29" s="255"/>
+      <c r="I29" s="255"/>
+      <c r="J29" s="255"/>
+      <c r="L29" s="254"/>
+      <c r="M29" s="254"/>
     </row>
     <row r="30" spans="1:26" s="87" customFormat="1" ht="15">
-      <c r="A30" s="251" t="s">
+      <c r="A30" s="249" t="s">
         <v>122</v>
       </c>
-      <c r="B30" s="252"/>
-      <c r="C30" s="257">
+      <c r="B30" s="250"/>
+      <c r="C30" s="255">
         <v>20</v>
       </c>
-      <c r="D30" s="257"/>
-      <c r="E30" s="257"/>
-      <c r="F30" s="257"/>
-      <c r="G30" s="257">
+      <c r="D30" s="255"/>
+      <c r="E30" s="255"/>
+      <c r="F30" s="255"/>
+      <c r="G30" s="255">
         <v>20</v>
       </c>
-      <c r="H30" s="257"/>
-      <c r="I30" s="257"/>
-      <c r="J30" s="257"/>
-      <c r="L30" s="256"/>
-      <c r="M30" s="256"/>
+      <c r="H30" s="255"/>
+      <c r="I30" s="255"/>
+      <c r="J30" s="255"/>
+      <c r="L30" s="254"/>
+      <c r="M30" s="254"/>
     </row>
     <row r="31" spans="1:26" s="87" customFormat="1" ht="15">
-      <c r="A31" s="251" t="s">
+      <c r="A31" s="249" t="s">
         <v>123</v>
       </c>
-      <c r="B31" s="252"/>
-      <c r="C31" s="257">
+      <c r="B31" s="250"/>
+      <c r="C31" s="255">
         <v>30</v>
       </c>
-      <c r="D31" s="257"/>
-      <c r="E31" s="257"/>
-      <c r="F31" s="257"/>
-      <c r="G31" s="257">
+      <c r="D31" s="255"/>
+      <c r="E31" s="255"/>
+      <c r="F31" s="255"/>
+      <c r="G31" s="255">
         <v>30</v>
       </c>
-      <c r="H31" s="257"/>
-      <c r="I31" s="257"/>
-      <c r="J31" s="257"/>
-      <c r="L31" s="256"/>
-      <c r="M31" s="256"/>
+      <c r="H31" s="255"/>
+      <c r="I31" s="255"/>
+      <c r="J31" s="255"/>
+      <c r="L31" s="254"/>
+      <c r="M31" s="254"/>
     </row>
     <row r="32" spans="1:26" s="87" customFormat="1" ht="15">
-      <c r="A32" s="251" t="s">
+      <c r="A32" s="249" t="s">
         <v>124</v>
       </c>
-      <c r="B32" s="252"/>
-      <c r="C32" s="253">
+      <c r="B32" s="250"/>
+      <c r="C32" s="251">
         <v>40</v>
       </c>
-      <c r="D32" s="254"/>
-      <c r="E32" s="254"/>
-      <c r="F32" s="255"/>
-      <c r="G32" s="253">
+      <c r="D32" s="252"/>
+      <c r="E32" s="252"/>
+      <c r="F32" s="253"/>
+      <c r="G32" s="251">
         <v>40</v>
       </c>
-      <c r="H32" s="254"/>
-      <c r="I32" s="254"/>
-      <c r="J32" s="255"/>
-      <c r="L32" s="256"/>
-      <c r="M32" s="256"/>
+      <c r="H32" s="252"/>
+      <c r="I32" s="252"/>
+      <c r="J32" s="253"/>
+      <c r="L32" s="254"/>
+      <c r="M32" s="254"/>
     </row>
     <row r="33" spans="1:26" s="87" customFormat="1" ht="15">
-      <c r="A33" s="251" t="s">
+      <c r="A33" s="249" t="s">
         <v>125</v>
       </c>
-      <c r="B33" s="252"/>
-      <c r="C33" s="257">
+      <c r="B33" s="250"/>
+      <c r="C33" s="255">
         <v>50</v>
       </c>
-      <c r="D33" s="257"/>
-      <c r="E33" s="257"/>
-      <c r="F33" s="257"/>
-      <c r="G33" s="257">
+      <c r="D33" s="255"/>
+      <c r="E33" s="255"/>
+      <c r="F33" s="255"/>
+      <c r="G33" s="255">
         <v>50</v>
       </c>
-      <c r="H33" s="257"/>
-      <c r="I33" s="257"/>
-      <c r="J33" s="257"/>
-      <c r="L33" s="256"/>
-      <c r="M33" s="256"/>
+      <c r="H33" s="255"/>
+      <c r="I33" s="255"/>
+      <c r="J33" s="255"/>
+      <c r="L33" s="254"/>
+      <c r="M33" s="254"/>
     </row>
     <row r="34" spans="1:26" s="87" customFormat="1" ht="15">
-      <c r="A34" s="251" t="s">
+      <c r="A34" s="249" t="s">
         <v>126</v>
       </c>
-      <c r="B34" s="252"/>
-      <c r="C34" s="257">
+      <c r="B34" s="250"/>
+      <c r="C34" s="255">
         <v>100</v>
       </c>
-      <c r="D34" s="257"/>
-      <c r="E34" s="257"/>
-      <c r="F34" s="257"/>
-      <c r="G34" s="257">
+      <c r="D34" s="255"/>
+      <c r="E34" s="255"/>
+      <c r="F34" s="255"/>
+      <c r="G34" s="255">
         <v>100</v>
       </c>
-      <c r="H34" s="257"/>
-      <c r="I34" s="257"/>
-      <c r="J34" s="257"/>
-      <c r="L34" s="256"/>
-      <c r="M34" s="256"/>
+      <c r="H34" s="255"/>
+      <c r="I34" s="255"/>
+      <c r="J34" s="255"/>
+      <c r="L34" s="254"/>
+      <c r="M34" s="254"/>
     </row>
     <row r="35" spans="1:26" s="87" customFormat="1" ht="15">
-      <c r="A35" s="251" t="s">
+      <c r="A35" s="249" t="s">
         <v>127</v>
       </c>
-      <c r="B35" s="252"/>
-      <c r="C35" s="257">
+      <c r="B35" s="250"/>
+      <c r="C35" s="255">
         <v>200</v>
       </c>
-      <c r="D35" s="257"/>
-      <c r="E35" s="257"/>
-      <c r="F35" s="257"/>
-      <c r="G35" s="257">
+      <c r="D35" s="255"/>
+      <c r="E35" s="255"/>
+      <c r="F35" s="255"/>
+      <c r="G35" s="255">
         <v>200</v>
       </c>
-      <c r="H35" s="257"/>
-      <c r="I35" s="257"/>
-      <c r="J35" s="257"/>
-      <c r="L35" s="256"/>
-      <c r="M35" s="256"/>
+      <c r="H35" s="255"/>
+      <c r="I35" s="255"/>
+      <c r="J35" s="255"/>
+      <c r="L35" s="254"/>
+      <c r="M35" s="254"/>
     </row>
     <row r="36" spans="1:26" s="87" customFormat="1" ht="15">
-      <c r="A36" s="251" t="s">
+      <c r="A36" s="249" t="s">
         <v>128</v>
       </c>
-      <c r="B36" s="252"/>
-      <c r="C36" s="253" t="s">
+      <c r="B36" s="250"/>
+      <c r="C36" s="251" t="s">
         <v>129</v>
       </c>
-      <c r="D36" s="254"/>
-      <c r="E36" s="254"/>
-      <c r="F36" s="254"/>
-      <c r="G36" s="254"/>
-      <c r="H36" s="254"/>
-      <c r="I36" s="254"/>
-      <c r="J36" s="255"/>
-      <c r="L36" s="256"/>
-      <c r="M36" s="256"/>
+      <c r="D36" s="252"/>
+      <c r="E36" s="252"/>
+      <c r="F36" s="252"/>
+      <c r="G36" s="252"/>
+      <c r="H36" s="252"/>
+      <c r="I36" s="252"/>
+      <c r="J36" s="253"/>
+      <c r="L36" s="254"/>
+      <c r="M36" s="254"/>
     </row>
     <row r="37" spans="1:26" s="87" customFormat="1" ht="15">
       <c r="A37" s="88"/>
-      <c r="L37" s="256"/>
-      <c r="M37" s="256"/>
+      <c r="L37" s="254"/>
+      <c r="M37" s="254"/>
     </row>
     <row r="38" spans="1:26" s="87" customFormat="1" ht="15">
       <c r="A38" s="88"/>
-      <c r="L38" s="256"/>
-      <c r="M38" s="256"/>
+      <c r="L38" s="254"/>
+      <c r="M38" s="254"/>
     </row>
     <row r="39" spans="1:26" s="14" customFormat="1" ht="13.8">
       <c r="A39" s="13"/>
-      <c r="L39" s="244"/>
-      <c r="M39" s="244"/>
+      <c r="L39" s="242"/>
+      <c r="M39" s="242"/>
     </row>
     <row r="40" spans="1:26" s="14" customFormat="1" ht="13.8">
       <c r="A40" s="13"/>
-      <c r="L40" s="244"/>
-      <c r="M40" s="244"/>
+      <c r="L40" s="242"/>
+      <c r="M40" s="242"/>
     </row>
     <row r="41" spans="1:26" s="14" customFormat="1" ht="13.8">
       <c r="A41" s="13"/>
-      <c r="L41" s="244"/>
-      <c r="M41" s="244"/>
+      <c r="L41" s="242"/>
+      <c r="M41" s="242"/>
     </row>
     <row r="42" spans="1:26" s="87" customFormat="1" ht="19.2" customHeight="1">
       <c r="A42" s="26" t="s">
@@ -9828,654 +9813,654 @@
       <c r="B42" s="29" t="s">
         <v>131</v>
       </c>
-      <c r="C42" s="245" t="s">
+      <c r="C42" s="243" t="s">
         <v>132</v>
       </c>
-      <c r="D42" s="246"/>
-      <c r="E42" s="246"/>
-      <c r="F42" s="246"/>
-      <c r="G42" s="246"/>
-      <c r="H42" s="246"/>
-      <c r="I42" s="246"/>
-      <c r="J42" s="246"/>
-      <c r="K42" s="246"/>
-      <c r="L42" s="246"/>
-      <c r="M42" s="246"/>
-      <c r="N42" s="247"/>
-      <c r="O42" s="248" t="s">
+      <c r="D42" s="244"/>
+      <c r="E42" s="244"/>
+      <c r="F42" s="244"/>
+      <c r="G42" s="244"/>
+      <c r="H42" s="244"/>
+      <c r="I42" s="244"/>
+      <c r="J42" s="244"/>
+      <c r="K42" s="244"/>
+      <c r="L42" s="244"/>
+      <c r="M42" s="244"/>
+      <c r="N42" s="245"/>
+      <c r="O42" s="246" t="s">
         <v>133</v>
       </c>
-      <c r="P42" s="249"/>
-      <c r="Q42" s="249"/>
-      <c r="R42" s="249"/>
-      <c r="S42" s="250"/>
-      <c r="T42" s="248" t="s">
+      <c r="P42" s="247"/>
+      <c r="Q42" s="247"/>
+      <c r="R42" s="247"/>
+      <c r="S42" s="248"/>
+      <c r="T42" s="246" t="s">
         <v>134</v>
       </c>
-      <c r="U42" s="249"/>
-      <c r="V42" s="249"/>
-      <c r="W42" s="250"/>
-      <c r="X42" s="249" t="s">
+      <c r="U42" s="247"/>
+      <c r="V42" s="247"/>
+      <c r="W42" s="248"/>
+      <c r="X42" s="247" t="s">
         <v>135</v>
       </c>
-      <c r="Y42" s="249"/>
-      <c r="Z42" s="250"/>
+      <c r="Y42" s="247"/>
+      <c r="Z42" s="248"/>
     </row>
     <row r="43" spans="1:26" s="14" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A43" s="219" t="s">
+      <c r="A43" s="217" t="s">
         <v>229</v>
       </c>
       <c r="B43" s="26" t="s">
         <v>136</v>
       </c>
-      <c r="C43" s="228" t="s">
+      <c r="C43" s="226" t="s">
         <v>137</v>
       </c>
-      <c r="D43" s="229"/>
-      <c r="E43" s="229"/>
-      <c r="F43" s="229"/>
-      <c r="G43" s="229"/>
-      <c r="H43" s="229"/>
-      <c r="I43" s="229"/>
-      <c r="J43" s="229"/>
-      <c r="K43" s="229"/>
-      <c r="L43" s="229"/>
-      <c r="M43" s="229"/>
-      <c r="N43" s="230"/>
-      <c r="O43" s="231" t="s">
+      <c r="D43" s="227"/>
+      <c r="E43" s="227"/>
+      <c r="F43" s="227"/>
+      <c r="G43" s="227"/>
+      <c r="H43" s="227"/>
+      <c r="I43" s="227"/>
+      <c r="J43" s="227"/>
+      <c r="K43" s="227"/>
+      <c r="L43" s="227"/>
+      <c r="M43" s="227"/>
+      <c r="N43" s="228"/>
+      <c r="O43" s="229" t="s">
         <v>1</v>
       </c>
-      <c r="P43" s="232"/>
-      <c r="Q43" s="232"/>
-      <c r="R43" s="232"/>
-      <c r="S43" s="233"/>
-      <c r="T43" s="231" t="s">
+      <c r="P43" s="230"/>
+      <c r="Q43" s="230"/>
+      <c r="R43" s="230"/>
+      <c r="S43" s="231"/>
+      <c r="T43" s="229" t="s">
         <v>7</v>
       </c>
-      <c r="U43" s="232"/>
-      <c r="V43" s="232"/>
-      <c r="W43" s="233"/>
-      <c r="X43" s="231">
+      <c r="U43" s="230"/>
+      <c r="V43" s="230"/>
+      <c r="W43" s="231"/>
+      <c r="X43" s="229">
         <v>1</v>
       </c>
-      <c r="Y43" s="232"/>
-      <c r="Z43" s="233"/>
+      <c r="Y43" s="230"/>
+      <c r="Z43" s="231"/>
     </row>
     <row r="44" spans="1:26" s="14" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A44" s="220"/>
+      <c r="A44" s="218"/>
       <c r="B44" s="26" t="s">
         <v>138</v>
       </c>
-      <c r="C44" s="228" t="s">
+      <c r="C44" s="226" t="s">
         <v>139</v>
       </c>
-      <c r="D44" s="229"/>
-      <c r="E44" s="229"/>
-      <c r="F44" s="229"/>
-      <c r="G44" s="229"/>
-      <c r="H44" s="229"/>
-      <c r="I44" s="229"/>
-      <c r="J44" s="229"/>
-      <c r="K44" s="229"/>
-      <c r="L44" s="229"/>
-      <c r="M44" s="229"/>
-      <c r="N44" s="230"/>
-      <c r="O44" s="231" t="s">
+      <c r="D44" s="227"/>
+      <c r="E44" s="227"/>
+      <c r="F44" s="227"/>
+      <c r="G44" s="227"/>
+      <c r="H44" s="227"/>
+      <c r="I44" s="227"/>
+      <c r="J44" s="227"/>
+      <c r="K44" s="227"/>
+      <c r="L44" s="227"/>
+      <c r="M44" s="227"/>
+      <c r="N44" s="228"/>
+      <c r="O44" s="229" t="s">
         <v>1</v>
       </c>
-      <c r="P44" s="232"/>
-      <c r="Q44" s="232"/>
-      <c r="R44" s="232"/>
-      <c r="S44" s="233"/>
-      <c r="T44" s="231" t="s">
+      <c r="P44" s="230"/>
+      <c r="Q44" s="230"/>
+      <c r="R44" s="230"/>
+      <c r="S44" s="231"/>
+      <c r="T44" s="229" t="s">
         <v>9</v>
       </c>
-      <c r="U44" s="232"/>
-      <c r="V44" s="232"/>
-      <c r="W44" s="233"/>
-      <c r="X44" s="231">
+      <c r="U44" s="230"/>
+      <c r="V44" s="230"/>
+      <c r="W44" s="231"/>
+      <c r="X44" s="229">
         <v>1</v>
       </c>
-      <c r="Y44" s="232"/>
-      <c r="Z44" s="233"/>
+      <c r="Y44" s="230"/>
+      <c r="Z44" s="231"/>
     </row>
     <row r="45" spans="1:26" s="14" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A45" s="220"/>
+      <c r="A45" s="218"/>
       <c r="B45" s="26" t="s">
         <v>140</v>
       </c>
-      <c r="C45" s="228" t="s">
+      <c r="C45" s="226" t="s">
         <v>141</v>
       </c>
-      <c r="D45" s="229"/>
-      <c r="E45" s="229"/>
-      <c r="F45" s="229"/>
-      <c r="G45" s="229"/>
-      <c r="H45" s="229"/>
-      <c r="I45" s="229"/>
-      <c r="J45" s="229"/>
-      <c r="K45" s="229"/>
-      <c r="L45" s="229"/>
-      <c r="M45" s="229"/>
-      <c r="N45" s="230"/>
-      <c r="O45" s="231" t="s">
+      <c r="D45" s="227"/>
+      <c r="E45" s="227"/>
+      <c r="F45" s="227"/>
+      <c r="G45" s="227"/>
+      <c r="H45" s="227"/>
+      <c r="I45" s="227"/>
+      <c r="J45" s="227"/>
+      <c r="K45" s="227"/>
+      <c r="L45" s="227"/>
+      <c r="M45" s="227"/>
+      <c r="N45" s="228"/>
+      <c r="O45" s="229" t="s">
         <v>2</v>
       </c>
-      <c r="P45" s="232"/>
-      <c r="Q45" s="232"/>
-      <c r="R45" s="232"/>
-      <c r="S45" s="233"/>
-      <c r="T45" s="231" t="s">
+      <c r="P45" s="230"/>
+      <c r="Q45" s="230"/>
+      <c r="R45" s="230"/>
+      <c r="S45" s="231"/>
+      <c r="T45" s="229" t="s">
         <v>10</v>
       </c>
-      <c r="U45" s="232"/>
-      <c r="V45" s="232"/>
-      <c r="W45" s="233"/>
-      <c r="X45" s="231">
+      <c r="U45" s="230"/>
+      <c r="V45" s="230"/>
+      <c r="W45" s="231"/>
+      <c r="X45" s="229">
         <v>6</v>
       </c>
-      <c r="Y45" s="232"/>
-      <c r="Z45" s="233"/>
+      <c r="Y45" s="230"/>
+      <c r="Z45" s="231"/>
     </row>
     <row r="46" spans="1:26" s="14" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A46" s="220"/>
+      <c r="A46" s="218"/>
       <c r="B46" s="26" t="s">
         <v>142</v>
       </c>
-      <c r="C46" s="228" t="s">
+      <c r="C46" s="226" t="s">
         <v>143</v>
       </c>
-      <c r="D46" s="229"/>
-      <c r="E46" s="229"/>
-      <c r="F46" s="229"/>
-      <c r="G46" s="229"/>
-      <c r="H46" s="229"/>
-      <c r="I46" s="229"/>
-      <c r="J46" s="229"/>
-      <c r="K46" s="229"/>
-      <c r="L46" s="229"/>
-      <c r="M46" s="229"/>
-      <c r="N46" s="230"/>
-      <c r="O46" s="231" t="s">
+      <c r="D46" s="227"/>
+      <c r="E46" s="227"/>
+      <c r="F46" s="227"/>
+      <c r="G46" s="227"/>
+      <c r="H46" s="227"/>
+      <c r="I46" s="227"/>
+      <c r="J46" s="227"/>
+      <c r="K46" s="227"/>
+      <c r="L46" s="227"/>
+      <c r="M46" s="227"/>
+      <c r="N46" s="228"/>
+      <c r="O46" s="229" t="s">
         <v>0</v>
       </c>
-      <c r="P46" s="232"/>
-      <c r="Q46" s="232"/>
-      <c r="R46" s="232"/>
-      <c r="S46" s="233"/>
-      <c r="T46" s="231" t="s">
+      <c r="P46" s="230"/>
+      <c r="Q46" s="230"/>
+      <c r="R46" s="230"/>
+      <c r="S46" s="231"/>
+      <c r="T46" s="229" t="s">
         <v>12</v>
       </c>
-      <c r="U46" s="232"/>
-      <c r="V46" s="232"/>
-      <c r="W46" s="233"/>
-      <c r="X46" s="231">
+      <c r="U46" s="230"/>
+      <c r="V46" s="230"/>
+      <c r="W46" s="231"/>
+      <c r="X46" s="229">
         <v>6</v>
       </c>
-      <c r="Y46" s="232"/>
-      <c r="Z46" s="233"/>
+      <c r="Y46" s="230"/>
+      <c r="Z46" s="231"/>
     </row>
     <row r="47" spans="1:26" s="14" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A47" s="221"/>
+      <c r="A47" s="219"/>
       <c r="B47" s="26" t="s">
         <v>144</v>
       </c>
-      <c r="C47" s="228" t="s">
+      <c r="C47" s="226" t="s">
         <v>145</v>
       </c>
-      <c r="D47" s="229"/>
-      <c r="E47" s="229"/>
-      <c r="F47" s="229"/>
-      <c r="G47" s="229"/>
-      <c r="H47" s="229"/>
-      <c r="I47" s="229"/>
-      <c r="J47" s="229"/>
-      <c r="K47" s="229"/>
-      <c r="L47" s="229"/>
-      <c r="M47" s="229"/>
-      <c r="N47" s="230"/>
-      <c r="O47" s="231" t="s">
+      <c r="D47" s="227"/>
+      <c r="E47" s="227"/>
+      <c r="F47" s="227"/>
+      <c r="G47" s="227"/>
+      <c r="H47" s="227"/>
+      <c r="I47" s="227"/>
+      <c r="J47" s="227"/>
+      <c r="K47" s="227"/>
+      <c r="L47" s="227"/>
+      <c r="M47" s="227"/>
+      <c r="N47" s="228"/>
+      <c r="O47" s="229" t="s">
         <v>0</v>
       </c>
-      <c r="P47" s="232"/>
-      <c r="Q47" s="232"/>
-      <c r="R47" s="232"/>
-      <c r="S47" s="233"/>
-      <c r="T47" s="231" t="s">
+      <c r="P47" s="230"/>
+      <c r="Q47" s="230"/>
+      <c r="R47" s="230"/>
+      <c r="S47" s="231"/>
+      <c r="T47" s="229" t="s">
         <v>14</v>
       </c>
-      <c r="U47" s="232"/>
-      <c r="V47" s="232"/>
-      <c r="W47" s="233"/>
-      <c r="X47" s="231">
+      <c r="U47" s="230"/>
+      <c r="V47" s="230"/>
+      <c r="W47" s="231"/>
+      <c r="X47" s="229">
         <v>6</v>
       </c>
-      <c r="Y47" s="232"/>
-      <c r="Z47" s="233"/>
+      <c r="Y47" s="230"/>
+      <c r="Z47" s="231"/>
     </row>
     <row r="48" spans="1:26" s="14" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A48" s="222" t="s">
+      <c r="A48" s="220" t="s">
         <v>230</v>
       </c>
       <c r="B48" s="26" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="228" t="s">
+      <c r="C48" s="226" t="s">
         <v>147</v>
       </c>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="229"/>
-      <c r="I48" s="229"/>
-      <c r="J48" s="229"/>
-      <c r="K48" s="229"/>
-      <c r="L48" s="229"/>
-      <c r="M48" s="229"/>
-      <c r="N48" s="230"/>
-      <c r="O48" s="231" t="s">
+      <c r="D48" s="227"/>
+      <c r="E48" s="227"/>
+      <c r="F48" s="227"/>
+      <c r="G48" s="227"/>
+      <c r="H48" s="227"/>
+      <c r="I48" s="227"/>
+      <c r="J48" s="227"/>
+      <c r="K48" s="227"/>
+      <c r="L48" s="227"/>
+      <c r="M48" s="227"/>
+      <c r="N48" s="228"/>
+      <c r="O48" s="229" t="s">
         <v>148</v>
       </c>
-      <c r="P48" s="232"/>
-      <c r="Q48" s="232"/>
-      <c r="R48" s="232"/>
-      <c r="S48" s="233"/>
-      <c r="T48" s="231" t="s">
+      <c r="P48" s="230"/>
+      <c r="Q48" s="230"/>
+      <c r="R48" s="230"/>
+      <c r="S48" s="231"/>
+      <c r="T48" s="229" t="s">
         <v>149</v>
       </c>
-      <c r="U48" s="232"/>
-      <c r="V48" s="232"/>
-      <c r="W48" s="233"/>
-      <c r="X48" s="231">
+      <c r="U48" s="230"/>
+      <c r="V48" s="230"/>
+      <c r="W48" s="231"/>
+      <c r="X48" s="229">
         <v>2</v>
       </c>
-      <c r="Y48" s="232"/>
-      <c r="Z48" s="233"/>
+      <c r="Y48" s="230"/>
+      <c r="Z48" s="231"/>
     </row>
     <row r="49" spans="1:26" s="14" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A49" s="148"/>
+      <c r="A49" s="146"/>
       <c r="B49" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="C49" s="228" t="s">
+      <c r="C49" s="226" t="s">
         <v>151</v>
       </c>
-      <c r="D49" s="229"/>
-      <c r="E49" s="229"/>
-      <c r="F49" s="229"/>
-      <c r="G49" s="229"/>
-      <c r="H49" s="229"/>
-      <c r="I49" s="229"/>
-      <c r="J49" s="229"/>
-      <c r="K49" s="229"/>
-      <c r="L49" s="229"/>
-      <c r="M49" s="229"/>
-      <c r="N49" s="230"/>
-      <c r="O49" s="231" t="s">
+      <c r="D49" s="227"/>
+      <c r="E49" s="227"/>
+      <c r="F49" s="227"/>
+      <c r="G49" s="227"/>
+      <c r="H49" s="227"/>
+      <c r="I49" s="227"/>
+      <c r="J49" s="227"/>
+      <c r="K49" s="227"/>
+      <c r="L49" s="227"/>
+      <c r="M49" s="227"/>
+      <c r="N49" s="228"/>
+      <c r="O49" s="229" t="s">
         <v>152</v>
       </c>
-      <c r="P49" s="232"/>
-      <c r="Q49" s="232"/>
-      <c r="R49" s="232"/>
-      <c r="S49" s="233"/>
-      <c r="T49" s="231" t="s">
+      <c r="P49" s="230"/>
+      <c r="Q49" s="230"/>
+      <c r="R49" s="230"/>
+      <c r="S49" s="231"/>
+      <c r="T49" s="229" t="s">
         <v>153</v>
       </c>
-      <c r="U49" s="232"/>
-      <c r="V49" s="232"/>
-      <c r="W49" s="233"/>
-      <c r="X49" s="231">
+      <c r="U49" s="230"/>
+      <c r="V49" s="230"/>
+      <c r="W49" s="231"/>
+      <c r="X49" s="229">
         <v>1</v>
       </c>
-      <c r="Y49" s="232"/>
-      <c r="Z49" s="233"/>
+      <c r="Y49" s="230"/>
+      <c r="Z49" s="231"/>
     </row>
     <row r="50" spans="1:26" s="14" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A50" s="222" t="s">
+      <c r="A50" s="220" t="s">
         <v>231</v>
       </c>
       <c r="B50" s="26" t="s">
         <v>154</v>
       </c>
-      <c r="C50" s="228" t="s">
+      <c r="C50" s="226" t="s">
         <v>155</v>
       </c>
-      <c r="D50" s="229"/>
-      <c r="E50" s="229"/>
-      <c r="F50" s="229"/>
-      <c r="G50" s="229"/>
-      <c r="H50" s="229"/>
-      <c r="I50" s="229"/>
-      <c r="J50" s="229"/>
-      <c r="K50" s="229"/>
-      <c r="L50" s="229"/>
-      <c r="M50" s="229"/>
-      <c r="N50" s="230"/>
-      <c r="O50" s="231" t="s">
+      <c r="D50" s="227"/>
+      <c r="E50" s="227"/>
+      <c r="F50" s="227"/>
+      <c r="G50" s="227"/>
+      <c r="H50" s="227"/>
+      <c r="I50" s="227"/>
+      <c r="J50" s="227"/>
+      <c r="K50" s="227"/>
+      <c r="L50" s="227"/>
+      <c r="M50" s="227"/>
+      <c r="N50" s="228"/>
+      <c r="O50" s="229" t="s">
         <v>156</v>
       </c>
-      <c r="P50" s="232"/>
-      <c r="Q50" s="232"/>
-      <c r="R50" s="232"/>
-      <c r="S50" s="233"/>
-      <c r="T50" s="231" t="s">
+      <c r="P50" s="230"/>
+      <c r="Q50" s="230"/>
+      <c r="R50" s="230"/>
+      <c r="S50" s="231"/>
+      <c r="T50" s="229" t="s">
         <v>157</v>
       </c>
-      <c r="U50" s="232"/>
-      <c r="V50" s="232"/>
-      <c r="W50" s="233"/>
-      <c r="X50" s="231">
+      <c r="U50" s="230"/>
+      <c r="V50" s="230"/>
+      <c r="W50" s="231"/>
+      <c r="X50" s="229">
         <v>1</v>
       </c>
-      <c r="Y50" s="232"/>
-      <c r="Z50" s="233"/>
+      <c r="Y50" s="230"/>
+      <c r="Z50" s="231"/>
     </row>
     <row r="51" spans="1:26" s="14" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A51" s="147"/>
+      <c r="A51" s="145"/>
       <c r="B51" s="26" t="s">
         <v>158</v>
       </c>
-      <c r="C51" s="228" t="s">
+      <c r="C51" s="226" t="s">
         <v>159</v>
       </c>
-      <c r="D51" s="229"/>
-      <c r="E51" s="229"/>
-      <c r="F51" s="229"/>
-      <c r="G51" s="229"/>
-      <c r="H51" s="229"/>
-      <c r="I51" s="229"/>
-      <c r="J51" s="229"/>
-      <c r="K51" s="229"/>
-      <c r="L51" s="229"/>
-      <c r="M51" s="229"/>
-      <c r="N51" s="230"/>
-      <c r="O51" s="231" t="s">
+      <c r="D51" s="227"/>
+      <c r="E51" s="227"/>
+      <c r="F51" s="227"/>
+      <c r="G51" s="227"/>
+      <c r="H51" s="227"/>
+      <c r="I51" s="227"/>
+      <c r="J51" s="227"/>
+      <c r="K51" s="227"/>
+      <c r="L51" s="227"/>
+      <c r="M51" s="227"/>
+      <c r="N51" s="228"/>
+      <c r="O51" s="229" t="s">
         <v>156</v>
       </c>
-      <c r="P51" s="232"/>
-      <c r="Q51" s="232"/>
-      <c r="R51" s="232"/>
-      <c r="S51" s="233"/>
-      <c r="T51" s="231" t="s">
+      <c r="P51" s="230"/>
+      <c r="Q51" s="230"/>
+      <c r="R51" s="230"/>
+      <c r="S51" s="231"/>
+      <c r="T51" s="229" t="s">
         <v>160</v>
       </c>
-      <c r="U51" s="232"/>
-      <c r="V51" s="232"/>
-      <c r="W51" s="233"/>
-      <c r="X51" s="231">
+      <c r="U51" s="230"/>
+      <c r="V51" s="230"/>
+      <c r="W51" s="231"/>
+      <c r="X51" s="229">
         <v>4</v>
       </c>
-      <c r="Y51" s="232"/>
-      <c r="Z51" s="233"/>
+      <c r="Y51" s="230"/>
+      <c r="Z51" s="231"/>
     </row>
     <row r="52" spans="1:26" s="14" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A52" s="147"/>
+      <c r="A52" s="145"/>
       <c r="B52" s="26" t="s">
         <v>161</v>
       </c>
-      <c r="C52" s="228" t="s">
+      <c r="C52" s="226" t="s">
         <v>162</v>
       </c>
-      <c r="D52" s="229"/>
-      <c r="E52" s="229"/>
-      <c r="F52" s="229"/>
-      <c r="G52" s="229"/>
-      <c r="H52" s="229"/>
-      <c r="I52" s="229"/>
-      <c r="J52" s="229"/>
-      <c r="K52" s="229"/>
-      <c r="L52" s="229"/>
-      <c r="M52" s="229"/>
-      <c r="N52" s="230"/>
-      <c r="O52" s="231" t="s">
+      <c r="D52" s="227"/>
+      <c r="E52" s="227"/>
+      <c r="F52" s="227"/>
+      <c r="G52" s="227"/>
+      <c r="H52" s="227"/>
+      <c r="I52" s="227"/>
+      <c r="J52" s="227"/>
+      <c r="K52" s="227"/>
+      <c r="L52" s="227"/>
+      <c r="M52" s="227"/>
+      <c r="N52" s="228"/>
+      <c r="O52" s="229" t="s">
         <v>1</v>
       </c>
-      <c r="P52" s="232"/>
-      <c r="Q52" s="232"/>
-      <c r="R52" s="232"/>
-      <c r="S52" s="233"/>
-      <c r="T52" s="231" t="s">
+      <c r="P52" s="230"/>
+      <c r="Q52" s="230"/>
+      <c r="R52" s="230"/>
+      <c r="S52" s="231"/>
+      <c r="T52" s="229" t="s">
         <v>163</v>
       </c>
-      <c r="U52" s="232"/>
-      <c r="V52" s="232"/>
-      <c r="W52" s="233"/>
-      <c r="X52" s="231">
+      <c r="U52" s="230"/>
+      <c r="V52" s="230"/>
+      <c r="W52" s="231"/>
+      <c r="X52" s="229">
         <v>1</v>
       </c>
-      <c r="Y52" s="232"/>
-      <c r="Z52" s="233"/>
+      <c r="Y52" s="230"/>
+      <c r="Z52" s="231"/>
     </row>
     <row r="53" spans="1:26" s="14" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A53" s="148"/>
+      <c r="A53" s="146"/>
       <c r="B53" s="26" t="s">
         <v>164</v>
       </c>
-      <c r="C53" s="228" t="s">
+      <c r="C53" s="226" t="s">
         <v>165</v>
       </c>
-      <c r="D53" s="229"/>
-      <c r="E53" s="229"/>
-      <c r="F53" s="229"/>
-      <c r="G53" s="229"/>
-      <c r="H53" s="229"/>
-      <c r="I53" s="229"/>
-      <c r="J53" s="229"/>
-      <c r="K53" s="229"/>
-      <c r="L53" s="229"/>
-      <c r="M53" s="229"/>
-      <c r="N53" s="230"/>
-      <c r="O53" s="231" t="s">
+      <c r="D53" s="227"/>
+      <c r="E53" s="227"/>
+      <c r="F53" s="227"/>
+      <c r="G53" s="227"/>
+      <c r="H53" s="227"/>
+      <c r="I53" s="227"/>
+      <c r="J53" s="227"/>
+      <c r="K53" s="227"/>
+      <c r="L53" s="227"/>
+      <c r="M53" s="227"/>
+      <c r="N53" s="228"/>
+      <c r="O53" s="229" t="s">
         <v>1</v>
       </c>
-      <c r="P53" s="232"/>
-      <c r="Q53" s="232"/>
-      <c r="R53" s="232"/>
-      <c r="S53" s="233"/>
-      <c r="T53" s="231" t="s">
+      <c r="P53" s="230"/>
+      <c r="Q53" s="230"/>
+      <c r="R53" s="230"/>
+      <c r="S53" s="231"/>
+      <c r="T53" s="229" t="s">
         <v>166</v>
       </c>
-      <c r="U53" s="232"/>
-      <c r="V53" s="232"/>
-      <c r="W53" s="233"/>
-      <c r="X53" s="231">
+      <c r="U53" s="230"/>
+      <c r="V53" s="230"/>
+      <c r="W53" s="231"/>
+      <c r="X53" s="229">
         <v>1</v>
       </c>
-      <c r="Y53" s="232"/>
-      <c r="Z53" s="233"/>
+      <c r="Y53" s="230"/>
+      <c r="Z53" s="231"/>
     </row>
     <row r="54" spans="1:26" s="14" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A54" s="223" t="s">
+      <c r="A54" s="221" t="s">
         <v>232</v>
       </c>
       <c r="B54" s="26" t="s">
         <v>167</v>
       </c>
-      <c r="C54" s="228" t="s">
+      <c r="C54" s="226" t="s">
         <v>168</v>
       </c>
-      <c r="D54" s="229"/>
-      <c r="E54" s="229"/>
-      <c r="F54" s="229"/>
-      <c r="G54" s="229"/>
-      <c r="H54" s="229"/>
-      <c r="I54" s="229"/>
-      <c r="J54" s="229"/>
-      <c r="K54" s="229"/>
-      <c r="L54" s="229"/>
-      <c r="M54" s="229"/>
-      <c r="N54" s="230"/>
-      <c r="O54" s="231" t="s">
+      <c r="D54" s="227"/>
+      <c r="E54" s="227"/>
+      <c r="F54" s="227"/>
+      <c r="G54" s="227"/>
+      <c r="H54" s="227"/>
+      <c r="I54" s="227"/>
+      <c r="J54" s="227"/>
+      <c r="K54" s="227"/>
+      <c r="L54" s="227"/>
+      <c r="M54" s="227"/>
+      <c r="N54" s="228"/>
+      <c r="O54" s="229" t="s">
         <v>169</v>
       </c>
-      <c r="P54" s="232"/>
-      <c r="Q54" s="232"/>
-      <c r="R54" s="232"/>
-      <c r="S54" s="233"/>
-      <c r="T54" s="231" t="s">
+      <c r="P54" s="230"/>
+      <c r="Q54" s="230"/>
+      <c r="R54" s="230"/>
+      <c r="S54" s="231"/>
+      <c r="T54" s="229" t="s">
         <v>170</v>
       </c>
-      <c r="U54" s="232"/>
-      <c r="V54" s="232"/>
-      <c r="W54" s="233"/>
-      <c r="X54" s="231">
+      <c r="U54" s="230"/>
+      <c r="V54" s="230"/>
+      <c r="W54" s="231"/>
+      <c r="X54" s="229">
         <v>1</v>
       </c>
-      <c r="Y54" s="232"/>
-      <c r="Z54" s="233"/>
+      <c r="Y54" s="230"/>
+      <c r="Z54" s="231"/>
     </row>
     <row r="55" spans="1:26" s="14" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A55" s="224"/>
+      <c r="A55" s="222"/>
       <c r="B55" s="26" t="s">
         <v>171</v>
       </c>
-      <c r="C55" s="228" t="s">
+      <c r="C55" s="226" t="s">
         <v>172</v>
       </c>
-      <c r="D55" s="229"/>
-      <c r="E55" s="229"/>
-      <c r="F55" s="229"/>
-      <c r="G55" s="229"/>
-      <c r="H55" s="229"/>
-      <c r="I55" s="229"/>
-      <c r="J55" s="229"/>
-      <c r="K55" s="229"/>
-      <c r="L55" s="229"/>
-      <c r="M55" s="229"/>
-      <c r="N55" s="230"/>
-      <c r="O55" s="231" t="s">
+      <c r="D55" s="227"/>
+      <c r="E55" s="227"/>
+      <c r="F55" s="227"/>
+      <c r="G55" s="227"/>
+      <c r="H55" s="227"/>
+      <c r="I55" s="227"/>
+      <c r="J55" s="227"/>
+      <c r="K55" s="227"/>
+      <c r="L55" s="227"/>
+      <c r="M55" s="227"/>
+      <c r="N55" s="228"/>
+      <c r="O55" s="229" t="s">
         <v>156</v>
       </c>
-      <c r="P55" s="232"/>
-      <c r="Q55" s="232"/>
-      <c r="R55" s="232"/>
-      <c r="S55" s="233"/>
-      <c r="T55" s="231" t="s">
+      <c r="P55" s="230"/>
+      <c r="Q55" s="230"/>
+      <c r="R55" s="230"/>
+      <c r="S55" s="231"/>
+      <c r="T55" s="229" t="s">
         <v>173</v>
       </c>
-      <c r="U55" s="232"/>
-      <c r="V55" s="232"/>
-      <c r="W55" s="233"/>
-      <c r="X55" s="231">
+      <c r="U55" s="230"/>
+      <c r="V55" s="230"/>
+      <c r="W55" s="231"/>
+      <c r="X55" s="229">
         <v>2</v>
       </c>
-      <c r="Y55" s="232"/>
-      <c r="Z55" s="233"/>
+      <c r="Y55" s="230"/>
+      <c r="Z55" s="231"/>
     </row>
     <row r="56" spans="1:26" s="14" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A56" s="224"/>
+      <c r="A56" s="222"/>
       <c r="B56" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="C56" s="228" t="s">
+      <c r="C56" s="226" t="s">
         <v>175</v>
       </c>
-      <c r="D56" s="229"/>
-      <c r="E56" s="229"/>
-      <c r="F56" s="229"/>
-      <c r="G56" s="229"/>
-      <c r="H56" s="229"/>
-      <c r="I56" s="229"/>
-      <c r="J56" s="229"/>
-      <c r="K56" s="229"/>
-      <c r="L56" s="229"/>
-      <c r="M56" s="229"/>
-      <c r="N56" s="230"/>
-      <c r="O56" s="231" t="s">
+      <c r="D56" s="227"/>
+      <c r="E56" s="227"/>
+      <c r="F56" s="227"/>
+      <c r="G56" s="227"/>
+      <c r="H56" s="227"/>
+      <c r="I56" s="227"/>
+      <c r="J56" s="227"/>
+      <c r="K56" s="227"/>
+      <c r="L56" s="227"/>
+      <c r="M56" s="227"/>
+      <c r="N56" s="228"/>
+      <c r="O56" s="229" t="s">
         <v>156</v>
       </c>
-      <c r="P56" s="232"/>
-      <c r="Q56" s="232"/>
-      <c r="R56" s="232"/>
-      <c r="S56" s="233"/>
-      <c r="T56" s="231" t="s">
+      <c r="P56" s="230"/>
+      <c r="Q56" s="230"/>
+      <c r="R56" s="230"/>
+      <c r="S56" s="231"/>
+      <c r="T56" s="229" t="s">
         <v>176</v>
       </c>
-      <c r="U56" s="232"/>
-      <c r="V56" s="232"/>
-      <c r="W56" s="233"/>
-      <c r="X56" s="231">
+      <c r="U56" s="230"/>
+      <c r="V56" s="230"/>
+      <c r="W56" s="231"/>
+      <c r="X56" s="229">
         <v>2</v>
       </c>
-      <c r="Y56" s="232"/>
-      <c r="Z56" s="233"/>
+      <c r="Y56" s="230"/>
+      <c r="Z56" s="231"/>
     </row>
     <row r="57" spans="1:26" s="14" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A57" s="224"/>
+      <c r="A57" s="222"/>
       <c r="B57" s="26" t="s">
         <v>177</v>
       </c>
-      <c r="C57" s="228" t="s">
+      <c r="C57" s="226" t="s">
         <v>178</v>
       </c>
-      <c r="D57" s="229"/>
-      <c r="E57" s="229"/>
-      <c r="F57" s="229"/>
-      <c r="G57" s="229"/>
-      <c r="H57" s="229"/>
-      <c r="I57" s="229"/>
-      <c r="J57" s="229"/>
-      <c r="K57" s="229"/>
-      <c r="L57" s="229"/>
-      <c r="M57" s="229"/>
-      <c r="N57" s="230"/>
-      <c r="O57" s="231" t="s">
+      <c r="D57" s="227"/>
+      <c r="E57" s="227"/>
+      <c r="F57" s="227"/>
+      <c r="G57" s="227"/>
+      <c r="H57" s="227"/>
+      <c r="I57" s="227"/>
+      <c r="J57" s="227"/>
+      <c r="K57" s="227"/>
+      <c r="L57" s="227"/>
+      <c r="M57" s="227"/>
+      <c r="N57" s="228"/>
+      <c r="O57" s="229" t="s">
         <v>156</v>
       </c>
-      <c r="P57" s="232"/>
-      <c r="Q57" s="232"/>
-      <c r="R57" s="232"/>
-      <c r="S57" s="233"/>
-      <c r="T57" s="231" t="s">
+      <c r="P57" s="230"/>
+      <c r="Q57" s="230"/>
+      <c r="R57" s="230"/>
+      <c r="S57" s="231"/>
+      <c r="T57" s="229" t="s">
         <v>179</v>
       </c>
-      <c r="U57" s="232"/>
-      <c r="V57" s="232"/>
-      <c r="W57" s="233"/>
-      <c r="X57" s="231">
+      <c r="U57" s="230"/>
+      <c r="V57" s="230"/>
+      <c r="W57" s="231"/>
+      <c r="X57" s="229">
         <v>2</v>
       </c>
-      <c r="Y57" s="232"/>
-      <c r="Z57" s="233"/>
+      <c r="Y57" s="230"/>
+      <c r="Z57" s="231"/>
     </row>
     <row r="58" spans="1:26" s="14" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A58" s="225"/>
+      <c r="A58" s="223"/>
       <c r="B58" s="26" t="s">
         <v>180</v>
       </c>
-      <c r="C58" s="228" t="s">
+      <c r="C58" s="226" t="s">
         <v>181</v>
       </c>
-      <c r="D58" s="229"/>
-      <c r="E58" s="229"/>
-      <c r="F58" s="229"/>
-      <c r="G58" s="229"/>
-      <c r="H58" s="229"/>
-      <c r="I58" s="229"/>
-      <c r="J58" s="229"/>
-      <c r="K58" s="229"/>
-      <c r="L58" s="229"/>
-      <c r="M58" s="229"/>
-      <c r="N58" s="230"/>
-      <c r="O58" s="231" t="s">
+      <c r="D58" s="227"/>
+      <c r="E58" s="227"/>
+      <c r="F58" s="227"/>
+      <c r="G58" s="227"/>
+      <c r="H58" s="227"/>
+      <c r="I58" s="227"/>
+      <c r="J58" s="227"/>
+      <c r="K58" s="227"/>
+      <c r="L58" s="227"/>
+      <c r="M58" s="227"/>
+      <c r="N58" s="228"/>
+      <c r="O58" s="229" t="s">
         <v>156</v>
       </c>
-      <c r="P58" s="232"/>
-      <c r="Q58" s="232"/>
-      <c r="R58" s="232"/>
-      <c r="S58" s="233"/>
-      <c r="T58" s="231" t="s">
+      <c r="P58" s="230"/>
+      <c r="Q58" s="230"/>
+      <c r="R58" s="230"/>
+      <c r="S58" s="231"/>
+      <c r="T58" s="229" t="s">
         <v>182</v>
       </c>
-      <c r="U58" s="232"/>
-      <c r="V58" s="232"/>
-      <c r="W58" s="233"/>
-      <c r="X58" s="231">
+      <c r="U58" s="230"/>
+      <c r="V58" s="230"/>
+      <c r="W58" s="231"/>
+      <c r="X58" s="229">
         <v>22</v>
       </c>
-      <c r="Y58" s="232"/>
-      <c r="Z58" s="233"/>
+      <c r="Y58" s="230"/>
+      <c r="Z58" s="231"/>
     </row>
     <row r="59" spans="1:26" s="14" customFormat="1" ht="16.5" customHeight="1">
       <c r="A59" s="90" t="s">
@@ -10484,38 +10469,38 @@
       <c r="B59" s="26" t="s">
         <v>183</v>
       </c>
-      <c r="C59" s="228" t="s">
+      <c r="C59" s="226" t="s">
         <v>184</v>
       </c>
-      <c r="D59" s="229"/>
-      <c r="E59" s="229"/>
-      <c r="F59" s="229"/>
-      <c r="G59" s="229"/>
-      <c r="H59" s="229"/>
-      <c r="I59" s="229"/>
-      <c r="J59" s="229"/>
-      <c r="K59" s="229"/>
-      <c r="L59" s="229"/>
-      <c r="M59" s="229"/>
-      <c r="N59" s="230"/>
-      <c r="O59" s="231" t="s">
+      <c r="D59" s="227"/>
+      <c r="E59" s="227"/>
+      <c r="F59" s="227"/>
+      <c r="G59" s="227"/>
+      <c r="H59" s="227"/>
+      <c r="I59" s="227"/>
+      <c r="J59" s="227"/>
+      <c r="K59" s="227"/>
+      <c r="L59" s="227"/>
+      <c r="M59" s="227"/>
+      <c r="N59" s="228"/>
+      <c r="O59" s="229" t="s">
         <v>156</v>
       </c>
-      <c r="P59" s="232"/>
-      <c r="Q59" s="232"/>
-      <c r="R59" s="232"/>
-      <c r="S59" s="233"/>
-      <c r="T59" s="231" t="s">
+      <c r="P59" s="230"/>
+      <c r="Q59" s="230"/>
+      <c r="R59" s="230"/>
+      <c r="S59" s="231"/>
+      <c r="T59" s="229" t="s">
         <v>185</v>
       </c>
-      <c r="U59" s="232"/>
-      <c r="V59" s="232"/>
-      <c r="W59" s="233"/>
-      <c r="X59" s="231">
+      <c r="U59" s="230"/>
+      <c r="V59" s="230"/>
+      <c r="W59" s="231"/>
+      <c r="X59" s="229">
         <v>8</v>
       </c>
-      <c r="Y59" s="232"/>
-      <c r="Z59" s="233"/>
+      <c r="Y59" s="230"/>
+      <c r="Z59" s="231"/>
     </row>
     <row r="60" spans="1:26" s="14" customFormat="1" ht="16.5" customHeight="1">
       <c r="A60" s="90" t="s">
@@ -10524,116 +10509,116 @@
       <c r="B60" s="26" t="s">
         <v>186</v>
       </c>
-      <c r="C60" s="228" t="s">
+      <c r="C60" s="226" t="s">
         <v>143</v>
       </c>
-      <c r="D60" s="229"/>
-      <c r="E60" s="229"/>
-      <c r="F60" s="229"/>
-      <c r="G60" s="229"/>
-      <c r="H60" s="229"/>
-      <c r="I60" s="229"/>
-      <c r="J60" s="229"/>
-      <c r="K60" s="229"/>
-      <c r="L60" s="229"/>
-      <c r="M60" s="229"/>
-      <c r="N60" s="230"/>
-      <c r="O60" s="231" t="s">
+      <c r="D60" s="227"/>
+      <c r="E60" s="227"/>
+      <c r="F60" s="227"/>
+      <c r="G60" s="227"/>
+      <c r="H60" s="227"/>
+      <c r="I60" s="227"/>
+      <c r="J60" s="227"/>
+      <c r="K60" s="227"/>
+      <c r="L60" s="227"/>
+      <c r="M60" s="227"/>
+      <c r="N60" s="228"/>
+      <c r="O60" s="229" t="s">
         <v>1</v>
       </c>
-      <c r="P60" s="232"/>
-      <c r="Q60" s="232"/>
-      <c r="R60" s="232"/>
-      <c r="S60" s="233"/>
-      <c r="T60" s="231" t="s">
+      <c r="P60" s="230"/>
+      <c r="Q60" s="230"/>
+      <c r="R60" s="230"/>
+      <c r="S60" s="231"/>
+      <c r="T60" s="229" t="s">
         <v>187</v>
       </c>
-      <c r="U60" s="232"/>
-      <c r="V60" s="232"/>
-      <c r="W60" s="233"/>
-      <c r="X60" s="231">
+      <c r="U60" s="230"/>
+      <c r="V60" s="230"/>
+      <c r="W60" s="231"/>
+      <c r="X60" s="229">
         <v>1</v>
       </c>
-      <c r="Y60" s="232"/>
-      <c r="Z60" s="233"/>
+      <c r="Y60" s="230"/>
+      <c r="Z60" s="231"/>
     </row>
     <row r="61" spans="1:26" s="14" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A61" s="217" t="s">
+      <c r="A61" s="215" t="s">
         <v>235</v>
       </c>
       <c r="B61" s="26" t="s">
         <v>188</v>
       </c>
-      <c r="C61" s="228" t="s">
+      <c r="C61" s="226" t="s">
         <v>172</v>
       </c>
-      <c r="D61" s="229"/>
-      <c r="E61" s="229"/>
-      <c r="F61" s="229"/>
-      <c r="G61" s="229"/>
-      <c r="H61" s="229"/>
-      <c r="I61" s="229"/>
-      <c r="J61" s="229"/>
-      <c r="K61" s="229"/>
-      <c r="L61" s="229"/>
-      <c r="M61" s="229"/>
-      <c r="N61" s="230"/>
-      <c r="O61" s="231" t="s">
+      <c r="D61" s="227"/>
+      <c r="E61" s="227"/>
+      <c r="F61" s="227"/>
+      <c r="G61" s="227"/>
+      <c r="H61" s="227"/>
+      <c r="I61" s="227"/>
+      <c r="J61" s="227"/>
+      <c r="K61" s="227"/>
+      <c r="L61" s="227"/>
+      <c r="M61" s="227"/>
+      <c r="N61" s="228"/>
+      <c r="O61" s="229" t="s">
         <v>156</v>
       </c>
-      <c r="P61" s="232"/>
-      <c r="Q61" s="232"/>
-      <c r="R61" s="232"/>
-      <c r="S61" s="233"/>
-      <c r="T61" s="231" t="s">
+      <c r="P61" s="230"/>
+      <c r="Q61" s="230"/>
+      <c r="R61" s="230"/>
+      <c r="S61" s="231"/>
+      <c r="T61" s="229" t="s">
         <v>173</v>
       </c>
-      <c r="U61" s="232"/>
-      <c r="V61" s="232"/>
-      <c r="W61" s="233"/>
-      <c r="X61" s="231">
+      <c r="U61" s="230"/>
+      <c r="V61" s="230"/>
+      <c r="W61" s="231"/>
+      <c r="X61" s="229">
         <v>2</v>
       </c>
-      <c r="Y61" s="232"/>
-      <c r="Z61" s="233"/>
+      <c r="Y61" s="230"/>
+      <c r="Z61" s="231"/>
     </row>
     <row r="62" spans="1:26" s="14" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A62" s="218"/>
+      <c r="A62" s="216"/>
       <c r="B62" s="26" t="s">
         <v>189</v>
       </c>
-      <c r="C62" s="228" t="s">
+      <c r="C62" s="226" t="s">
         <v>190</v>
       </c>
-      <c r="D62" s="229"/>
-      <c r="E62" s="229"/>
-      <c r="F62" s="229"/>
-      <c r="G62" s="229"/>
-      <c r="H62" s="229"/>
-      <c r="I62" s="229"/>
-      <c r="J62" s="229"/>
-      <c r="K62" s="229"/>
-      <c r="L62" s="229"/>
-      <c r="M62" s="229"/>
-      <c r="N62" s="230"/>
-      <c r="O62" s="231" t="s">
+      <c r="D62" s="227"/>
+      <c r="E62" s="227"/>
+      <c r="F62" s="227"/>
+      <c r="G62" s="227"/>
+      <c r="H62" s="227"/>
+      <c r="I62" s="227"/>
+      <c r="J62" s="227"/>
+      <c r="K62" s="227"/>
+      <c r="L62" s="227"/>
+      <c r="M62" s="227"/>
+      <c r="N62" s="228"/>
+      <c r="O62" s="229" t="s">
         <v>156</v>
       </c>
-      <c r="P62" s="232"/>
-      <c r="Q62" s="232"/>
-      <c r="R62" s="232"/>
-      <c r="S62" s="233"/>
-      <c r="T62" s="231" t="s">
+      <c r="P62" s="230"/>
+      <c r="Q62" s="230"/>
+      <c r="R62" s="230"/>
+      <c r="S62" s="231"/>
+      <c r="T62" s="229" t="s">
         <v>191</v>
       </c>
-      <c r="U62" s="232"/>
-      <c r="V62" s="232"/>
-      <c r="W62" s="233"/>
-      <c r="X62" s="231">
+      <c r="U62" s="230"/>
+      <c r="V62" s="230"/>
+      <c r="W62" s="231"/>
+      <c r="X62" s="229">
         <v>1</v>
       </c>
-      <c r="Y62" s="232"/>
-      <c r="Z62" s="233"/>
+      <c r="Y62" s="230"/>
+      <c r="Z62" s="231"/>
     </row>
     <row r="63" spans="1:26" s="14" customFormat="1" ht="16.5" customHeight="1">
       <c r="A63" s="90" t="s">
@@ -10642,38 +10627,38 @@
       <c r="B63" s="26" t="s">
         <v>192</v>
       </c>
-      <c r="C63" s="228" t="s">
+      <c r="C63" s="226" t="s">
         <v>145</v>
       </c>
-      <c r="D63" s="229"/>
-      <c r="E63" s="229"/>
-      <c r="F63" s="229"/>
-      <c r="G63" s="229"/>
-      <c r="H63" s="229"/>
-      <c r="I63" s="229"/>
-      <c r="J63" s="229"/>
-      <c r="K63" s="229"/>
-      <c r="L63" s="229"/>
-      <c r="M63" s="229"/>
-      <c r="N63" s="230"/>
-      <c r="O63" s="231" t="s">
+      <c r="D63" s="227"/>
+      <c r="E63" s="227"/>
+      <c r="F63" s="227"/>
+      <c r="G63" s="227"/>
+      <c r="H63" s="227"/>
+      <c r="I63" s="227"/>
+      <c r="J63" s="227"/>
+      <c r="K63" s="227"/>
+      <c r="L63" s="227"/>
+      <c r="M63" s="227"/>
+      <c r="N63" s="228"/>
+      <c r="O63" s="229" t="s">
         <v>0</v>
       </c>
-      <c r="P63" s="232"/>
-      <c r="Q63" s="232"/>
-      <c r="R63" s="232"/>
-      <c r="S63" s="233"/>
-      <c r="T63" s="231" t="s">
+      <c r="P63" s="230"/>
+      <c r="Q63" s="230"/>
+      <c r="R63" s="230"/>
+      <c r="S63" s="231"/>
+      <c r="T63" s="229" t="s">
         <v>14</v>
       </c>
-      <c r="U63" s="232"/>
-      <c r="V63" s="232"/>
-      <c r="W63" s="233"/>
-      <c r="X63" s="231">
+      <c r="U63" s="230"/>
+      <c r="V63" s="230"/>
+      <c r="W63" s="231"/>
+      <c r="X63" s="229">
         <v>1</v>
       </c>
-      <c r="Y63" s="232"/>
-      <c r="Z63" s="233"/>
+      <c r="Y63" s="230"/>
+      <c r="Z63" s="231"/>
     </row>
     <row r="64" spans="1:26" s="14" customFormat="1" ht="16.5" customHeight="1">
       <c r="A64" s="90" t="s">
@@ -10682,38 +10667,38 @@
       <c r="B64" s="26" t="s">
         <v>193</v>
       </c>
-      <c r="C64" s="228" t="s">
+      <c r="C64" s="226" t="s">
         <v>168</v>
       </c>
-      <c r="D64" s="229"/>
-      <c r="E64" s="229"/>
-      <c r="F64" s="229"/>
-      <c r="G64" s="229"/>
-      <c r="H64" s="229"/>
-      <c r="I64" s="229"/>
-      <c r="J64" s="229"/>
-      <c r="K64" s="229"/>
-      <c r="L64" s="229"/>
-      <c r="M64" s="229"/>
-      <c r="N64" s="230"/>
-      <c r="O64" s="231" t="s">
+      <c r="D64" s="227"/>
+      <c r="E64" s="227"/>
+      <c r="F64" s="227"/>
+      <c r="G64" s="227"/>
+      <c r="H64" s="227"/>
+      <c r="I64" s="227"/>
+      <c r="J64" s="227"/>
+      <c r="K64" s="227"/>
+      <c r="L64" s="227"/>
+      <c r="M64" s="227"/>
+      <c r="N64" s="228"/>
+      <c r="O64" s="229" t="s">
         <v>169</v>
       </c>
-      <c r="P64" s="232"/>
-      <c r="Q64" s="232"/>
-      <c r="R64" s="232"/>
-      <c r="S64" s="233"/>
-      <c r="T64" s="231" t="s">
+      <c r="P64" s="230"/>
+      <c r="Q64" s="230"/>
+      <c r="R64" s="230"/>
+      <c r="S64" s="231"/>
+      <c r="T64" s="229" t="s">
         <v>170</v>
       </c>
-      <c r="U64" s="232"/>
-      <c r="V64" s="232"/>
-      <c r="W64" s="233"/>
-      <c r="X64" s="231">
+      <c r="U64" s="230"/>
+      <c r="V64" s="230"/>
+      <c r="W64" s="231"/>
+      <c r="X64" s="229">
         <v>1</v>
       </c>
-      <c r="Y64" s="232"/>
-      <c r="Z64" s="233"/>
+      <c r="Y64" s="230"/>
+      <c r="Z64" s="231"/>
     </row>
     <row r="65" spans="1:26" s="14" customFormat="1" ht="16.5" customHeight="1">
       <c r="A65" s="90" t="s">
@@ -10722,38 +10707,38 @@
       <c r="B65" s="26" t="s">
         <v>194</v>
       </c>
-      <c r="C65" s="228" t="s">
+      <c r="C65" s="226" t="s">
         <v>137</v>
       </c>
-      <c r="D65" s="229"/>
-      <c r="E65" s="229"/>
-      <c r="F65" s="229"/>
-      <c r="G65" s="229"/>
-      <c r="H65" s="229"/>
-      <c r="I65" s="229"/>
-      <c r="J65" s="229"/>
-      <c r="K65" s="229"/>
-      <c r="L65" s="229"/>
-      <c r="M65" s="229"/>
-      <c r="N65" s="230"/>
-      <c r="O65" s="231" t="s">
+      <c r="D65" s="227"/>
+      <c r="E65" s="227"/>
+      <c r="F65" s="227"/>
+      <c r="G65" s="227"/>
+      <c r="H65" s="227"/>
+      <c r="I65" s="227"/>
+      <c r="J65" s="227"/>
+      <c r="K65" s="227"/>
+      <c r="L65" s="227"/>
+      <c r="M65" s="227"/>
+      <c r="N65" s="228"/>
+      <c r="O65" s="229" t="s">
         <v>1</v>
       </c>
-      <c r="P65" s="232"/>
-      <c r="Q65" s="232"/>
-      <c r="R65" s="232"/>
-      <c r="S65" s="233"/>
-      <c r="T65" s="231" t="s">
+      <c r="P65" s="230"/>
+      <c r="Q65" s="230"/>
+      <c r="R65" s="230"/>
+      <c r="S65" s="231"/>
+      <c r="T65" s="229" t="s">
         <v>195</v>
       </c>
-      <c r="U65" s="232"/>
-      <c r="V65" s="232"/>
-      <c r="W65" s="233"/>
-      <c r="X65" s="231">
+      <c r="U65" s="230"/>
+      <c r="V65" s="230"/>
+      <c r="W65" s="231"/>
+      <c r="X65" s="229">
         <v>1</v>
       </c>
-      <c r="Y65" s="232"/>
-      <c r="Z65" s="233"/>
+      <c r="Y65" s="230"/>
+      <c r="Z65" s="231"/>
     </row>
     <row r="66" spans="1:26" s="14" customFormat="1" ht="16.5" customHeight="1">
       <c r="A66" s="90" t="s">
@@ -10762,38 +10747,38 @@
       <c r="B66" s="26" t="s">
         <v>196</v>
       </c>
-      <c r="C66" s="228" t="s">
+      <c r="C66" s="226" t="s">
         <v>162</v>
       </c>
-      <c r="D66" s="229"/>
-      <c r="E66" s="229"/>
-      <c r="F66" s="229"/>
-      <c r="G66" s="229"/>
-      <c r="H66" s="229"/>
-      <c r="I66" s="229"/>
-      <c r="J66" s="229"/>
-      <c r="K66" s="229"/>
-      <c r="L66" s="229"/>
-      <c r="M66" s="229"/>
-      <c r="N66" s="230"/>
-      <c r="O66" s="231" t="s">
+      <c r="D66" s="227"/>
+      <c r="E66" s="227"/>
+      <c r="F66" s="227"/>
+      <c r="G66" s="227"/>
+      <c r="H66" s="227"/>
+      <c r="I66" s="227"/>
+      <c r="J66" s="227"/>
+      <c r="K66" s="227"/>
+      <c r="L66" s="227"/>
+      <c r="M66" s="227"/>
+      <c r="N66" s="228"/>
+      <c r="O66" s="229" t="s">
         <v>1</v>
       </c>
-      <c r="P66" s="232"/>
-      <c r="Q66" s="232"/>
-      <c r="R66" s="232"/>
-      <c r="S66" s="233"/>
-      <c r="T66" s="231" t="s">
+      <c r="P66" s="230"/>
+      <c r="Q66" s="230"/>
+      <c r="R66" s="230"/>
+      <c r="S66" s="231"/>
+      <c r="T66" s="229" t="s">
         <v>163</v>
       </c>
-      <c r="U66" s="232"/>
-      <c r="V66" s="232"/>
-      <c r="W66" s="233"/>
-      <c r="X66" s="231">
+      <c r="U66" s="230"/>
+      <c r="V66" s="230"/>
+      <c r="W66" s="231"/>
+      <c r="X66" s="229">
         <v>1</v>
       </c>
-      <c r="Y66" s="232"/>
-      <c r="Z66" s="233"/>
+      <c r="Y66" s="230"/>
+      <c r="Z66" s="231"/>
     </row>
     <row r="67" spans="1:26" s="14" customFormat="1" ht="16.5" customHeight="1">
       <c r="A67" s="90" t="s">
@@ -10802,38 +10787,38 @@
       <c r="B67" s="26" t="s">
         <v>197</v>
       </c>
-      <c r="C67" s="228" t="s">
+      <c r="C67" s="226" t="s">
         <v>198</v>
       </c>
-      <c r="D67" s="229"/>
-      <c r="E67" s="229"/>
-      <c r="F67" s="229"/>
-      <c r="G67" s="229"/>
-      <c r="H67" s="229"/>
-      <c r="I67" s="229"/>
-      <c r="J67" s="229"/>
-      <c r="K67" s="229"/>
-      <c r="L67" s="229"/>
-      <c r="M67" s="229"/>
-      <c r="N67" s="230"/>
-      <c r="O67" s="231" t="s">
+      <c r="D67" s="227"/>
+      <c r="E67" s="227"/>
+      <c r="F67" s="227"/>
+      <c r="G67" s="227"/>
+      <c r="H67" s="227"/>
+      <c r="I67" s="227"/>
+      <c r="J67" s="227"/>
+      <c r="K67" s="227"/>
+      <c r="L67" s="227"/>
+      <c r="M67" s="227"/>
+      <c r="N67" s="228"/>
+      <c r="O67" s="229" t="s">
         <v>0</v>
       </c>
-      <c r="P67" s="232"/>
-      <c r="Q67" s="232"/>
-      <c r="R67" s="232"/>
-      <c r="S67" s="233"/>
-      <c r="T67" s="231" t="s">
+      <c r="P67" s="230"/>
+      <c r="Q67" s="230"/>
+      <c r="R67" s="230"/>
+      <c r="S67" s="231"/>
+      <c r="T67" s="229" t="s">
         <v>12</v>
       </c>
-      <c r="U67" s="232"/>
-      <c r="V67" s="232"/>
-      <c r="W67" s="233"/>
-      <c r="X67" s="231">
+      <c r="U67" s="230"/>
+      <c r="V67" s="230"/>
+      <c r="W67" s="231"/>
+      <c r="X67" s="229">
         <v>6</v>
       </c>
-      <c r="Y67" s="232"/>
-      <c r="Z67" s="233"/>
+      <c r="Y67" s="230"/>
+      <c r="Z67" s="231"/>
     </row>
     <row r="68" spans="1:26" s="14" customFormat="1" ht="16.5" customHeight="1">
       <c r="A68" s="26">
@@ -10842,38 +10827,38 @@
       <c r="B68" s="26" t="s">
         <v>199</v>
       </c>
-      <c r="C68" s="234" t="s">
+      <c r="C68" s="232" t="s">
         <v>78</v>
       </c>
-      <c r="D68" s="242"/>
-      <c r="E68" s="242"/>
-      <c r="F68" s="242"/>
-      <c r="G68" s="242"/>
-      <c r="H68" s="242"/>
-      <c r="I68" s="242"/>
-      <c r="J68" s="242"/>
-      <c r="K68" s="242"/>
-      <c r="L68" s="242"/>
-      <c r="M68" s="242"/>
-      <c r="N68" s="243"/>
-      <c r="O68" s="235" t="s">
+      <c r="D68" s="240"/>
+      <c r="E68" s="240"/>
+      <c r="F68" s="240"/>
+      <c r="G68" s="240"/>
+      <c r="H68" s="240"/>
+      <c r="I68" s="240"/>
+      <c r="J68" s="240"/>
+      <c r="K68" s="240"/>
+      <c r="L68" s="240"/>
+      <c r="M68" s="240"/>
+      <c r="N68" s="241"/>
+      <c r="O68" s="233" t="s">
         <v>1</v>
       </c>
-      <c r="P68" s="236"/>
-      <c r="Q68" s="236"/>
-      <c r="R68" s="236"/>
-      <c r="S68" s="237"/>
-      <c r="T68" s="231" t="s">
+      <c r="P68" s="234"/>
+      <c r="Q68" s="234"/>
+      <c r="R68" s="234"/>
+      <c r="S68" s="235"/>
+      <c r="T68" s="229" t="s">
         <v>7</v>
       </c>
-      <c r="U68" s="232"/>
-      <c r="V68" s="232"/>
-      <c r="W68" s="233"/>
-      <c r="X68" s="231">
+      <c r="U68" s="230"/>
+      <c r="V68" s="230"/>
+      <c r="W68" s="231"/>
+      <c r="X68" s="229">
         <v>1</v>
       </c>
-      <c r="Y68" s="232"/>
-      <c r="Z68" s="233"/>
+      <c r="Y68" s="230"/>
+      <c r="Z68" s="231"/>
     </row>
     <row r="69" spans="1:26" s="14" customFormat="1" ht="16.5" customHeight="1">
       <c r="A69" s="26" t="s">
@@ -10882,38 +10867,38 @@
       <c r="B69" s="26" t="s">
         <v>200</v>
       </c>
-      <c r="C69" s="234" t="s">
+      <c r="C69" s="232" t="s">
         <v>79</v>
       </c>
-      <c r="D69" s="242"/>
-      <c r="E69" s="242"/>
-      <c r="F69" s="242"/>
-      <c r="G69" s="242"/>
-      <c r="H69" s="242"/>
-      <c r="I69" s="242"/>
-      <c r="J69" s="242"/>
-      <c r="K69" s="242"/>
-      <c r="L69" s="242"/>
-      <c r="M69" s="242"/>
-      <c r="N69" s="243"/>
-      <c r="O69" s="235" t="s">
+      <c r="D69" s="240"/>
+      <c r="E69" s="240"/>
+      <c r="F69" s="240"/>
+      <c r="G69" s="240"/>
+      <c r="H69" s="240"/>
+      <c r="I69" s="240"/>
+      <c r="J69" s="240"/>
+      <c r="K69" s="240"/>
+      <c r="L69" s="240"/>
+      <c r="M69" s="240"/>
+      <c r="N69" s="241"/>
+      <c r="O69" s="233" t="s">
         <v>1</v>
       </c>
-      <c r="P69" s="236"/>
-      <c r="Q69" s="236"/>
-      <c r="R69" s="236"/>
-      <c r="S69" s="237"/>
-      <c r="T69" s="231" t="s">
+      <c r="P69" s="234"/>
+      <c r="Q69" s="234"/>
+      <c r="R69" s="234"/>
+      <c r="S69" s="235"/>
+      <c r="T69" s="229" t="s">
         <v>9</v>
       </c>
-      <c r="U69" s="232"/>
-      <c r="V69" s="232"/>
-      <c r="W69" s="233"/>
-      <c r="X69" s="231">
+      <c r="U69" s="230"/>
+      <c r="V69" s="230"/>
+      <c r="W69" s="231"/>
+      <c r="X69" s="229">
         <v>1</v>
       </c>
-      <c r="Y69" s="232"/>
-      <c r="Z69" s="233"/>
+      <c r="Y69" s="230"/>
+      <c r="Z69" s="231"/>
     </row>
     <row r="70" spans="1:26" s="14" customFormat="1" ht="16.5" customHeight="1">
       <c r="A70" s="26" t="s">
@@ -10922,38 +10907,38 @@
       <c r="B70" s="26" t="s">
         <v>201</v>
       </c>
-      <c r="C70" s="234" t="s">
+      <c r="C70" s="232" t="s">
         <v>202</v>
       </c>
-      <c r="D70" s="242"/>
-      <c r="E70" s="242"/>
-      <c r="F70" s="242"/>
-      <c r="G70" s="242"/>
-      <c r="H70" s="242"/>
-      <c r="I70" s="242"/>
-      <c r="J70" s="242"/>
-      <c r="K70" s="242"/>
-      <c r="L70" s="242"/>
-      <c r="M70" s="242"/>
-      <c r="N70" s="243"/>
-      <c r="O70" s="235" t="s">
+      <c r="D70" s="240"/>
+      <c r="E70" s="240"/>
+      <c r="F70" s="240"/>
+      <c r="G70" s="240"/>
+      <c r="H70" s="240"/>
+      <c r="I70" s="240"/>
+      <c r="J70" s="240"/>
+      <c r="K70" s="240"/>
+      <c r="L70" s="240"/>
+      <c r="M70" s="240"/>
+      <c r="N70" s="241"/>
+      <c r="O70" s="233" t="s">
         <v>2</v>
       </c>
-      <c r="P70" s="236"/>
-      <c r="Q70" s="236"/>
-      <c r="R70" s="236"/>
-      <c r="S70" s="237"/>
-      <c r="T70" s="231" t="s">
+      <c r="P70" s="234"/>
+      <c r="Q70" s="234"/>
+      <c r="R70" s="234"/>
+      <c r="S70" s="235"/>
+      <c r="T70" s="229" t="s">
         <v>10</v>
       </c>
-      <c r="U70" s="232"/>
-      <c r="V70" s="232"/>
-      <c r="W70" s="233"/>
-      <c r="X70" s="231">
+      <c r="U70" s="230"/>
+      <c r="V70" s="230"/>
+      <c r="W70" s="231"/>
+      <c r="X70" s="229">
         <v>6</v>
       </c>
-      <c r="Y70" s="232"/>
-      <c r="Z70" s="233"/>
+      <c r="Y70" s="230"/>
+      <c r="Z70" s="231"/>
     </row>
     <row r="71" spans="1:26" s="14" customFormat="1" ht="16.5" customHeight="1">
       <c r="A71" s="26" t="s">
@@ -10962,38 +10947,38 @@
       <c r="B71" s="26" t="s">
         <v>203</v>
       </c>
-      <c r="C71" s="234" t="s">
+      <c r="C71" s="232" t="s">
         <v>204</v>
       </c>
-      <c r="D71" s="242"/>
-      <c r="E71" s="242"/>
-      <c r="F71" s="242"/>
-      <c r="G71" s="242"/>
-      <c r="H71" s="242"/>
-      <c r="I71" s="242"/>
-      <c r="J71" s="242"/>
-      <c r="K71" s="242"/>
-      <c r="L71" s="242"/>
-      <c r="M71" s="242"/>
-      <c r="N71" s="243"/>
-      <c r="O71" s="235" t="s">
+      <c r="D71" s="240"/>
+      <c r="E71" s="240"/>
+      <c r="F71" s="240"/>
+      <c r="G71" s="240"/>
+      <c r="H71" s="240"/>
+      <c r="I71" s="240"/>
+      <c r="J71" s="240"/>
+      <c r="K71" s="240"/>
+      <c r="L71" s="240"/>
+      <c r="M71" s="240"/>
+      <c r="N71" s="241"/>
+      <c r="O71" s="233" t="s">
         <v>0</v>
       </c>
-      <c r="P71" s="236"/>
-      <c r="Q71" s="236"/>
-      <c r="R71" s="236"/>
-      <c r="S71" s="237"/>
-      <c r="T71" s="231" t="s">
+      <c r="P71" s="234"/>
+      <c r="Q71" s="234"/>
+      <c r="R71" s="234"/>
+      <c r="S71" s="235"/>
+      <c r="T71" s="229" t="s">
         <v>12</v>
       </c>
-      <c r="U71" s="232"/>
-      <c r="V71" s="232"/>
-      <c r="W71" s="233"/>
-      <c r="X71" s="231">
+      <c r="U71" s="230"/>
+      <c r="V71" s="230"/>
+      <c r="W71" s="231"/>
+      <c r="X71" s="229">
         <v>6</v>
       </c>
-      <c r="Y71" s="232"/>
-      <c r="Z71" s="233"/>
+      <c r="Y71" s="230"/>
+      <c r="Z71" s="231"/>
     </row>
     <row r="72" spans="1:26" s="14" customFormat="1" ht="16.5" customHeight="1">
       <c r="A72" s="26" t="s">
@@ -11002,38 +10987,38 @@
       <c r="B72" s="26" t="s">
         <v>205</v>
       </c>
-      <c r="C72" s="234" t="s">
+      <c r="C72" s="232" t="s">
         <v>81</v>
       </c>
-      <c r="D72" s="242"/>
-      <c r="E72" s="242"/>
-      <c r="F72" s="242"/>
-      <c r="G72" s="242"/>
-      <c r="H72" s="242"/>
-      <c r="I72" s="242"/>
-      <c r="J72" s="242"/>
-      <c r="K72" s="242"/>
-      <c r="L72" s="242"/>
-      <c r="M72" s="242"/>
-      <c r="N72" s="243"/>
-      <c r="O72" s="235" t="s">
+      <c r="D72" s="240"/>
+      <c r="E72" s="240"/>
+      <c r="F72" s="240"/>
+      <c r="G72" s="240"/>
+      <c r="H72" s="240"/>
+      <c r="I72" s="240"/>
+      <c r="J72" s="240"/>
+      <c r="K72" s="240"/>
+      <c r="L72" s="240"/>
+      <c r="M72" s="240"/>
+      <c r="N72" s="241"/>
+      <c r="O72" s="233" t="s">
         <v>0</v>
       </c>
-      <c r="P72" s="236"/>
-      <c r="Q72" s="236"/>
-      <c r="R72" s="236"/>
-      <c r="S72" s="237"/>
-      <c r="T72" s="231" t="s">
+      <c r="P72" s="234"/>
+      <c r="Q72" s="234"/>
+      <c r="R72" s="234"/>
+      <c r="S72" s="235"/>
+      <c r="T72" s="229" t="s">
         <v>14</v>
       </c>
-      <c r="U72" s="232"/>
-      <c r="V72" s="232"/>
-      <c r="W72" s="233"/>
-      <c r="X72" s="231">
+      <c r="U72" s="230"/>
+      <c r="V72" s="230"/>
+      <c r="W72" s="231"/>
+      <c r="X72" s="229">
         <v>6</v>
       </c>
-      <c r="Y72" s="232"/>
-      <c r="Z72" s="233"/>
+      <c r="Y72" s="230"/>
+      <c r="Z72" s="231"/>
     </row>
     <row r="73" spans="1:26" s="14" customFormat="1" ht="16.5" customHeight="1">
       <c r="A73" s="26">
@@ -11042,38 +11027,38 @@
       <c r="B73" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="C73" s="234" t="s">
+      <c r="C73" s="232" t="s">
         <v>207</v>
       </c>
-      <c r="D73" s="232"/>
-      <c r="E73" s="232"/>
-      <c r="F73" s="232"/>
-      <c r="G73" s="232"/>
-      <c r="H73" s="232"/>
-      <c r="I73" s="232"/>
-      <c r="J73" s="232"/>
-      <c r="K73" s="232"/>
-      <c r="L73" s="232"/>
-      <c r="M73" s="232"/>
-      <c r="N73" s="233"/>
-      <c r="O73" s="235" t="s">
+      <c r="D73" s="230"/>
+      <c r="E73" s="230"/>
+      <c r="F73" s="230"/>
+      <c r="G73" s="230"/>
+      <c r="H73" s="230"/>
+      <c r="I73" s="230"/>
+      <c r="J73" s="230"/>
+      <c r="K73" s="230"/>
+      <c r="L73" s="230"/>
+      <c r="M73" s="230"/>
+      <c r="N73" s="231"/>
+      <c r="O73" s="233" t="s">
         <v>156</v>
       </c>
-      <c r="P73" s="236"/>
-      <c r="Q73" s="236"/>
-      <c r="R73" s="236"/>
-      <c r="S73" s="237"/>
-      <c r="T73" s="231" t="s">
+      <c r="P73" s="234"/>
+      <c r="Q73" s="234"/>
+      <c r="R73" s="234"/>
+      <c r="S73" s="235"/>
+      <c r="T73" s="229" t="s">
         <v>157</v>
       </c>
-      <c r="U73" s="232"/>
-      <c r="V73" s="232"/>
-      <c r="W73" s="233"/>
-      <c r="X73" s="238">
+      <c r="U73" s="230"/>
+      <c r="V73" s="230"/>
+      <c r="W73" s="231"/>
+      <c r="X73" s="236">
         <v>1</v>
       </c>
-      <c r="Y73" s="239"/>
-      <c r="Z73" s="240"/>
+      <c r="Y73" s="237"/>
+      <c r="Z73" s="238"/>
     </row>
     <row r="74" spans="1:26" s="14" customFormat="1" ht="16.5" customHeight="1">
       <c r="A74" s="26" t="s">
@@ -11082,38 +11067,38 @@
       <c r="B74" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="C74" s="234" t="s">
+      <c r="C74" s="232" t="s">
         <v>209</v>
       </c>
-      <c r="D74" s="232"/>
-      <c r="E74" s="232"/>
-      <c r="F74" s="232"/>
-      <c r="G74" s="232"/>
-      <c r="H74" s="232"/>
-      <c r="I74" s="232"/>
-      <c r="J74" s="232"/>
-      <c r="K74" s="232"/>
-      <c r="L74" s="232"/>
-      <c r="M74" s="232"/>
-      <c r="N74" s="233"/>
-      <c r="O74" s="235" t="s">
+      <c r="D74" s="230"/>
+      <c r="E74" s="230"/>
+      <c r="F74" s="230"/>
+      <c r="G74" s="230"/>
+      <c r="H74" s="230"/>
+      <c r="I74" s="230"/>
+      <c r="J74" s="230"/>
+      <c r="K74" s="230"/>
+      <c r="L74" s="230"/>
+      <c r="M74" s="230"/>
+      <c r="N74" s="231"/>
+      <c r="O74" s="233" t="s">
         <v>156</v>
       </c>
-      <c r="P74" s="236"/>
-      <c r="Q74" s="236"/>
-      <c r="R74" s="236"/>
-      <c r="S74" s="237"/>
-      <c r="T74" s="231" t="s">
+      <c r="P74" s="234"/>
+      <c r="Q74" s="234"/>
+      <c r="R74" s="234"/>
+      <c r="S74" s="235"/>
+      <c r="T74" s="229" t="s">
         <v>160</v>
       </c>
-      <c r="U74" s="232"/>
-      <c r="V74" s="232"/>
-      <c r="W74" s="233"/>
-      <c r="X74" s="238">
+      <c r="U74" s="230"/>
+      <c r="V74" s="230"/>
+      <c r="W74" s="231"/>
+      <c r="X74" s="236">
         <v>4</v>
       </c>
-      <c r="Y74" s="239"/>
-      <c r="Z74" s="240"/>
+      <c r="Y74" s="237"/>
+      <c r="Z74" s="238"/>
     </row>
     <row r="75" spans="1:26" s="14" customFormat="1" ht="16.5" customHeight="1">
       <c r="A75" s="26" t="s">
@@ -11122,38 +11107,38 @@
       <c r="B75" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="C75" s="234" t="s">
+      <c r="C75" s="232" t="s">
         <v>211</v>
       </c>
-      <c r="D75" s="232"/>
-      <c r="E75" s="232"/>
-      <c r="F75" s="232"/>
-      <c r="G75" s="232"/>
-      <c r="H75" s="232"/>
-      <c r="I75" s="232"/>
-      <c r="J75" s="232"/>
-      <c r="K75" s="232"/>
-      <c r="L75" s="232"/>
-      <c r="M75" s="232"/>
-      <c r="N75" s="233"/>
-      <c r="O75" s="235" t="s">
+      <c r="D75" s="230"/>
+      <c r="E75" s="230"/>
+      <c r="F75" s="230"/>
+      <c r="G75" s="230"/>
+      <c r="H75" s="230"/>
+      <c r="I75" s="230"/>
+      <c r="J75" s="230"/>
+      <c r="K75" s="230"/>
+      <c r="L75" s="230"/>
+      <c r="M75" s="230"/>
+      <c r="N75" s="231"/>
+      <c r="O75" s="233" t="s">
         <v>1</v>
       </c>
-      <c r="P75" s="236"/>
-      <c r="Q75" s="236"/>
-      <c r="R75" s="236"/>
-      <c r="S75" s="237"/>
-      <c r="T75" s="231" t="s">
+      <c r="P75" s="234"/>
+      <c r="Q75" s="234"/>
+      <c r="R75" s="234"/>
+      <c r="S75" s="235"/>
+      <c r="T75" s="229" t="s">
         <v>163</v>
       </c>
-      <c r="U75" s="232"/>
-      <c r="V75" s="232"/>
-      <c r="W75" s="233"/>
-      <c r="X75" s="238">
+      <c r="U75" s="230"/>
+      <c r="V75" s="230"/>
+      <c r="W75" s="231"/>
+      <c r="X75" s="236">
         <v>1</v>
       </c>
-      <c r="Y75" s="239"/>
-      <c r="Z75" s="240"/>
+      <c r="Y75" s="237"/>
+      <c r="Z75" s="238"/>
     </row>
     <row r="76" spans="1:26" s="14" customFormat="1" ht="16.5" customHeight="1">
       <c r="A76" s="26" t="s">
@@ -11162,38 +11147,38 @@
       <c r="B76" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="C76" s="234" t="s">
+      <c r="C76" s="232" t="s">
         <v>213</v>
       </c>
-      <c r="D76" s="232"/>
-      <c r="E76" s="232"/>
-      <c r="F76" s="232"/>
-      <c r="G76" s="232"/>
-      <c r="H76" s="232"/>
-      <c r="I76" s="232"/>
-      <c r="J76" s="232"/>
-      <c r="K76" s="232"/>
-      <c r="L76" s="232"/>
-      <c r="M76" s="232"/>
-      <c r="N76" s="233"/>
-      <c r="O76" s="235" t="s">
+      <c r="D76" s="230"/>
+      <c r="E76" s="230"/>
+      <c r="F76" s="230"/>
+      <c r="G76" s="230"/>
+      <c r="H76" s="230"/>
+      <c r="I76" s="230"/>
+      <c r="J76" s="230"/>
+      <c r="K76" s="230"/>
+      <c r="L76" s="230"/>
+      <c r="M76" s="230"/>
+      <c r="N76" s="231"/>
+      <c r="O76" s="233" t="s">
         <v>1</v>
       </c>
-      <c r="P76" s="236"/>
-      <c r="Q76" s="236"/>
-      <c r="R76" s="236"/>
-      <c r="S76" s="237"/>
-      <c r="T76" s="231" t="s">
+      <c r="P76" s="234"/>
+      <c r="Q76" s="234"/>
+      <c r="R76" s="234"/>
+      <c r="S76" s="235"/>
+      <c r="T76" s="229" t="s">
         <v>166</v>
       </c>
-      <c r="U76" s="232"/>
-      <c r="V76" s="232"/>
-      <c r="W76" s="233"/>
-      <c r="X76" s="238">
+      <c r="U76" s="230"/>
+      <c r="V76" s="230"/>
+      <c r="W76" s="231"/>
+      <c r="X76" s="236">
         <v>1</v>
       </c>
-      <c r="Y76" s="239"/>
-      <c r="Z76" s="240"/>
+      <c r="Y76" s="237"/>
+      <c r="Z76" s="238"/>
     </row>
     <row r="77" spans="1:26" s="14" customFormat="1" ht="16.5" customHeight="1">
       <c r="A77" s="26">
@@ -11202,38 +11187,38 @@
       <c r="B77" s="26" t="s">
         <v>214</v>
       </c>
-      <c r="C77" s="234" t="s">
+      <c r="C77" s="232" t="s">
         <v>215</v>
       </c>
-      <c r="D77" s="232"/>
-      <c r="E77" s="232"/>
-      <c r="F77" s="232"/>
-      <c r="G77" s="232"/>
-      <c r="H77" s="232"/>
-      <c r="I77" s="232"/>
-      <c r="J77" s="232"/>
-      <c r="K77" s="232"/>
-      <c r="L77" s="232"/>
-      <c r="M77" s="232"/>
-      <c r="N77" s="233"/>
-      <c r="O77" s="231" t="s">
+      <c r="D77" s="230"/>
+      <c r="E77" s="230"/>
+      <c r="F77" s="230"/>
+      <c r="G77" s="230"/>
+      <c r="H77" s="230"/>
+      <c r="I77" s="230"/>
+      <c r="J77" s="230"/>
+      <c r="K77" s="230"/>
+      <c r="L77" s="230"/>
+      <c r="M77" s="230"/>
+      <c r="N77" s="231"/>
+      <c r="O77" s="229" t="s">
         <v>169</v>
       </c>
-      <c r="P77" s="232"/>
-      <c r="Q77" s="232"/>
-      <c r="R77" s="232"/>
-      <c r="S77" s="233"/>
-      <c r="T77" s="231" t="s">
+      <c r="P77" s="230"/>
+      <c r="Q77" s="230"/>
+      <c r="R77" s="230"/>
+      <c r="S77" s="231"/>
+      <c r="T77" s="229" t="s">
         <v>170</v>
       </c>
-      <c r="U77" s="232"/>
-      <c r="V77" s="232"/>
-      <c r="W77" s="233"/>
-      <c r="X77" s="231">
+      <c r="U77" s="230"/>
+      <c r="V77" s="230"/>
+      <c r="W77" s="231"/>
+      <c r="X77" s="229">
         <v>1</v>
       </c>
-      <c r="Y77" s="232"/>
-      <c r="Z77" s="233"/>
+      <c r="Y77" s="230"/>
+      <c r="Z77" s="231"/>
     </row>
     <row r="78" spans="1:26" s="14" customFormat="1" ht="16.5" customHeight="1">
       <c r="A78" s="26" t="s">
@@ -11242,38 +11227,38 @@
       <c r="B78" s="26" t="s">
         <v>216</v>
       </c>
-      <c r="C78" s="234" t="s">
+      <c r="C78" s="232" t="s">
         <v>217</v>
       </c>
-      <c r="D78" s="232"/>
-      <c r="E78" s="232"/>
-      <c r="F78" s="232"/>
-      <c r="G78" s="232"/>
-      <c r="H78" s="232"/>
-      <c r="I78" s="232"/>
-      <c r="J78" s="232"/>
-      <c r="K78" s="232"/>
-      <c r="L78" s="232"/>
-      <c r="M78" s="232"/>
-      <c r="N78" s="233"/>
-      <c r="O78" s="235" t="s">
+      <c r="D78" s="230"/>
+      <c r="E78" s="230"/>
+      <c r="F78" s="230"/>
+      <c r="G78" s="230"/>
+      <c r="H78" s="230"/>
+      <c r="I78" s="230"/>
+      <c r="J78" s="230"/>
+      <c r="K78" s="230"/>
+      <c r="L78" s="230"/>
+      <c r="M78" s="230"/>
+      <c r="N78" s="231"/>
+      <c r="O78" s="233" t="s">
         <v>156</v>
       </c>
-      <c r="P78" s="236"/>
-      <c r="Q78" s="236"/>
-      <c r="R78" s="236"/>
-      <c r="S78" s="237"/>
-      <c r="T78" s="231" t="s">
+      <c r="P78" s="234"/>
+      <c r="Q78" s="234"/>
+      <c r="R78" s="234"/>
+      <c r="S78" s="235"/>
+      <c r="T78" s="229" t="s">
         <v>173</v>
       </c>
-      <c r="U78" s="232"/>
-      <c r="V78" s="232"/>
-      <c r="W78" s="233"/>
-      <c r="X78" s="231">
+      <c r="U78" s="230"/>
+      <c r="V78" s="230"/>
+      <c r="W78" s="231"/>
+      <c r="X78" s="229">
         <v>2</v>
       </c>
-      <c r="Y78" s="232"/>
-      <c r="Z78" s="233"/>
+      <c r="Y78" s="230"/>
+      <c r="Z78" s="231"/>
     </row>
     <row r="79" spans="1:26" s="14" customFormat="1" ht="16.5" customHeight="1">
       <c r="A79" s="26" t="s">
@@ -11282,38 +11267,38 @@
       <c r="B79" s="26" t="s">
         <v>218</v>
       </c>
-      <c r="C79" s="234" t="s">
+      <c r="C79" s="232" t="s">
         <v>219</v>
       </c>
-      <c r="D79" s="232"/>
-      <c r="E79" s="232"/>
-      <c r="F79" s="232"/>
-      <c r="G79" s="232"/>
-      <c r="H79" s="232"/>
-      <c r="I79" s="232"/>
-      <c r="J79" s="232"/>
-      <c r="K79" s="232"/>
-      <c r="L79" s="232"/>
-      <c r="M79" s="232"/>
-      <c r="N79" s="233"/>
-      <c r="O79" s="235" t="s">
+      <c r="D79" s="230"/>
+      <c r="E79" s="230"/>
+      <c r="F79" s="230"/>
+      <c r="G79" s="230"/>
+      <c r="H79" s="230"/>
+      <c r="I79" s="230"/>
+      <c r="J79" s="230"/>
+      <c r="K79" s="230"/>
+      <c r="L79" s="230"/>
+      <c r="M79" s="230"/>
+      <c r="N79" s="231"/>
+      <c r="O79" s="233" t="s">
         <v>156</v>
       </c>
-      <c r="P79" s="236"/>
-      <c r="Q79" s="236"/>
-      <c r="R79" s="236"/>
-      <c r="S79" s="237"/>
-      <c r="T79" s="231" t="s">
+      <c r="P79" s="234"/>
+      <c r="Q79" s="234"/>
+      <c r="R79" s="234"/>
+      <c r="S79" s="235"/>
+      <c r="T79" s="229" t="s">
         <v>176</v>
       </c>
-      <c r="U79" s="232"/>
-      <c r="V79" s="232"/>
-      <c r="W79" s="233"/>
-      <c r="X79" s="231">
+      <c r="U79" s="230"/>
+      <c r="V79" s="230"/>
+      <c r="W79" s="231"/>
+      <c r="X79" s="229">
         <v>2</v>
       </c>
-      <c r="Y79" s="232"/>
-      <c r="Z79" s="233"/>
+      <c r="Y79" s="230"/>
+      <c r="Z79" s="231"/>
     </row>
     <row r="80" spans="1:26" s="14" customFormat="1" ht="16.5" customHeight="1">
       <c r="A80" s="26" t="s">
@@ -11322,38 +11307,38 @@
       <c r="B80" s="26" t="s">
         <v>220</v>
       </c>
-      <c r="C80" s="234" t="s">
+      <c r="C80" s="232" t="s">
         <v>221</v>
       </c>
-      <c r="D80" s="232"/>
-      <c r="E80" s="232"/>
-      <c r="F80" s="232"/>
-      <c r="G80" s="232"/>
-      <c r="H80" s="232"/>
-      <c r="I80" s="232"/>
-      <c r="J80" s="232"/>
-      <c r="K80" s="232"/>
-      <c r="L80" s="232"/>
-      <c r="M80" s="232"/>
-      <c r="N80" s="233"/>
-      <c r="O80" s="235" t="s">
+      <c r="D80" s="230"/>
+      <c r="E80" s="230"/>
+      <c r="F80" s="230"/>
+      <c r="G80" s="230"/>
+      <c r="H80" s="230"/>
+      <c r="I80" s="230"/>
+      <c r="J80" s="230"/>
+      <c r="K80" s="230"/>
+      <c r="L80" s="230"/>
+      <c r="M80" s="230"/>
+      <c r="N80" s="231"/>
+      <c r="O80" s="233" t="s">
         <v>156</v>
       </c>
-      <c r="P80" s="236"/>
-      <c r="Q80" s="236"/>
-      <c r="R80" s="236"/>
-      <c r="S80" s="237"/>
-      <c r="T80" s="231" t="s">
+      <c r="P80" s="234"/>
+      <c r="Q80" s="234"/>
+      <c r="R80" s="234"/>
+      <c r="S80" s="235"/>
+      <c r="T80" s="229" t="s">
         <v>179</v>
       </c>
-      <c r="U80" s="232"/>
-      <c r="V80" s="232"/>
-      <c r="W80" s="233"/>
-      <c r="X80" s="231">
+      <c r="U80" s="230"/>
+      <c r="V80" s="230"/>
+      <c r="W80" s="231"/>
+      <c r="X80" s="229">
         <v>2</v>
       </c>
-      <c r="Y80" s="232"/>
-      <c r="Z80" s="233"/>
+      <c r="Y80" s="230"/>
+      <c r="Z80" s="231"/>
     </row>
     <row r="81" spans="1:26" s="14" customFormat="1" ht="16.5" customHeight="1">
       <c r="A81" s="26" t="s">
@@ -11362,67 +11347,67 @@
       <c r="B81" s="26" t="s">
         <v>222</v>
       </c>
-      <c r="C81" s="234" t="s">
+      <c r="C81" s="232" t="s">
         <v>223</v>
       </c>
-      <c r="D81" s="232"/>
-      <c r="E81" s="232"/>
-      <c r="F81" s="232"/>
-      <c r="G81" s="232"/>
-      <c r="H81" s="232"/>
-      <c r="I81" s="232"/>
-      <c r="J81" s="232"/>
-      <c r="K81" s="232"/>
-      <c r="L81" s="232"/>
-      <c r="M81" s="232"/>
-      <c r="N81" s="233"/>
-      <c r="O81" s="235" t="s">
+      <c r="D81" s="230"/>
+      <c r="E81" s="230"/>
+      <c r="F81" s="230"/>
+      <c r="G81" s="230"/>
+      <c r="H81" s="230"/>
+      <c r="I81" s="230"/>
+      <c r="J81" s="230"/>
+      <c r="K81" s="230"/>
+      <c r="L81" s="230"/>
+      <c r="M81" s="230"/>
+      <c r="N81" s="231"/>
+      <c r="O81" s="233" t="s">
         <v>156</v>
       </c>
-      <c r="P81" s="236"/>
-      <c r="Q81" s="236"/>
-      <c r="R81" s="236"/>
-      <c r="S81" s="237"/>
-      <c r="T81" s="231" t="s">
+      <c r="P81" s="234"/>
+      <c r="Q81" s="234"/>
+      <c r="R81" s="234"/>
+      <c r="S81" s="235"/>
+      <c r="T81" s="229" t="s">
         <v>182</v>
       </c>
-      <c r="U81" s="232"/>
-      <c r="V81" s="232"/>
-      <c r="W81" s="233"/>
-      <c r="X81" s="231">
+      <c r="U81" s="230"/>
+      <c r="V81" s="230"/>
+      <c r="W81" s="231"/>
+      <c r="X81" s="229">
         <v>2</v>
       </c>
-      <c r="Y81" s="232"/>
-      <c r="Z81" s="233"/>
+      <c r="Y81" s="230"/>
+      <c r="Z81" s="231"/>
     </row>
     <row r="82" spans="1:26" s="14" customFormat="1" ht="20.399999999999999" customHeight="1">
       <c r="A82" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C82" s="241"/>
-      <c r="D82" s="241"/>
-      <c r="E82" s="241"/>
-      <c r="F82" s="241"/>
-      <c r="G82" s="241"/>
-      <c r="H82" s="241"/>
-      <c r="I82" s="241"/>
-      <c r="J82" s="241"/>
-      <c r="K82" s="241"/>
-      <c r="L82" s="241"/>
-      <c r="M82" s="241"/>
-      <c r="N82" s="241"/>
-      <c r="O82" s="241"/>
-      <c r="P82" s="241"/>
-      <c r="Q82" s="241"/>
-      <c r="R82" s="241"/>
-      <c r="S82" s="241"/>
-      <c r="T82" s="241"/>
-      <c r="U82" s="241"/>
-      <c r="V82" s="241"/>
-      <c r="W82" s="241"/>
-      <c r="X82" s="241"/>
-      <c r="Y82" s="241"/>
-      <c r="Z82" s="241"/>
+      <c r="C82" s="239"/>
+      <c r="D82" s="239"/>
+      <c r="E82" s="239"/>
+      <c r="F82" s="239"/>
+      <c r="G82" s="239"/>
+      <c r="H82" s="239"/>
+      <c r="I82" s="239"/>
+      <c r="J82" s="239"/>
+      <c r="K82" s="239"/>
+      <c r="L82" s="239"/>
+      <c r="M82" s="239"/>
+      <c r="N82" s="239"/>
+      <c r="O82" s="239"/>
+      <c r="P82" s="239"/>
+      <c r="Q82" s="239"/>
+      <c r="R82" s="239"/>
+      <c r="S82" s="239"/>
+      <c r="T82" s="239"/>
+      <c r="U82" s="239"/>
+      <c r="V82" s="239"/>
+      <c r="W82" s="239"/>
+      <c r="X82" s="239"/>
+      <c r="Y82" s="239"/>
+      <c r="Z82" s="239"/>
     </row>
     <row r="83" spans="1:26" ht="15.6">
       <c r="A83" s="81"/>
@@ -11749,28 +11734,28 @@
   <sheetData>
     <row r="1" spans="1:26" ht="15">
       <c r="A1" s="78"/>
-      <c r="B1" s="266" t="s">
+      <c r="B1" s="264" t="s">
         <v>103</v>
       </c>
-      <c r="C1" s="266"/>
-      <c r="D1" s="266"/>
-      <c r="E1" s="266"/>
-      <c r="F1" s="266"/>
-      <c r="G1" s="266"/>
-      <c r="H1" s="266"/>
-      <c r="I1" s="266"/>
-      <c r="J1" s="266"/>
-      <c r="K1" s="266"/>
-      <c r="L1" s="266"/>
-      <c r="M1" s="266"/>
-      <c r="N1" s="266"/>
-      <c r="O1" s="266"/>
-      <c r="P1" s="266"/>
-      <c r="Q1" s="266"/>
-      <c r="R1" s="266"/>
-      <c r="S1" s="266"/>
-      <c r="T1" s="266"/>
-      <c r="U1" s="266"/>
+      <c r="C1" s="264"/>
+      <c r="D1" s="264"/>
+      <c r="E1" s="264"/>
+      <c r="F1" s="264"/>
+      <c r="G1" s="264"/>
+      <c r="H1" s="264"/>
+      <c r="I1" s="264"/>
+      <c r="J1" s="264"/>
+      <c r="K1" s="264"/>
+      <c r="L1" s="264"/>
+      <c r="M1" s="264"/>
+      <c r="N1" s="264"/>
+      <c r="O1" s="264"/>
+      <c r="P1" s="264"/>
+      <c r="Q1" s="264"/>
+      <c r="R1" s="264"/>
+      <c r="S1" s="264"/>
+      <c r="T1" s="264"/>
+      <c r="U1" s="264"/>
       <c r="V1" s="79"/>
       <c r="W1" s="79"/>
       <c r="X1" s="79"/>
@@ -11779,26 +11764,26 @@
     </row>
     <row r="2" spans="1:26" ht="15">
       <c r="A2" s="78"/>
-      <c r="B2" s="266"/>
-      <c r="C2" s="266"/>
-      <c r="D2" s="266"/>
-      <c r="E2" s="266"/>
-      <c r="F2" s="266"/>
-      <c r="G2" s="266"/>
-      <c r="H2" s="266"/>
-      <c r="I2" s="266"/>
-      <c r="J2" s="266"/>
-      <c r="K2" s="266"/>
-      <c r="L2" s="266"/>
-      <c r="M2" s="266"/>
-      <c r="N2" s="266"/>
-      <c r="O2" s="266"/>
-      <c r="P2" s="266"/>
-      <c r="Q2" s="266"/>
-      <c r="R2" s="266"/>
-      <c r="S2" s="266"/>
-      <c r="T2" s="266"/>
-      <c r="U2" s="266"/>
+      <c r="B2" s="264"/>
+      <c r="C2" s="264"/>
+      <c r="D2" s="264"/>
+      <c r="E2" s="264"/>
+      <c r="F2" s="264"/>
+      <c r="G2" s="264"/>
+      <c r="H2" s="264"/>
+      <c r="I2" s="264"/>
+      <c r="J2" s="264"/>
+      <c r="K2" s="264"/>
+      <c r="L2" s="264"/>
+      <c r="M2" s="264"/>
+      <c r="N2" s="264"/>
+      <c r="O2" s="264"/>
+      <c r="P2" s="264"/>
+      <c r="Q2" s="264"/>
+      <c r="R2" s="264"/>
+      <c r="S2" s="264"/>
+      <c r="T2" s="264"/>
+      <c r="U2" s="264"/>
       <c r="V2" s="79"/>
       <c r="W2" s="79"/>
       <c r="X2" s="79"/>
@@ -11807,26 +11792,26 @@
     </row>
     <row r="3" spans="1:26" ht="15">
       <c r="A3" s="78"/>
-      <c r="B3" s="266"/>
-      <c r="C3" s="266"/>
-      <c r="D3" s="266"/>
-      <c r="E3" s="266"/>
-      <c r="F3" s="266"/>
-      <c r="G3" s="266"/>
-      <c r="H3" s="266"/>
-      <c r="I3" s="266"/>
-      <c r="J3" s="266"/>
-      <c r="K3" s="266"/>
-      <c r="L3" s="266"/>
-      <c r="M3" s="266"/>
-      <c r="N3" s="266"/>
-      <c r="O3" s="266"/>
-      <c r="P3" s="266"/>
-      <c r="Q3" s="266"/>
-      <c r="R3" s="266"/>
-      <c r="S3" s="266"/>
-      <c r="T3" s="266"/>
-      <c r="U3" s="266"/>
+      <c r="B3" s="264"/>
+      <c r="C3" s="264"/>
+      <c r="D3" s="264"/>
+      <c r="E3" s="264"/>
+      <c r="F3" s="264"/>
+      <c r="G3" s="264"/>
+      <c r="H3" s="264"/>
+      <c r="I3" s="264"/>
+      <c r="J3" s="264"/>
+      <c r="K3" s="264"/>
+      <c r="L3" s="264"/>
+      <c r="M3" s="264"/>
+      <c r="N3" s="264"/>
+      <c r="O3" s="264"/>
+      <c r="P3" s="264"/>
+      <c r="Q3" s="264"/>
+      <c r="R3" s="264"/>
+      <c r="S3" s="264"/>
+      <c r="T3" s="264"/>
+      <c r="U3" s="264"/>
       <c r="V3" s="79"/>
       <c r="W3" s="79"/>
       <c r="X3" s="79"/>
@@ -11835,26 +11820,26 @@
     </row>
     <row r="4" spans="1:26" ht="15">
       <c r="A4" s="78"/>
-      <c r="B4" s="266"/>
-      <c r="C4" s="266"/>
-      <c r="D4" s="266"/>
-      <c r="E4" s="266"/>
-      <c r="F4" s="266"/>
-      <c r="G4" s="266"/>
-      <c r="H4" s="266"/>
-      <c r="I4" s="266"/>
-      <c r="J4" s="266"/>
-      <c r="K4" s="266"/>
-      <c r="L4" s="266"/>
-      <c r="M4" s="266"/>
-      <c r="N4" s="266"/>
-      <c r="O4" s="266"/>
-      <c r="P4" s="266"/>
-      <c r="Q4" s="266"/>
-      <c r="R4" s="266"/>
-      <c r="S4" s="266"/>
-      <c r="T4" s="266"/>
-      <c r="U4" s="266"/>
+      <c r="B4" s="264"/>
+      <c r="C4" s="264"/>
+      <c r="D4" s="264"/>
+      <c r="E4" s="264"/>
+      <c r="F4" s="264"/>
+      <c r="G4" s="264"/>
+      <c r="H4" s="264"/>
+      <c r="I4" s="264"/>
+      <c r="J4" s="264"/>
+      <c r="K4" s="264"/>
+      <c r="L4" s="264"/>
+      <c r="M4" s="264"/>
+      <c r="N4" s="264"/>
+      <c r="O4" s="264"/>
+      <c r="P4" s="264"/>
+      <c r="Q4" s="264"/>
+      <c r="R4" s="264"/>
+      <c r="S4" s="264"/>
+      <c r="T4" s="264"/>
+      <c r="U4" s="264"/>
       <c r="V4" s="79"/>
       <c r="W4" s="79"/>
       <c r="X4" s="79"/>
@@ -11863,26 +11848,26 @@
     </row>
     <row r="5" spans="1:26" ht="15">
       <c r="A5" s="78"/>
-      <c r="B5" s="266"/>
-      <c r="C5" s="266"/>
-      <c r="D5" s="266"/>
-      <c r="E5" s="266"/>
-      <c r="F5" s="266"/>
-      <c r="G5" s="266"/>
-      <c r="H5" s="266"/>
-      <c r="I5" s="266"/>
-      <c r="J5" s="266"/>
-      <c r="K5" s="266"/>
-      <c r="L5" s="266"/>
-      <c r="M5" s="266"/>
-      <c r="N5" s="266"/>
-      <c r="O5" s="266"/>
-      <c r="P5" s="266"/>
-      <c r="Q5" s="266"/>
-      <c r="R5" s="266"/>
-      <c r="S5" s="266"/>
-      <c r="T5" s="266"/>
-      <c r="U5" s="266"/>
+      <c r="B5" s="264"/>
+      <c r="C5" s="264"/>
+      <c r="D5" s="264"/>
+      <c r="E5" s="264"/>
+      <c r="F5" s="264"/>
+      <c r="G5" s="264"/>
+      <c r="H5" s="264"/>
+      <c r="I5" s="264"/>
+      <c r="J5" s="264"/>
+      <c r="K5" s="264"/>
+      <c r="L5" s="264"/>
+      <c r="M5" s="264"/>
+      <c r="N5" s="264"/>
+      <c r="O5" s="264"/>
+      <c r="P5" s="264"/>
+      <c r="Q5" s="264"/>
+      <c r="R5" s="264"/>
+      <c r="S5" s="264"/>
+      <c r="T5" s="264"/>
+      <c r="U5" s="264"/>
       <c r="V5" s="79"/>
       <c r="W5" s="79"/>
       <c r="X5" s="79"/>
@@ -11890,53 +11875,53 @@
       <c r="Z5" s="79"/>
     </row>
     <row r="6" spans="1:26" ht="30">
-      <c r="A6" s="278" t="s">
+      <c r="A6" s="276" t="s">
         <v>228</v>
       </c>
-      <c r="B6" s="278"/>
-      <c r="C6" s="278"/>
-      <c r="D6" s="278"/>
-      <c r="E6" s="278"/>
-      <c r="F6" s="278"/>
-      <c r="G6" s="278"/>
-      <c r="H6" s="278"/>
-      <c r="I6" s="278"/>
-      <c r="J6" s="278"/>
-      <c r="K6" s="278"/>
-      <c r="L6" s="278"/>
-      <c r="M6" s="278"/>
-      <c r="N6" s="278"/>
-      <c r="O6" s="278"/>
-      <c r="P6" s="278"/>
-      <c r="Q6" s="278"/>
-      <c r="R6" s="278"/>
-      <c r="S6" s="278"/>
-      <c r="T6" s="278"/>
-      <c r="U6" s="278"/>
-      <c r="V6" s="278"/>
-      <c r="W6" s="278"/>
-      <c r="X6" s="278"/>
-      <c r="Y6" s="278"/>
-      <c r="Z6" s="278"/>
+      <c r="B6" s="276"/>
+      <c r="C6" s="276"/>
+      <c r="D6" s="276"/>
+      <c r="E6" s="276"/>
+      <c r="F6" s="276"/>
+      <c r="G6" s="276"/>
+      <c r="H6" s="276"/>
+      <c r="I6" s="276"/>
+      <c r="J6" s="276"/>
+      <c r="K6" s="276"/>
+      <c r="L6" s="276"/>
+      <c r="M6" s="276"/>
+      <c r="N6" s="276"/>
+      <c r="O6" s="276"/>
+      <c r="P6" s="276"/>
+      <c r="Q6" s="276"/>
+      <c r="R6" s="276"/>
+      <c r="S6" s="276"/>
+      <c r="T6" s="276"/>
+      <c r="U6" s="276"/>
+      <c r="V6" s="276"/>
+      <c r="W6" s="276"/>
+      <c r="X6" s="276"/>
+      <c r="Y6" s="276"/>
+      <c r="Z6" s="276"/>
     </row>
     <row r="7" spans="1:26" s="14" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A7" s="267" t="s">
+      <c r="A7" s="265" t="s">
         <v>228</v>
       </c>
-      <c r="B7" s="267"/>
+      <c r="B7" s="265"/>
       <c r="C7" s="72" t="s">
         <v>224</v>
       </c>
       <c r="E7" s="19"/>
       <c r="F7" s="19"/>
-      <c r="G7" s="280">
+      <c r="G7" s="278" t="str">
         <f>'ใบงาน Agilent_JOB 1.1'!F7</f>
-        <v>0</v>
-      </c>
-      <c r="H7" s="280"/>
-      <c r="I7" s="280"/>
-      <c r="J7" s="280"/>
-      <c r="K7" s="280"/>
+        <v>xxx</v>
+      </c>
+      <c r="H7" s="278"/>
+      <c r="I7" s="278"/>
+      <c r="J7" s="278"/>
+      <c r="K7" s="278"/>
       <c r="L7" s="19"/>
       <c r="M7" s="19"/>
       <c r="N7" s="19"/>
@@ -11947,404 +11932,404 @@
       <c r="S7" s="82" t="s">
         <v>87</v>
       </c>
-      <c r="W7" s="279">
-        <f>'ใบงาน Agilent_JOB 1.1'!M7</f>
+      <c r="W7" s="277">
+        <f>'ใบงาน Agilent_JOB 1.1'!N7</f>
         <v>20260803</v>
       </c>
-      <c r="X7" s="279"/>
+      <c r="X7" s="277"/>
       <c r="Y7" s="42"/>
       <c r="Z7" s="42"/>
     </row>
     <row r="8" spans="1:26" s="42" customFormat="1" ht="21" customHeight="1">
-      <c r="A8" s="96" t="s">
+      <c r="A8" s="95" t="s">
         <v>225</v>
       </c>
-      <c r="B8" s="97" t="str">
+      <c r="B8" s="96" t="str">
         <f>'ใบงาน Agilent_JOB 1.1'!F8</f>
         <v>K9801-60098</v>
       </c>
-      <c r="C8" s="97" t="s">
+      <c r="C8" s="96" t="s">
         <v>226</v>
       </c>
-      <c r="D8" s="97"/>
-      <c r="E8" s="97"/>
-      <c r="F8" s="97"/>
-      <c r="G8" s="279" t="str">
+      <c r="D8" s="96"/>
+      <c r="E8" s="96"/>
+      <c r="F8" s="96"/>
+      <c r="G8" s="277" t="str">
         <f>'ใบงาน Agilent_JOB 1.1'!F9</f>
         <v>K9801-60079</v>
       </c>
-      <c r="H8" s="279"/>
-      <c r="I8" s="279"/>
-      <c r="J8" s="279"/>
-      <c r="K8" s="97"/>
-      <c r="L8" s="97"/>
-      <c r="M8" s="97"/>
-      <c r="N8" s="97"/>
-      <c r="O8" s="97"/>
-      <c r="P8" s="97"/>
-      <c r="Q8" s="97"/>
-      <c r="R8" s="97"/>
-      <c r="S8" s="97" t="s">
+      <c r="H8" s="277"/>
+      <c r="I8" s="277"/>
+      <c r="J8" s="277"/>
+      <c r="K8" s="96"/>
+      <c r="L8" s="96"/>
+      <c r="M8" s="96"/>
+      <c r="N8" s="96"/>
+      <c r="O8" s="96"/>
+      <c r="P8" s="96"/>
+      <c r="Q8" s="96"/>
+      <c r="R8" s="96"/>
+      <c r="S8" s="96" t="s">
         <v>242</v>
       </c>
-      <c r="U8" s="96"/>
-      <c r="V8" s="98"/>
-      <c r="W8" s="99" t="str">
-        <f>'ใบงาน Agilent_JOB 1.1'!M9</f>
+      <c r="U8" s="95"/>
+      <c r="V8" s="97"/>
+      <c r="W8" s="98" t="str">
+        <f>'ใบงาน Agilent_JOB 1.1'!N9</f>
         <v>PO12345</v>
       </c>
-      <c r="X8" s="99"/>
-      <c r="Y8" s="99"/>
-      <c r="Z8" s="99"/>
+      <c r="X8" s="98"/>
+      <c r="Y8" s="98"/>
+      <c r="Z8" s="98"/>
     </row>
     <row r="9" spans="1:26" s="42" customFormat="1" ht="13.8">
-      <c r="A9" s="268" t="s">
+      <c r="A9" s="266" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="268"/>
-      <c r="G9" s="279" t="str">
+      <c r="B9" s="266"/>
+      <c r="G9" s="277" t="str">
         <f>'ใบงาน Agilent_JOB 1.2'!F9</f>
         <v>K9801-60080</v>
       </c>
-      <c r="H9" s="279"/>
-      <c r="I9" s="279"/>
-      <c r="J9" s="279"/>
-      <c r="L9" s="101"/>
-      <c r="M9" s="101"/>
-      <c r="N9" s="101"/>
-      <c r="O9" s="101"/>
-      <c r="P9" s="101"/>
-      <c r="Q9" s="101"/>
-      <c r="R9" s="101"/>
+      <c r="H9" s="277"/>
+      <c r="I9" s="277"/>
+      <c r="J9" s="277"/>
+      <c r="L9" s="100"/>
+      <c r="M9" s="100"/>
+      <c r="N9" s="100"/>
+      <c r="O9" s="100"/>
+      <c r="P9" s="100"/>
+      <c r="Q9" s="100"/>
+      <c r="R9" s="100"/>
     </row>
     <row r="10" spans="1:26" s="42" customFormat="1" ht="13.8">
-      <c r="A10" s="97" t="s">
+      <c r="A10" s="96" t="s">
         <v>246</v>
       </c>
-      <c r="B10" s="101">
-        <f>'ใบงาน Agilent_JOB 1.1'!M8/50</f>
+      <c r="B10" s="100">
+        <f>'ใบงาน Agilent_JOB 1.1'!N8/50</f>
         <v>40</v>
       </c>
-      <c r="C10" s="101"/>
-      <c r="D10" s="226" t="s">
+      <c r="C10" s="100"/>
+      <c r="D10" s="224" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="226"/>
-      <c r="F10" s="226"/>
-      <c r="G10" s="226" t="str">
+      <c r="E10" s="224"/>
+      <c r="F10" s="224"/>
+      <c r="G10" s="224" t="str">
         <f>'ใบงาน Agilent_JOB 1.3'!F9</f>
         <v>K9801-60081</v>
       </c>
-      <c r="H10" s="226"/>
-      <c r="I10" s="226"/>
-      <c r="J10" s="226"/>
-      <c r="K10" s="100"/>
-      <c r="L10" s="101"/>
-      <c r="M10" s="101"/>
-      <c r="N10" s="101"/>
-      <c r="O10" s="101"/>
-      <c r="P10" s="101"/>
-      <c r="Q10" s="101"/>
-      <c r="R10" s="101"/>
+      <c r="H10" s="224"/>
+      <c r="I10" s="224"/>
+      <c r="J10" s="224"/>
+      <c r="K10" s="99"/>
+      <c r="L10" s="100"/>
+      <c r="M10" s="100"/>
+      <c r="N10" s="100"/>
+      <c r="O10" s="100"/>
+      <c r="P10" s="100"/>
+      <c r="Q10" s="100"/>
+      <c r="R10" s="100"/>
     </row>
     <row r="11" spans="1:26" s="42" customFormat="1" ht="16.95" customHeight="1">
-      <c r="B11" s="226"/>
-      <c r="C11" s="101"/>
-      <c r="D11" s="101"/>
-      <c r="E11" s="101"/>
-      <c r="F11" s="101"/>
-      <c r="G11" s="226" t="str">
+      <c r="B11" s="224"/>
+      <c r="C11" s="100"/>
+      <c r="D11" s="100"/>
+      <c r="E11" s="100"/>
+      <c r="F11" s="100"/>
+      <c r="G11" s="224" t="str">
         <f>'ใบงาน Agilent_JOB 1.4'!F9</f>
         <v>K9801-60084</v>
       </c>
-      <c r="H11" s="226"/>
-      <c r="I11" s="226"/>
-      <c r="J11" s="226"/>
-      <c r="K11" s="101"/>
-      <c r="L11" s="101"/>
-      <c r="M11" s="101"/>
-      <c r="N11" s="101"/>
-      <c r="O11" s="101"/>
-      <c r="P11" s="101"/>
-      <c r="Q11" s="101"/>
-      <c r="R11" s="101"/>
-      <c r="S11" s="282" t="s">
+      <c r="H11" s="224"/>
+      <c r="I11" s="224"/>
+      <c r="J11" s="224"/>
+      <c r="K11" s="100"/>
+      <c r="L11" s="100"/>
+      <c r="M11" s="100"/>
+      <c r="N11" s="100"/>
+      <c r="O11" s="100"/>
+      <c r="P11" s="100"/>
+      <c r="Q11" s="100"/>
+      <c r="R11" s="100"/>
+      <c r="S11" s="279" t="s">
         <v>245</v>
       </c>
-      <c r="T11" s="282"/>
-      <c r="U11" s="282"/>
-      <c r="V11" s="282"/>
+      <c r="T11" s="279"/>
+      <c r="U11" s="279"/>
+      <c r="V11" s="279"/>
     </row>
     <row r="12" spans="1:26" s="42" customFormat="1" ht="13.8">
-      <c r="A12" s="101" t="s">
+      <c r="A12" s="100" t="s">
         <v>243</v>
       </c>
-      <c r="B12" s="226"/>
-      <c r="C12" s="101"/>
-      <c r="D12" s="101"/>
-      <c r="E12" s="101"/>
-      <c r="F12" s="101"/>
-      <c r="G12" s="226" t="str">
+      <c r="B12" s="224"/>
+      <c r="C12" s="100"/>
+      <c r="D12" s="100"/>
+      <c r="E12" s="100"/>
+      <c r="F12" s="100"/>
+      <c r="G12" s="224" t="str">
         <f>'ใบงาน Agilent_JOB 1.5'!F9</f>
         <v>K9801-60085</v>
       </c>
-      <c r="H12" s="226"/>
-      <c r="I12" s="226"/>
-      <c r="J12" s="226"/>
-      <c r="K12" s="101"/>
-      <c r="L12" s="101"/>
-      <c r="M12" s="101"/>
-      <c r="N12" s="101"/>
-      <c r="O12" s="101"/>
-      <c r="P12" s="101"/>
-      <c r="Q12" s="101"/>
-      <c r="R12" s="101"/>
-      <c r="S12" s="282"/>
-      <c r="T12" s="282"/>
-      <c r="U12" s="282"/>
-      <c r="V12" s="282"/>
+      <c r="H12" s="224"/>
+      <c r="I12" s="224"/>
+      <c r="J12" s="224"/>
+      <c r="K12" s="100"/>
+      <c r="L12" s="100"/>
+      <c r="M12" s="100"/>
+      <c r="N12" s="100"/>
+      <c r="O12" s="100"/>
+      <c r="P12" s="100"/>
+      <c r="Q12" s="100"/>
+      <c r="R12" s="100"/>
+      <c r="S12" s="279"/>
+      <c r="T12" s="279"/>
+      <c r="U12" s="279"/>
+      <c r="V12" s="279"/>
     </row>
     <row r="13" spans="1:26" s="42" customFormat="1" ht="13.8">
-      <c r="A13" s="101"/>
-      <c r="B13" s="281"/>
-      <c r="C13" s="101"/>
-      <c r="D13" s="101"/>
-      <c r="E13" s="101"/>
-      <c r="F13" s="101"/>
-      <c r="G13" s="100"/>
-      <c r="H13" s="101"/>
-      <c r="I13" s="101"/>
-      <c r="J13" s="101"/>
-      <c r="K13" s="101"/>
-      <c r="L13" s="101"/>
-      <c r="M13" s="101"/>
-      <c r="N13" s="101"/>
-      <c r="O13" s="101"/>
-      <c r="P13" s="101"/>
-      <c r="Q13" s="101"/>
-      <c r="R13" s="101"/>
-      <c r="S13" s="101"/>
-      <c r="T13" s="101"/>
+      <c r="A13" s="100"/>
+      <c r="B13" s="280"/>
+      <c r="C13" s="100"/>
+      <c r="D13" s="100"/>
+      <c r="E13" s="100"/>
+      <c r="F13" s="100"/>
+      <c r="G13" s="99"/>
+      <c r="H13" s="100"/>
+      <c r="I13" s="100"/>
+      <c r="J13" s="100"/>
+      <c r="K13" s="100"/>
+      <c r="L13" s="100"/>
+      <c r="M13" s="100"/>
+      <c r="N13" s="100"/>
+      <c r="O13" s="100"/>
+      <c r="P13" s="100"/>
+      <c r="Q13" s="100"/>
+      <c r="R13" s="100"/>
+      <c r="S13" s="100"/>
+      <c r="T13" s="100"/>
     </row>
     <row r="14" spans="1:26" s="14" customFormat="1" ht="13.8">
-      <c r="A14" s="269" t="s">
+      <c r="A14" s="267" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="269" t="s">
+      <c r="B14" s="267" t="s">
         <v>105</v>
       </c>
-      <c r="C14" s="197" t="s">
+      <c r="C14" s="195" t="s">
         <v>106</v>
       </c>
-      <c r="D14" s="271"/>
-      <c r="E14" s="271"/>
-      <c r="F14" s="271"/>
-      <c r="G14" s="271"/>
-      <c r="H14" s="272"/>
-      <c r="I14" s="197" t="s">
+      <c r="D14" s="269"/>
+      <c r="E14" s="269"/>
+      <c r="F14" s="269"/>
+      <c r="G14" s="269"/>
+      <c r="H14" s="270"/>
+      <c r="I14" s="195" t="s">
         <v>39</v>
       </c>
-      <c r="J14" s="271"/>
-      <c r="K14" s="271"/>
-      <c r="L14" s="271"/>
-      <c r="M14" s="271"/>
-      <c r="N14" s="272"/>
-      <c r="O14" s="197" t="s">
+      <c r="J14" s="269"/>
+      <c r="K14" s="269"/>
+      <c r="L14" s="269"/>
+      <c r="M14" s="269"/>
+      <c r="N14" s="270"/>
+      <c r="O14" s="195" t="s">
         <v>40</v>
       </c>
-      <c r="P14" s="275"/>
-      <c r="Q14" s="275"/>
-      <c r="R14" s="275"/>
-      <c r="S14" s="275"/>
-      <c r="T14" s="198"/>
-      <c r="U14" s="277" t="s">
+      <c r="P14" s="273"/>
+      <c r="Q14" s="273"/>
+      <c r="R14" s="273"/>
+      <c r="S14" s="273"/>
+      <c r="T14" s="196"/>
+      <c r="U14" s="275" t="s">
         <v>107</v>
       </c>
-      <c r="V14" s="277"/>
-      <c r="W14" s="277"/>
-      <c r="X14" s="277"/>
-      <c r="Y14" s="277"/>
-      <c r="Z14" s="277"/>
+      <c r="V14" s="275"/>
+      <c r="W14" s="275"/>
+      <c r="X14" s="275"/>
+      <c r="Y14" s="275"/>
+      <c r="Z14" s="275"/>
     </row>
     <row r="15" spans="1:26" s="14" customFormat="1" ht="13.8">
-      <c r="A15" s="270"/>
-      <c r="B15" s="269"/>
-      <c r="C15" s="193"/>
-      <c r="D15" s="273"/>
-      <c r="E15" s="273"/>
-      <c r="F15" s="273"/>
-      <c r="G15" s="273"/>
-      <c r="H15" s="274"/>
-      <c r="I15" s="193"/>
-      <c r="J15" s="273"/>
-      <c r="K15" s="273"/>
-      <c r="L15" s="273"/>
-      <c r="M15" s="273"/>
-      <c r="N15" s="274"/>
-      <c r="O15" s="199"/>
-      <c r="P15" s="276"/>
-      <c r="Q15" s="276"/>
-      <c r="R15" s="276"/>
-      <c r="S15" s="276"/>
-      <c r="T15" s="200"/>
-      <c r="U15" s="277"/>
-      <c r="V15" s="277"/>
-      <c r="W15" s="277"/>
-      <c r="X15" s="277"/>
-      <c r="Y15" s="277"/>
-      <c r="Z15" s="277"/>
+      <c r="A15" s="268"/>
+      <c r="B15" s="267"/>
+      <c r="C15" s="191"/>
+      <c r="D15" s="271"/>
+      <c r="E15" s="271"/>
+      <c r="F15" s="271"/>
+      <c r="G15" s="271"/>
+      <c r="H15" s="272"/>
+      <c r="I15" s="191"/>
+      <c r="J15" s="271"/>
+      <c r="K15" s="271"/>
+      <c r="L15" s="271"/>
+      <c r="M15" s="271"/>
+      <c r="N15" s="272"/>
+      <c r="O15" s="197"/>
+      <c r="P15" s="274"/>
+      <c r="Q15" s="274"/>
+      <c r="R15" s="274"/>
+      <c r="S15" s="274"/>
+      <c r="T15" s="198"/>
+      <c r="U15" s="275"/>
+      <c r="V15" s="275"/>
+      <c r="W15" s="275"/>
+      <c r="X15" s="275"/>
+      <c r="Y15" s="275"/>
+      <c r="Z15" s="275"/>
     </row>
     <row r="16" spans="1:26" s="83" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A16" s="263">
+      <c r="A16" s="261">
         <v>1</v>
       </c>
       <c r="B16" s="86" t="s">
         <v>109</v>
       </c>
-      <c r="C16" s="227"/>
-      <c r="D16" s="227"/>
-      <c r="E16" s="227"/>
-      <c r="F16" s="227"/>
-      <c r="G16" s="227"/>
-      <c r="H16" s="227"/>
-      <c r="I16" s="227"/>
-      <c r="J16" s="227"/>
-      <c r="K16" s="227"/>
-      <c r="L16" s="227"/>
-      <c r="M16" s="227"/>
-      <c r="N16" s="227"/>
-      <c r="O16" s="227"/>
-      <c r="P16" s="227"/>
-      <c r="Q16" s="227"/>
-      <c r="R16" s="227"/>
-      <c r="S16" s="227"/>
-      <c r="T16" s="227"/>
-      <c r="U16" s="227"/>
-      <c r="V16" s="227"/>
-      <c r="W16" s="227"/>
-      <c r="X16" s="227"/>
-      <c r="Y16" s="227"/>
-      <c r="Z16" s="227"/>
+      <c r="C16" s="225"/>
+      <c r="D16" s="225"/>
+      <c r="E16" s="225"/>
+      <c r="F16" s="225"/>
+      <c r="G16" s="225"/>
+      <c r="H16" s="225"/>
+      <c r="I16" s="225"/>
+      <c r="J16" s="225"/>
+      <c r="K16" s="225"/>
+      <c r="L16" s="225"/>
+      <c r="M16" s="225"/>
+      <c r="N16" s="225"/>
+      <c r="O16" s="225"/>
+      <c r="P16" s="225"/>
+      <c r="Q16" s="225"/>
+      <c r="R16" s="225"/>
+      <c r="S16" s="225"/>
+      <c r="T16" s="225"/>
+      <c r="U16" s="225"/>
+      <c r="V16" s="225"/>
+      <c r="W16" s="225"/>
+      <c r="X16" s="225"/>
+      <c r="Y16" s="225"/>
+      <c r="Z16" s="225"/>
     </row>
     <row r="17" spans="1:26" s="83" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A17" s="264"/>
+      <c r="A17" s="262"/>
       <c r="B17" s="86" t="s">
         <v>110</v>
       </c>
-      <c r="C17" s="227"/>
-      <c r="D17" s="227"/>
-      <c r="E17" s="227"/>
-      <c r="F17" s="227"/>
-      <c r="G17" s="227"/>
-      <c r="H17" s="227"/>
-      <c r="I17" s="227"/>
-      <c r="J17" s="227"/>
-      <c r="K17" s="227"/>
-      <c r="L17" s="227"/>
-      <c r="M17" s="227"/>
-      <c r="N17" s="227"/>
-      <c r="O17" s="227"/>
-      <c r="P17" s="227"/>
-      <c r="Q17" s="227"/>
-      <c r="R17" s="227"/>
-      <c r="S17" s="227"/>
-      <c r="T17" s="227"/>
-      <c r="U17" s="227"/>
-      <c r="V17" s="227"/>
-      <c r="W17" s="227"/>
-      <c r="X17" s="227"/>
-      <c r="Y17" s="227"/>
-      <c r="Z17" s="227"/>
+      <c r="C17" s="225"/>
+      <c r="D17" s="225"/>
+      <c r="E17" s="225"/>
+      <c r="F17" s="225"/>
+      <c r="G17" s="225"/>
+      <c r="H17" s="225"/>
+      <c r="I17" s="225"/>
+      <c r="J17" s="225"/>
+      <c r="K17" s="225"/>
+      <c r="L17" s="225"/>
+      <c r="M17" s="225"/>
+      <c r="N17" s="225"/>
+      <c r="O17" s="225"/>
+      <c r="P17" s="225"/>
+      <c r="Q17" s="225"/>
+      <c r="R17" s="225"/>
+      <c r="S17" s="225"/>
+      <c r="T17" s="225"/>
+      <c r="U17" s="225"/>
+      <c r="V17" s="225"/>
+      <c r="W17" s="225"/>
+      <c r="X17" s="225"/>
+      <c r="Y17" s="225"/>
+      <c r="Z17" s="225"/>
     </row>
     <row r="18" spans="1:26" s="83" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A18" s="264"/>
+      <c r="A18" s="262"/>
       <c r="B18" s="86" t="s">
         <v>111</v>
       </c>
-      <c r="C18" s="227"/>
-      <c r="D18" s="227"/>
-      <c r="E18" s="227"/>
-      <c r="F18" s="227"/>
-      <c r="G18" s="227"/>
-      <c r="H18" s="227"/>
-      <c r="I18" s="227"/>
-      <c r="J18" s="227"/>
-      <c r="K18" s="227"/>
-      <c r="L18" s="227"/>
-      <c r="M18" s="227"/>
-      <c r="N18" s="227"/>
-      <c r="O18" s="227"/>
-      <c r="P18" s="227"/>
-      <c r="Q18" s="227"/>
-      <c r="R18" s="227"/>
-      <c r="S18" s="227"/>
-      <c r="T18" s="227"/>
-      <c r="U18" s="227"/>
-      <c r="V18" s="227"/>
-      <c r="W18" s="227"/>
-      <c r="X18" s="227"/>
-      <c r="Y18" s="227"/>
-      <c r="Z18" s="227"/>
+      <c r="C18" s="225"/>
+      <c r="D18" s="225"/>
+      <c r="E18" s="225"/>
+      <c r="F18" s="225"/>
+      <c r="G18" s="225"/>
+      <c r="H18" s="225"/>
+      <c r="I18" s="225"/>
+      <c r="J18" s="225"/>
+      <c r="K18" s="225"/>
+      <c r="L18" s="225"/>
+      <c r="M18" s="225"/>
+      <c r="N18" s="225"/>
+      <c r="O18" s="225"/>
+      <c r="P18" s="225"/>
+      <c r="Q18" s="225"/>
+      <c r="R18" s="225"/>
+      <c r="S18" s="225"/>
+      <c r="T18" s="225"/>
+      <c r="U18" s="225"/>
+      <c r="V18" s="225"/>
+      <c r="W18" s="225"/>
+      <c r="X18" s="225"/>
+      <c r="Y18" s="225"/>
+      <c r="Z18" s="225"/>
     </row>
     <row r="19" spans="1:26" s="83" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A19" s="264"/>
+      <c r="A19" s="262"/>
       <c r="B19" s="86" t="s">
         <v>112</v>
       </c>
-      <c r="C19" s="227"/>
-      <c r="D19" s="227"/>
-      <c r="E19" s="227"/>
-      <c r="F19" s="227"/>
-      <c r="G19" s="227"/>
-      <c r="H19" s="227"/>
-      <c r="I19" s="227"/>
-      <c r="J19" s="227"/>
-      <c r="K19" s="227"/>
-      <c r="L19" s="227"/>
-      <c r="M19" s="227"/>
-      <c r="N19" s="227"/>
-      <c r="O19" s="227"/>
-      <c r="P19" s="227"/>
-      <c r="Q19" s="227"/>
-      <c r="R19" s="227"/>
-      <c r="S19" s="227"/>
-      <c r="T19" s="227"/>
-      <c r="U19" s="227"/>
-      <c r="V19" s="227"/>
-      <c r="W19" s="227"/>
-      <c r="X19" s="227"/>
-      <c r="Y19" s="227"/>
-      <c r="Z19" s="227"/>
+      <c r="C19" s="225"/>
+      <c r="D19" s="225"/>
+      <c r="E19" s="225"/>
+      <c r="F19" s="225"/>
+      <c r="G19" s="225"/>
+      <c r="H19" s="225"/>
+      <c r="I19" s="225"/>
+      <c r="J19" s="225"/>
+      <c r="K19" s="225"/>
+      <c r="L19" s="225"/>
+      <c r="M19" s="225"/>
+      <c r="N19" s="225"/>
+      <c r="O19" s="225"/>
+      <c r="P19" s="225"/>
+      <c r="Q19" s="225"/>
+      <c r="R19" s="225"/>
+      <c r="S19" s="225"/>
+      <c r="T19" s="225"/>
+      <c r="U19" s="225"/>
+      <c r="V19" s="225"/>
+      <c r="W19" s="225"/>
+      <c r="X19" s="225"/>
+      <c r="Y19" s="225"/>
+      <c r="Z19" s="225"/>
     </row>
     <row r="20" spans="1:26" s="83" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A20" s="265"/>
+      <c r="A20" s="263"/>
       <c r="B20" s="86" t="s">
         <v>113</v>
       </c>
-      <c r="C20" s="227"/>
-      <c r="D20" s="227"/>
-      <c r="E20" s="227"/>
-      <c r="F20" s="227"/>
-      <c r="G20" s="227"/>
-      <c r="H20" s="227"/>
-      <c r="I20" s="227"/>
-      <c r="J20" s="227"/>
-      <c r="K20" s="227"/>
-      <c r="L20" s="227"/>
-      <c r="M20" s="227"/>
-      <c r="N20" s="227"/>
-      <c r="O20" s="227"/>
-      <c r="P20" s="227"/>
-      <c r="Q20" s="227"/>
-      <c r="R20" s="227"/>
-      <c r="S20" s="227"/>
-      <c r="T20" s="227"/>
-      <c r="U20" s="227"/>
-      <c r="V20" s="227"/>
-      <c r="W20" s="227"/>
-      <c r="X20" s="227"/>
-      <c r="Y20" s="227"/>
-      <c r="Z20" s="227"/>
+      <c r="C20" s="225"/>
+      <c r="D20" s="225"/>
+      <c r="E20" s="225"/>
+      <c r="F20" s="225"/>
+      <c r="G20" s="225"/>
+      <c r="H20" s="225"/>
+      <c r="I20" s="225"/>
+      <c r="J20" s="225"/>
+      <c r="K20" s="225"/>
+      <c r="L20" s="225"/>
+      <c r="M20" s="225"/>
+      <c r="N20" s="225"/>
+      <c r="O20" s="225"/>
+      <c r="P20" s="225"/>
+      <c r="Q20" s="225"/>
+      <c r="R20" s="225"/>
+      <c r="S20" s="225"/>
+      <c r="T20" s="225"/>
+      <c r="U20" s="225"/>
+      <c r="V20" s="225"/>
+      <c r="W20" s="225"/>
+      <c r="X20" s="225"/>
+      <c r="Y20" s="225"/>
+      <c r="Z20" s="225"/>
     </row>
     <row r="21" spans="1:26" s="83" customFormat="1" ht="22.5" customHeight="1">
       <c r="A21" s="84">
@@ -12353,30 +12338,30 @@
       <c r="B21" s="85" t="s">
         <v>114</v>
       </c>
-      <c r="C21" s="227"/>
-      <c r="D21" s="227"/>
-      <c r="E21" s="227"/>
-      <c r="F21" s="227"/>
-      <c r="G21" s="227"/>
-      <c r="H21" s="227"/>
-      <c r="I21" s="227"/>
-      <c r="J21" s="227"/>
-      <c r="K21" s="227"/>
-      <c r="L21" s="227"/>
-      <c r="M21" s="227"/>
-      <c r="N21" s="227"/>
-      <c r="O21" s="227"/>
-      <c r="P21" s="227"/>
-      <c r="Q21" s="227"/>
-      <c r="R21" s="227"/>
-      <c r="S21" s="227"/>
-      <c r="T21" s="227"/>
-      <c r="U21" s="227"/>
-      <c r="V21" s="227"/>
-      <c r="W21" s="227"/>
-      <c r="X21" s="227"/>
-      <c r="Y21" s="227"/>
-      <c r="Z21" s="227"/>
+      <c r="C21" s="225"/>
+      <c r="D21" s="225"/>
+      <c r="E21" s="225"/>
+      <c r="F21" s="225"/>
+      <c r="G21" s="225"/>
+      <c r="H21" s="225"/>
+      <c r="I21" s="225"/>
+      <c r="J21" s="225"/>
+      <c r="K21" s="225"/>
+      <c r="L21" s="225"/>
+      <c r="M21" s="225"/>
+      <c r="N21" s="225"/>
+      <c r="O21" s="225"/>
+      <c r="P21" s="225"/>
+      <c r="Q21" s="225"/>
+      <c r="R21" s="225"/>
+      <c r="S21" s="225"/>
+      <c r="T21" s="225"/>
+      <c r="U21" s="225"/>
+      <c r="V21" s="225"/>
+      <c r="W21" s="225"/>
+      <c r="X21" s="225"/>
+      <c r="Y21" s="225"/>
+      <c r="Z21" s="225"/>
     </row>
     <row r="22" spans="1:26" s="83" customFormat="1" ht="22.5" customHeight="1">
       <c r="A22" s="84">
@@ -12385,30 +12370,30 @@
       <c r="B22" s="85" t="s">
         <v>241</v>
       </c>
-      <c r="C22" s="227"/>
-      <c r="D22" s="227"/>
-      <c r="E22" s="227"/>
-      <c r="F22" s="227"/>
-      <c r="G22" s="227"/>
-      <c r="H22" s="227"/>
-      <c r="I22" s="227"/>
-      <c r="J22" s="227"/>
-      <c r="K22" s="227"/>
-      <c r="L22" s="227"/>
-      <c r="M22" s="227"/>
-      <c r="N22" s="227"/>
-      <c r="O22" s="227"/>
-      <c r="P22" s="227"/>
-      <c r="Q22" s="227"/>
-      <c r="R22" s="227"/>
-      <c r="S22" s="227"/>
-      <c r="T22" s="227"/>
-      <c r="U22" s="227"/>
-      <c r="V22" s="227"/>
-      <c r="W22" s="227"/>
-      <c r="X22" s="227"/>
-      <c r="Y22" s="227"/>
-      <c r="Z22" s="227"/>
+      <c r="C22" s="225"/>
+      <c r="D22" s="225"/>
+      <c r="E22" s="225"/>
+      <c r="F22" s="225"/>
+      <c r="G22" s="225"/>
+      <c r="H22" s="225"/>
+      <c r="I22" s="225"/>
+      <c r="J22" s="225"/>
+      <c r="K22" s="225"/>
+      <c r="L22" s="225"/>
+      <c r="M22" s="225"/>
+      <c r="N22" s="225"/>
+      <c r="O22" s="225"/>
+      <c r="P22" s="225"/>
+      <c r="Q22" s="225"/>
+      <c r="R22" s="225"/>
+      <c r="S22" s="225"/>
+      <c r="T22" s="225"/>
+      <c r="U22" s="225"/>
+      <c r="V22" s="225"/>
+      <c r="W22" s="225"/>
+      <c r="X22" s="225"/>
+      <c r="Y22" s="225"/>
+      <c r="Z22" s="225"/>
     </row>
     <row r="23" spans="1:26" s="83" customFormat="1" ht="20.7" customHeight="1">
       <c r="A23" s="84">
@@ -12417,66 +12402,65 @@
       <c r="B23" s="85" t="s">
         <v>248</v>
       </c>
-      <c r="C23" s="227"/>
-      <c r="D23" s="227"/>
-      <c r="E23" s="227"/>
-      <c r="F23" s="227"/>
-      <c r="G23" s="227"/>
-      <c r="H23" s="227"/>
-      <c r="I23" s="227"/>
-      <c r="J23" s="227"/>
-      <c r="K23" s="227"/>
-      <c r="L23" s="227"/>
-      <c r="M23" s="227"/>
-      <c r="N23" s="227"/>
-      <c r="O23" s="227"/>
-      <c r="P23" s="227"/>
-      <c r="Q23" s="227"/>
-      <c r="R23" s="227"/>
-      <c r="S23" s="227"/>
-      <c r="T23" s="227"/>
-      <c r="U23" s="227"/>
-      <c r="V23" s="227"/>
-      <c r="W23" s="227"/>
-      <c r="X23" s="227"/>
-      <c r="Y23" s="227"/>
-      <c r="Z23" s="227"/>
+      <c r="C23" s="225"/>
+      <c r="D23" s="225"/>
+      <c r="E23" s="225"/>
+      <c r="F23" s="225"/>
+      <c r="G23" s="225"/>
+      <c r="H23" s="225"/>
+      <c r="I23" s="225"/>
+      <c r="J23" s="225"/>
+      <c r="K23" s="225"/>
+      <c r="L23" s="225"/>
+      <c r="M23" s="225"/>
+      <c r="N23" s="225"/>
+      <c r="O23" s="225"/>
+      <c r="P23" s="225"/>
+      <c r="Q23" s="225"/>
+      <c r="R23" s="225"/>
+      <c r="S23" s="225"/>
+      <c r="T23" s="225"/>
+      <c r="U23" s="225"/>
+      <c r="V23" s="225"/>
+      <c r="W23" s="225"/>
+      <c r="X23" s="225"/>
+      <c r="Y23" s="225"/>
+      <c r="Z23" s="225"/>
     </row>
     <row r="24" spans="1:26" s="14" customFormat="1" ht="13.8">
       <c r="A24" s="13"/>
-      <c r="C24" s="244"/>
-      <c r="D24" s="244"/>
-      <c r="E24" s="244"/>
-      <c r="F24" s="244"/>
+      <c r="C24" s="242"/>
+      <c r="D24" s="242"/>
+      <c r="E24" s="242"/>
+      <c r="F24" s="242"/>
     </row>
     <row r="25" spans="1:26" s="87" customFormat="1" ht="15">
       <c r="A25" s="88"/>
-      <c r="L25" s="256"/>
-      <c r="M25" s="256"/>
+      <c r="L25" s="254"/>
+      <c r="M25" s="254"/>
     </row>
     <row r="26" spans="1:26" s="14" customFormat="1" ht="13.8">
       <c r="A26" s="13"/>
-      <c r="L26" s="244"/>
-      <c r="M26" s="244"/>
+      <c r="L26" s="242"/>
+      <c r="M26" s="242"/>
     </row>
     <row r="27" spans="1:26" s="14" customFormat="1" ht="13.8">
       <c r="A27" s="13"/>
-      <c r="L27" s="244"/>
-      <c r="M27" s="244"/>
+      <c r="L27" s="242"/>
+      <c r="M27" s="242"/>
     </row>
     <row r="28" spans="1:26" s="14" customFormat="1" ht="13.8">
       <c r="A28" s="13"/>
-      <c r="L28" s="244"/>
-      <c r="M28" s="244"/>
+      <c r="L28" s="242"/>
+      <c r="M28" s="242"/>
     </row>
   </sheetData>
   <mergeCells count="58">
-    <mergeCell ref="G10:J10"/>
-    <mergeCell ref="G11:J11"/>
-    <mergeCell ref="G12:J12"/>
-    <mergeCell ref="S11:V12"/>
-    <mergeCell ref="O14:T15"/>
-    <mergeCell ref="U14:Z15"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:H15"/>
     <mergeCell ref="B1:U5"/>
     <mergeCell ref="A6:Z6"/>
     <mergeCell ref="A7:B7"/>
@@ -12485,24 +12469,25 @@
     <mergeCell ref="G9:J9"/>
     <mergeCell ref="G7:K7"/>
     <mergeCell ref="W7:X7"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:H15"/>
-    <mergeCell ref="I14:N15"/>
-    <mergeCell ref="D10:F10"/>
     <mergeCell ref="A16:A20"/>
     <mergeCell ref="C16:H16"/>
     <mergeCell ref="I16:N16"/>
     <mergeCell ref="O16:T16"/>
-    <mergeCell ref="U16:Z16"/>
+    <mergeCell ref="C18:H18"/>
+    <mergeCell ref="I18:N18"/>
+    <mergeCell ref="O18:T18"/>
     <mergeCell ref="C17:H17"/>
     <mergeCell ref="I17:N17"/>
     <mergeCell ref="O17:T17"/>
+    <mergeCell ref="I14:N15"/>
+    <mergeCell ref="G10:J10"/>
+    <mergeCell ref="G11:J11"/>
+    <mergeCell ref="G12:J12"/>
+    <mergeCell ref="U16:Z16"/>
+    <mergeCell ref="S11:V12"/>
+    <mergeCell ref="O14:T15"/>
+    <mergeCell ref="U14:Z15"/>
     <mergeCell ref="U17:Z17"/>
-    <mergeCell ref="C18:H18"/>
-    <mergeCell ref="I18:N18"/>
-    <mergeCell ref="O18:T18"/>
     <mergeCell ref="U18:Z18"/>
     <mergeCell ref="C19:H19"/>
     <mergeCell ref="I19:N19"/>
@@ -12519,9 +12504,9 @@
     <mergeCell ref="O22:T22"/>
     <mergeCell ref="U22:Z22"/>
     <mergeCell ref="C21:H21"/>
+    <mergeCell ref="U21:Z21"/>
     <mergeCell ref="I21:N21"/>
     <mergeCell ref="O21:T21"/>
-    <mergeCell ref="U21:Z21"/>
     <mergeCell ref="L27:M27"/>
     <mergeCell ref="L28:M28"/>
     <mergeCell ref="L25:M25"/>
